--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -1633,7 +1633,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76550462277683</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -2326,7 +2326,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70.83</v>
+        <v>70.78</v>
       </c>
       <c r="F12" t="n">
-        <v>68.63</v>
+        <v>68.56</v>
       </c>
       <c r="G12" t="n">
         <v>83.33333333333333</v>
@@ -3077,7 +3077,7 @@
         <v>83.87</v>
       </c>
       <c r="L12" t="n">
-        <v>82.55</v>
+        <v>81.88</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr"/>
@@ -5681,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>18018230272</v>
+        <v>18537529344</v>
       </c>
       <c r="AN23" t="n">
         <v>6.56</v>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63.17</v>
+        <v>63.1</v>
       </c>
       <c r="F33" t="n">
-        <v>63.73</v>
+        <v>63.64</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>83.22</v>
+        <v>82.55</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -8748,7 +8748,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62749400029969</v>
+        <v>-19.62750247023346</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -10014,7 +10014,7 @@
         <v>1</v>
       </c>
       <c r="AM42" t="n">
-        <v>171916886016</v>
+        <v>165008867328</v>
       </c>
       <c r="AN42" t="n">
         <v>6.48</v>
@@ -10108,7 +10108,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.7134172222279</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.87</v>
+        <v>59.91</v>
       </c>
       <c r="F43" t="n">
-        <v>55.73</v>
+        <v>55.78</v>
       </c>
       <c r="G43" t="n">
         <v>83.33333333333333</v>
@@ -10160,7 +10160,7 @@
         <v>78.54000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18.14</v>
+        <v>18.34</v>
       </c>
       <c r="K43" t="n">
         <v>54.08</v>
@@ -12629,7 +12629,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-19.41669381125899</v>
+        <v>-19.41668752521939</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
@@ -12649,45 +12649,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.26</v>
+        <v>57.31</v>
       </c>
       <c r="F54" t="n">
-        <v>52.65</v>
+        <v>55.66</v>
       </c>
       <c r="G54" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>56.34</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>27.79</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>74.59</v>
+        <v>63.66</v>
       </c>
       <c r="L54" t="n">
-        <v>54.36</v>
+        <v>20.13</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P54" t="n">
         <v>7</v>
@@ -12721,13 +12721,13 @@
         <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -12742,17 +12742,17 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
         <v>1</v>
       </c>
       <c r="AI54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="b">
         <v>1</v>
@@ -12762,83 +12762,83 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>1902465664</v>
+        <v>201903325184</v>
       </c>
       <c r="AN54" t="n">
-        <v>12.25</v>
+        <v>32.3</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.01</v>
+        <v>10.71</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.34</v>
+        <v>4.17</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5.97</v>
+        <v>2.33</v>
       </c>
       <c r="AR54" t="n">
-        <v>16.39</v>
+        <v>33.16</v>
       </c>
       <c r="AS54" t="n">
-        <v>10.11</v>
+        <v>24.33</v>
       </c>
       <c r="AT54" t="n">
-        <v>8.91</v>
+        <v>15.58</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="AX54" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="AY54" t="n">
-        <v>22.85000038146973</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9.75</v>
+        <v>8.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
       <c r="BB54" t="n">
-        <v>20.28</v>
+        <v>19.74</v>
       </c>
       <c r="BC54" t="n">
-        <v>21.84</v>
+        <v>12.27</v>
       </c>
       <c r="BD54" t="n">
-        <v>19.34</v>
+        <v>15.69</v>
       </c>
       <c r="BE54" t="n">
-        <v>17.21</v>
+        <v>14.11</v>
       </c>
       <c r="BF54" t="n">
-        <v>19.34</v>
+        <v>14.86</v>
       </c>
       <c r="BG54" t="n">
-        <v>17.41</v>
+        <v>13.37</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-23.81</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-24.68</v>
+        <v>-70.67</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -12854,13 +12854,13 @@
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>24.03000068664551</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR54" t="n">
-        <v>-4.910529635696426</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS54" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -12873,52 +12873,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>57.26</v>
       </c>
       <c r="F55" t="n">
-        <v>55.6</v>
+        <v>52.65</v>
       </c>
       <c r="G55" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>86.20999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="J55" t="n">
-        <v>8.25</v>
+        <v>27.79</v>
       </c>
       <c r="K55" t="n">
-        <v>63.66</v>
+        <v>74.59</v>
       </c>
       <c r="L55" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -12952,13 +12952,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -12973,17 +12973,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -12993,83 +12993,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN55" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO55" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR55" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS55" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT55" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY55" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB55" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC55" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD55" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE55" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF55" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG55" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -13085,13 +13085,13 @@
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR55" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -13143,13 +13143,13 @@
         <v>75.51000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>32.89</v>
+        <v>32.07</v>
       </c>
       <c r="K56" t="n">
         <v>22.81</v>
       </c>
       <c r="L56" t="n">
-        <v>81.88</v>
+        <v>83.89</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -13236,7 +13236,7 @@
         <v>8.33</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.06</v>
+        <v>10.3</v>
       </c>
       <c r="AR56" t="n">
         <v>23.72</v>
@@ -13255,43 +13255,43 @@
         <v>1.43</v>
       </c>
       <c r="AX56" t="n">
-        <v>3.85</v>
+        <v>4.89</v>
       </c>
       <c r="AY56" t="n">
         <v>44.79999923706055</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.21</v>
+        <v>32.96</v>
       </c>
       <c r="BA56" t="n">
-        <v>39.54</v>
+        <v>38.61</v>
       </c>
       <c r="BB56" t="n">
-        <v>43.84</v>
+        <v>41.84</v>
       </c>
       <c r="BC56" t="n">
         <v>48.76</v>
       </c>
       <c r="BD56" t="n">
-        <v>61.97</v>
+        <v>60.65</v>
       </c>
       <c r="BE56" t="n">
-        <v>45.26</v>
+        <v>44.56</v>
       </c>
       <c r="BF56" t="n">
-        <v>43.84</v>
+        <v>41.84</v>
       </c>
       <c r="BG56" t="n">
-        <v>39.46</v>
+        <v>37.66</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-11.93</v>
+        <v>-15.94</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1.03</v>
+        <v>-0.53</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.35821943150735</v>
+        <v>-16.35820625379285</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -15387,7 +15387,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82515452490343</v>
+        <v>-25.82514761546183</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -18476,7 +18476,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76550462277683</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -19169,7 +19169,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -19901,10 +19901,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70.83</v>
+        <v>70.78</v>
       </c>
       <c r="F12" t="n">
-        <v>68.63</v>
+        <v>68.56</v>
       </c>
       <c r="G12" t="n">
         <v>83.33333333333333</v>
@@ -19920,7 +19920,7 @@
         <v>83.87</v>
       </c>
       <c r="L12" t="n">
-        <v>82.55</v>
+        <v>81.88</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
@@ -21680,12 +21680,12 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr"/>
@@ -22524,7 +22524,7 @@
         <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>18018230272</v>
+        <v>18537529344</v>
       </c>
       <c r="AN23" t="n">
         <v>6.56</v>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63.17</v>
+        <v>63.1</v>
       </c>
       <c r="F33" t="n">
-        <v>63.73</v>
+        <v>63.64</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>83.22</v>
+        <v>82.55</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -25591,7 +25591,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62749400029969</v>
+        <v>-19.62750247023346</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -26857,7 +26857,7 @@
         <v>1</v>
       </c>
       <c r="AM42" t="n">
-        <v>171916886016</v>
+        <v>165008867328</v>
       </c>
       <c r="AN42" t="n">
         <v>6.48</v>
@@ -26951,7 +26951,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.7134172222279</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -26990,10 +26990,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.87</v>
+        <v>59.91</v>
       </c>
       <c r="F43" t="n">
-        <v>55.73</v>
+        <v>55.78</v>
       </c>
       <c r="G43" t="n">
         <v>83.33333333333333</v>
@@ -27003,7 +27003,7 @@
         <v>78.54000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18.14</v>
+        <v>18.34</v>
       </c>
       <c r="K43" t="n">
         <v>54.08</v>
@@ -29472,7 +29472,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-19.41669381125899</v>
+        <v>-19.41668752521939</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
@@ -29492,45 +29492,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.26</v>
+        <v>57.31</v>
       </c>
       <c r="F54" t="n">
-        <v>52.65</v>
+        <v>55.66</v>
       </c>
       <c r="G54" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>56.34</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>27.79</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>74.59</v>
+        <v>63.66</v>
       </c>
       <c r="L54" t="n">
-        <v>54.36</v>
+        <v>20.13</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -29541,7 +29541,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P54" t="n">
         <v>7</v>
@@ -29564,13 +29564,13 @@
         <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -29585,17 +29585,17 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
         <v>1</v>
       </c>
       <c r="AI54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="b">
         <v>1</v>
@@ -29605,83 +29605,83 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>1902465664</v>
+        <v>201903325184</v>
       </c>
       <c r="AN54" t="n">
-        <v>12.25</v>
+        <v>32.3</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.01</v>
+        <v>10.71</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.34</v>
+        <v>4.17</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5.97</v>
+        <v>2.33</v>
       </c>
       <c r="AR54" t="n">
-        <v>16.39</v>
+        <v>33.16</v>
       </c>
       <c r="AS54" t="n">
-        <v>10.11</v>
+        <v>24.33</v>
       </c>
       <c r="AT54" t="n">
-        <v>8.91</v>
+        <v>15.58</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="AX54" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="AY54" t="n">
-        <v>22.85000038146973</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9.75</v>
+        <v>8.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
       <c r="BB54" t="n">
-        <v>20.28</v>
+        <v>19.74</v>
       </c>
       <c r="BC54" t="n">
-        <v>21.84</v>
+        <v>12.27</v>
       </c>
       <c r="BD54" t="n">
-        <v>19.34</v>
+        <v>15.69</v>
       </c>
       <c r="BE54" t="n">
-        <v>17.21</v>
+        <v>14.11</v>
       </c>
       <c r="BF54" t="n">
-        <v>19.34</v>
+        <v>14.86</v>
       </c>
       <c r="BG54" t="n">
-        <v>17.41</v>
+        <v>13.37</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-23.81</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-24.68</v>
+        <v>-70.67</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -29697,13 +29697,13 @@
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>24.03000068664551</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR54" t="n">
-        <v>-4.910529635696426</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS54" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -29716,52 +29716,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>57.26</v>
       </c>
       <c r="F55" t="n">
-        <v>55.6</v>
+        <v>52.65</v>
       </c>
       <c r="G55" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>86.20999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="J55" t="n">
-        <v>8.25</v>
+        <v>27.79</v>
       </c>
       <c r="K55" t="n">
-        <v>63.66</v>
+        <v>74.59</v>
       </c>
       <c r="L55" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -29772,7 +29772,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -29795,13 +29795,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -29816,17 +29816,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -29836,83 +29836,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN55" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO55" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR55" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS55" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT55" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY55" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB55" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC55" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD55" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE55" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF55" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG55" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -29928,13 +29928,13 @@
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR55" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -29986,13 +29986,13 @@
         <v>75.51000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>32.89</v>
+        <v>32.07</v>
       </c>
       <c r="K56" t="n">
         <v>22.81</v>
       </c>
       <c r="L56" t="n">
-        <v>81.88</v>
+        <v>83.89</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -30079,7 +30079,7 @@
         <v>8.33</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.06</v>
+        <v>10.3</v>
       </c>
       <c r="AR56" t="n">
         <v>23.72</v>
@@ -30098,43 +30098,43 @@
         <v>1.43</v>
       </c>
       <c r="AX56" t="n">
-        <v>3.85</v>
+        <v>4.89</v>
       </c>
       <c r="AY56" t="n">
         <v>44.79999923706055</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.21</v>
+        <v>32.96</v>
       </c>
       <c r="BA56" t="n">
-        <v>39.54</v>
+        <v>38.61</v>
       </c>
       <c r="BB56" t="n">
-        <v>43.84</v>
+        <v>41.84</v>
       </c>
       <c r="BC56" t="n">
         <v>48.76</v>
       </c>
       <c r="BD56" t="n">
-        <v>61.97</v>
+        <v>60.65</v>
       </c>
       <c r="BE56" t="n">
-        <v>45.26</v>
+        <v>44.56</v>
       </c>
       <c r="BF56" t="n">
-        <v>43.84</v>
+        <v>41.84</v>
       </c>
       <c r="BG56" t="n">
-        <v>39.46</v>
+        <v>37.66</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-11.93</v>
+        <v>-15.94</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1.03</v>
+        <v>-0.53</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.35821943150735</v>
+        <v>-16.35820625379285</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -32230,7 +32230,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82515452490343</v>
+        <v>-25.82514761546183</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -35019,10 +35019,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>50.28</v>
+        <v>50.32</v>
       </c>
       <c r="F78" t="n">
-        <v>53.27</v>
+        <v>53.32</v>
       </c>
       <c r="G78" t="n">
         <v>33.33333333333334</v>
@@ -35032,7 +35032,7 @@
         <v>45.05</v>
       </c>
       <c r="J78" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="K78" t="n">
         <v>46.98</v>
@@ -35246,10 +35246,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>50.11</v>
+        <v>50.05</v>
       </c>
       <c r="F79" t="n">
-        <v>50.13</v>
+        <v>50.06</v>
       </c>
       <c r="G79" t="n">
         <v>50</v>
@@ -35265,7 +35265,7 @@
         <v>42.11</v>
       </c>
       <c r="L79" t="n">
-        <v>83.89</v>
+        <v>83.22</v>
       </c>
       <c r="M79" t="n">
         <v>78</v>
@@ -36698,7 +36698,7 @@
         <v>1</v>
       </c>
       <c r="AM85" t="n">
-        <v>13472881664</v>
+        <v>13473802240</v>
       </c>
       <c r="AN85" t="n">
         <v>14.53</v>
@@ -36792,7 +36792,7 @@
         <v>-2.285089473123469</v>
       </c>
       <c r="BS85" t="n">
-        <v>-17.85090042584634</v>
+        <v>-17.850910086273</v>
       </c>
       <c r="BT85" t="b">
         <v>0</v>
@@ -37913,7 +37913,7 @@
         <v>-1.900235700265374</v>
       </c>
       <c r="BS90" t="n">
-        <v>-15.22971914757722</v>
+        <v>-15.22972761158513</v>
       </c>
       <c r="BT90" t="b">
         <v>0</v>
@@ -40617,7 +40617,7 @@
         <v>-2.411569511092404</v>
       </c>
       <c r="BS102" t="n">
-        <v>-25.49989727527226</v>
+        <v>-25.49988843235376</v>
       </c>
       <c r="BT102" t="b">
         <v>0</v>
@@ -44579,7 +44579,7 @@
         <v>-9.242822111007619</v>
       </c>
       <c r="BS120" t="n">
-        <v>-19.44250955845246</v>
+        <v>-19.44251454422593</v>
       </c>
       <c r="BT120" t="b">
         <v>0</v>
@@ -45656,7 +45656,7 @@
         <v>-7.69230636971937</v>
       </c>
       <c r="BS125" t="n">
-        <v>-54.87060603413229</v>
+        <v>-54.87060095233498</v>
       </c>
       <c r="BT125" t="b">
         <v>0</v>
@@ -46370,10 +46370,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>34.58</v>
+        <v>34.62</v>
       </c>
       <c r="F129" t="n">
-        <v>34.8</v>
+        <v>34.85</v>
       </c>
       <c r="G129" t="n">
         <v>33.33333333333334</v>
@@ -46383,7 +46383,7 @@
         <v>49.38</v>
       </c>
       <c r="J129" t="n">
-        <v>27.3</v>
+        <v>27.51</v>
       </c>
       <c r="K129" t="n">
         <v>22.05</v>

--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70.78</v>
+        <v>70.83</v>
       </c>
       <c r="F12" t="n">
-        <v>68.56</v>
+        <v>68.63</v>
       </c>
       <c r="G12" t="n">
         <v>83.33333333333333</v>
@@ -3077,7 +3077,7 @@
         <v>83.87</v>
       </c>
       <c r="L12" t="n">
-        <v>81.88</v>
+        <v>82.55</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
@@ -6010,7 +6010,7 @@
         <v>-4.89390291386349</v>
       </c>
       <c r="BS24" t="n">
-        <v>-21.22606264717445</v>
+        <v>-21.22605409112423</v>
       </c>
       <c r="BT24" t="b">
         <v>1</v>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63.1</v>
+        <v>63.17</v>
       </c>
       <c r="F33" t="n">
-        <v>63.64</v>
+        <v>63.73</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>82.55</v>
+        <v>83.22</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -8517,7 +8517,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS35" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="BT35" t="b">
         <v>1</v>
@@ -8748,7 +8748,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62750247023346</v>
+        <v>-19.62749400029969</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -9666,7 +9666,7 @@
         <v>-9.81405715898066</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.91</v>
+        <v>59.87</v>
       </c>
       <c r="F43" t="n">
-        <v>55.78</v>
+        <v>55.73</v>
       </c>
       <c r="G43" t="n">
         <v>83.33333333333333</v>
@@ -10160,7 +10160,7 @@
         <v>78.54000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18.34</v>
+        <v>18.14</v>
       </c>
       <c r="K43" t="n">
         <v>54.08</v>
@@ -10787,7 +10787,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS45" t="n">
-        <v>-19.71820629342497</v>
+        <v>-19.7182148933239</v>
       </c>
       <c r="BT45" t="b">
         <v>1</v>
@@ -12629,7 +12629,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-19.41668752521939</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
@@ -12649,45 +12649,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.31</v>
+        <v>57.26</v>
       </c>
       <c r="F54" t="n">
-        <v>55.66</v>
+        <v>52.65</v>
       </c>
       <c r="G54" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>86.20999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="J54" t="n">
-        <v>8.460000000000001</v>
+        <v>27.79</v>
       </c>
       <c r="K54" t="n">
-        <v>63.66</v>
+        <v>74.59</v>
       </c>
       <c r="L54" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
         <v>7</v>
@@ -12721,13 +12721,13 @@
         <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -12742,17 +12742,17 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
         <v>1</v>
       </c>
       <c r="AI54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ54" t="b">
         <v>1</v>
@@ -12762,83 +12762,83 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN54" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO54" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP54" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR54" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS54" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT54" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX54" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY54" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ54" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB54" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC54" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD54" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE54" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF54" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG54" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -12854,13 +12854,13 @@
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR54" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS54" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -12873,52 +12873,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>57.26</v>
       </c>
       <c r="F55" t="n">
-        <v>52.65</v>
+        <v>55.6</v>
       </c>
       <c r="G55" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>56.34</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>27.79</v>
+        <v>8.25</v>
       </c>
       <c r="K55" t="n">
-        <v>74.59</v>
+        <v>63.66</v>
       </c>
       <c r="L55" t="n">
-        <v>54.36</v>
+        <v>20.13</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -12952,13 +12952,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -12973,17 +12973,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -12993,83 +12993,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>1902465664</v>
+        <v>201903325184</v>
       </c>
       <c r="AN55" t="n">
-        <v>12.25</v>
+        <v>32.3</v>
       </c>
       <c r="AO55" t="n">
-        <v>2.01</v>
+        <v>10.71</v>
       </c>
       <c r="AP55" t="n">
-        <v>9.34</v>
+        <v>4.17</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5.97</v>
+        <v>2.33</v>
       </c>
       <c r="AR55" t="n">
-        <v>16.39</v>
+        <v>33.16</v>
       </c>
       <c r="AS55" t="n">
-        <v>10.11</v>
+        <v>24.33</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.91</v>
+        <v>15.58</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="AX55" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="AY55" t="n">
-        <v>22.85000038146973</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ55" t="n">
-        <v>9.75</v>
+        <v>8.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
       <c r="BB55" t="n">
-        <v>20.28</v>
+        <v>19.74</v>
       </c>
       <c r="BC55" t="n">
-        <v>21.84</v>
+        <v>12.27</v>
       </c>
       <c r="BD55" t="n">
-        <v>19.34</v>
+        <v>15.69</v>
       </c>
       <c r="BE55" t="n">
-        <v>17.21</v>
+        <v>14.11</v>
       </c>
       <c r="BF55" t="n">
-        <v>19.34</v>
+        <v>14.86</v>
       </c>
       <c r="BG55" t="n">
-        <v>17.41</v>
+        <v>13.37</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-23.81</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-24.68</v>
+        <v>-70.67</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -13085,13 +13085,13 @@
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>24.03000068664551</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR55" t="n">
-        <v>-4.910529635696426</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.35737468710545</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -13143,13 +13143,13 @@
         <v>75.51000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>32.07</v>
+        <v>32.89</v>
       </c>
       <c r="K56" t="n">
         <v>22.81</v>
       </c>
       <c r="L56" t="n">
-        <v>83.89</v>
+        <v>81.88</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -13236,7 +13236,7 @@
         <v>8.33</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.3</v>
+        <v>10.06</v>
       </c>
       <c r="AR56" t="n">
         <v>23.72</v>
@@ -13255,43 +13255,43 @@
         <v>1.43</v>
       </c>
       <c r="AX56" t="n">
-        <v>4.89</v>
+        <v>3.85</v>
       </c>
       <c r="AY56" t="n">
         <v>44.79999923706055</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.96</v>
+        <v>32.21</v>
       </c>
       <c r="BA56" t="n">
-        <v>38.61</v>
+        <v>39.54</v>
       </c>
       <c r="BB56" t="n">
-        <v>41.84</v>
+        <v>43.84</v>
       </c>
       <c r="BC56" t="n">
         <v>48.76</v>
       </c>
       <c r="BD56" t="n">
-        <v>60.65</v>
+        <v>61.97</v>
       </c>
       <c r="BE56" t="n">
-        <v>44.56</v>
+        <v>45.26</v>
       </c>
       <c r="BF56" t="n">
-        <v>41.84</v>
+        <v>43.84</v>
       </c>
       <c r="BG56" t="n">
-        <v>37.66</v>
+        <v>39.46</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-15.94</v>
+        <v>-11.93</v>
       </c>
       <c r="BJ56" t="n">
-        <v>-0.53</v>
+        <v>1.03</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>-2.880272661462469</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.6228216922185</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -15387,7 +15387,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82514761546183</v>
+        <v>-25.82515452490343</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -19901,10 +19901,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70.78</v>
+        <v>70.83</v>
       </c>
       <c r="F12" t="n">
-        <v>68.56</v>
+        <v>68.63</v>
       </c>
       <c r="G12" t="n">
         <v>83.33333333333333</v>
@@ -19920,7 +19920,7 @@
         <v>83.87</v>
       </c>
       <c r="L12" t="n">
-        <v>81.88</v>
+        <v>82.55</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
@@ -22853,7 +22853,7 @@
         <v>-4.89390291386349</v>
       </c>
       <c r="BS24" t="n">
-        <v>-21.22606264717445</v>
+        <v>-21.22605409112423</v>
       </c>
       <c r="BT24" t="b">
         <v>1</v>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63.1</v>
+        <v>63.17</v>
       </c>
       <c r="F33" t="n">
-        <v>63.64</v>
+        <v>63.73</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>82.55</v>
+        <v>83.22</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -25360,7 +25360,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS35" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="BT35" t="b">
         <v>1</v>
@@ -25591,7 +25591,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62750247023346</v>
+        <v>-19.62749400029969</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -26509,7 +26509,7 @@
         <v>-9.81405715898066</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -26990,10 +26990,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.91</v>
+        <v>59.87</v>
       </c>
       <c r="F43" t="n">
-        <v>55.78</v>
+        <v>55.73</v>
       </c>
       <c r="G43" t="n">
         <v>83.33333333333333</v>
@@ -27003,7 +27003,7 @@
         <v>78.54000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18.34</v>
+        <v>18.14</v>
       </c>
       <c r="K43" t="n">
         <v>54.08</v>
@@ -27630,7 +27630,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS45" t="n">
-        <v>-19.71820629342497</v>
+        <v>-19.7182148933239</v>
       </c>
       <c r="BT45" t="b">
         <v>1</v>
@@ -29472,7 +29472,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-19.41668752521939</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
@@ -29492,45 +29492,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.31</v>
+        <v>57.26</v>
       </c>
       <c r="F54" t="n">
-        <v>55.66</v>
+        <v>52.65</v>
       </c>
       <c r="G54" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>86.20999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="J54" t="n">
-        <v>8.460000000000001</v>
+        <v>27.79</v>
       </c>
       <c r="K54" t="n">
-        <v>63.66</v>
+        <v>74.59</v>
       </c>
       <c r="L54" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -29541,7 +29541,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
         <v>7</v>
@@ -29564,13 +29564,13 @@
         <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -29585,17 +29585,17 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
         <v>1</v>
       </c>
       <c r="AI54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ54" t="b">
         <v>1</v>
@@ -29605,83 +29605,83 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN54" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO54" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP54" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR54" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS54" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT54" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX54" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY54" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ54" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB54" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC54" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD54" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE54" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF54" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG54" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -29697,13 +29697,13 @@
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR54" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS54" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -29716,52 +29716,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>57.26</v>
       </c>
       <c r="F55" t="n">
-        <v>52.65</v>
+        <v>55.6</v>
       </c>
       <c r="G55" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>56.34</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>27.79</v>
+        <v>8.25</v>
       </c>
       <c r="K55" t="n">
-        <v>74.59</v>
+        <v>63.66</v>
       </c>
       <c r="L55" t="n">
-        <v>54.36</v>
+        <v>20.13</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -29772,7 +29772,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -29795,13 +29795,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -29816,17 +29816,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -29836,83 +29836,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>1902465664</v>
+        <v>201903325184</v>
       </c>
       <c r="AN55" t="n">
-        <v>12.25</v>
+        <v>32.3</v>
       </c>
       <c r="AO55" t="n">
-        <v>2.01</v>
+        <v>10.71</v>
       </c>
       <c r="AP55" t="n">
-        <v>9.34</v>
+        <v>4.17</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5.97</v>
+        <v>2.33</v>
       </c>
       <c r="AR55" t="n">
-        <v>16.39</v>
+        <v>33.16</v>
       </c>
       <c r="AS55" t="n">
-        <v>10.11</v>
+        <v>24.33</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.91</v>
+        <v>15.58</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="AX55" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="AY55" t="n">
-        <v>22.85000038146973</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ55" t="n">
-        <v>9.75</v>
+        <v>8.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
       <c r="BB55" t="n">
-        <v>20.28</v>
+        <v>19.74</v>
       </c>
       <c r="BC55" t="n">
-        <v>21.84</v>
+        <v>12.27</v>
       </c>
       <c r="BD55" t="n">
-        <v>19.34</v>
+        <v>15.69</v>
       </c>
       <c r="BE55" t="n">
-        <v>17.21</v>
+        <v>14.11</v>
       </c>
       <c r="BF55" t="n">
-        <v>19.34</v>
+        <v>14.86</v>
       </c>
       <c r="BG55" t="n">
-        <v>17.41</v>
+        <v>13.37</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-23.81</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-24.68</v>
+        <v>-70.67</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -29928,13 +29928,13 @@
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>24.03000068664551</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR55" t="n">
-        <v>-4.910529635696426</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.35737468710545</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -29986,13 +29986,13 @@
         <v>75.51000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>32.07</v>
+        <v>32.89</v>
       </c>
       <c r="K56" t="n">
         <v>22.81</v>
       </c>
       <c r="L56" t="n">
-        <v>83.89</v>
+        <v>81.88</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -30079,7 +30079,7 @@
         <v>8.33</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.3</v>
+        <v>10.06</v>
       </c>
       <c r="AR56" t="n">
         <v>23.72</v>
@@ -30098,43 +30098,43 @@
         <v>1.43</v>
       </c>
       <c r="AX56" t="n">
-        <v>4.89</v>
+        <v>3.85</v>
       </c>
       <c r="AY56" t="n">
         <v>44.79999923706055</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.96</v>
+        <v>32.21</v>
       </c>
       <c r="BA56" t="n">
-        <v>38.61</v>
+        <v>39.54</v>
       </c>
       <c r="BB56" t="n">
-        <v>41.84</v>
+        <v>43.84</v>
       </c>
       <c r="BC56" t="n">
         <v>48.76</v>
       </c>
       <c r="BD56" t="n">
-        <v>60.65</v>
+        <v>61.97</v>
       </c>
       <c r="BE56" t="n">
-        <v>44.56</v>
+        <v>45.26</v>
       </c>
       <c r="BF56" t="n">
-        <v>41.84</v>
+        <v>43.84</v>
       </c>
       <c r="BG56" t="n">
-        <v>37.66</v>
+        <v>39.46</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-15.94</v>
+        <v>-11.93</v>
       </c>
       <c r="BJ56" t="n">
-        <v>-0.53</v>
+        <v>1.03</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>-2.880272661462469</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.6228216922185</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -32230,7 +32230,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82514761546183</v>
+        <v>-25.82515452490343</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -34753,7 +34753,7 @@
         <v>-5.436300030681352</v>
       </c>
       <c r="BS76" t="n">
-        <v>-24.54173046087656</v>
+        <v>-24.54173690556859</v>
       </c>
       <c r="BT76" t="b">
         <v>0</v>
@@ -35019,10 +35019,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>50.32</v>
+        <v>50.28</v>
       </c>
       <c r="F78" t="n">
-        <v>53.32</v>
+        <v>53.27</v>
       </c>
       <c r="G78" t="n">
         <v>33.33333333333334</v>
@@ -35032,7 +35032,7 @@
         <v>45.05</v>
       </c>
       <c r="J78" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="K78" t="n">
         <v>46.98</v>
@@ -35246,10 +35246,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>50.05</v>
+        <v>50.11</v>
       </c>
       <c r="F79" t="n">
-        <v>50.06</v>
+        <v>50.13</v>
       </c>
       <c r="G79" t="n">
         <v>50</v>
@@ -35265,7 +35265,7 @@
         <v>42.11</v>
       </c>
       <c r="L79" t="n">
-        <v>83.22</v>
+        <v>83.89</v>
       </c>
       <c r="M79" t="n">
         <v>78</v>
@@ -36338,7 +36338,7 @@
         <v>-6.267030362183146</v>
       </c>
       <c r="BS83" t="n">
-        <v>-52.97215903119552</v>
+        <v>-52.97216216294481</v>
       </c>
       <c r="BT83" t="b">
         <v>0</v>
@@ -36792,7 +36792,7 @@
         <v>-2.285089473123469</v>
       </c>
       <c r="BS85" t="n">
-        <v>-17.850910086273</v>
+        <v>-17.85090042584634</v>
       </c>
       <c r="BT85" t="b">
         <v>0</v>
@@ -40617,7 +40617,7 @@
         <v>-2.411569511092404</v>
       </c>
       <c r="BS102" t="n">
-        <v>-25.49988843235376</v>
+        <v>-25.49989727527226</v>
       </c>
       <c r="BT102" t="b">
         <v>0</v>
@@ -44579,7 +44579,7 @@
         <v>-9.242822111007619</v>
       </c>
       <c r="BS120" t="n">
-        <v>-19.44251454422593</v>
+        <v>-19.44250955845246</v>
       </c>
       <c r="BT120" t="b">
         <v>0</v>
@@ -45656,7 +45656,7 @@
         <v>-7.69230636971937</v>
       </c>
       <c r="BS125" t="n">
-        <v>-54.87060095233498</v>
+        <v>-54.87060603413229</v>
       </c>
       <c r="BT125" t="b">
         <v>0</v>
@@ -46370,10 +46370,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>34.62</v>
+        <v>34.58</v>
       </c>
       <c r="F129" t="n">
-        <v>34.85</v>
+        <v>34.8</v>
       </c>
       <c r="G129" t="n">
         <v>33.33333333333334</v>
@@ -46383,7 +46383,7 @@
         <v>49.38</v>
       </c>
       <c r="J129" t="n">
-        <v>27.51</v>
+        <v>27.3</v>
       </c>
       <c r="K129" t="n">
         <v>22.05</v>

--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1380,11 +1380,19 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation atrativo, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam muito acima dos pares do setor de consumo cíclico (8,4% e 11,4%, respectivamente), sugerindo uma eficiência superior na alocação de capital. Essa rentabilidade robusta convive com múltiplos de preço historicamente baixos, como o P/L de 4,8 e o P/VP de 1,68, indicando que o mercado pode estar subavaliando a capacidade de geração de valor da companhia. A saúde financeira da empresa é sólida, com um endividamento sobre o patrimônio de apenas 0,37 e uma folgada liquidez corrente de 2,96, o que garante que o expressivo dividend yield de 28,86% seja sustentável e coerente com a forte geração de lucro e a baixa alavancagem. No quesito expansão, o crescimento de receita nos últimos cinco anos registrou uma taxa anual composta de 11,2%, superando amplamente a estagnação do setor de 0,0%, o que reforça o perfil de crescimento e eficiência da empresa. O checklist fundamentalista chancela essa solidez ao aprovar 6 dos 7 critérios avaliados, falhando apenas na questão de vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 de Bazin até os otimistas R$ 71,67 de Lynch, mas convergindo para um preço-teto ajustado com margem de segurança de R$ 25,88, o que sinaliza um expressivo potencial de valorização de 84,3% frente ao preço atual de R$ 14,04. Em termos gráficos, o papel exibe uma tendência lateral no curto prazo, embora já configure um pivô de alta que pode indicar reversão positiva. Como balanço final, os prós residem na excepcional rentabilidade, no endividamento sob controle, no dividendo altamente generoso e no forte desconto patrimonial, enquanto os contras limitam-se ao comportamento recente dos insiders e à volatilidade intrínseca ao setor de consumo cíclico.</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ4" t="n">
@@ -1400,14 +1408,14 @@
         <v>1</v>
       </c>
       <c r="BU4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1547,7 @@
         <v>6.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="AR5" t="n">
         <v>27.12</v>
@@ -1564,10 +1572,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.31</v>
+        <v>11.11</v>
       </c>
       <c r="BB5" t="n">
         <v>37.13</v>
@@ -1576,25 +1584,25 @@
         <v>25.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>64.2</v>
+        <v>63.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>24.67</v>
+        <v>34.41</v>
       </c>
       <c r="BF5" t="n">
-        <v>25.58</v>
+        <v>31.36</v>
       </c>
       <c r="BG5" t="n">
-        <v>23.02</v>
+        <v>28.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>113.35</v>
+        <v>161.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>128.67</v>
+        <v>218.93</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -1615,7 +1623,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ5" t="n">
@@ -1625,7 +1633,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76549937388828</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -1638,7 +1646,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2009,7 @@
         <v>15.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>23.93</v>
@@ -2026,10 +2034,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.38</v>
+        <v>16.37</v>
       </c>
       <c r="BA7" t="n">
-        <v>30.38</v>
+        <v>30.36</v>
       </c>
       <c r="BB7" t="n">
         <v>64.44</v>
@@ -2038,7 +2046,7 @@
         <v>47.07</v>
       </c>
       <c r="BD7" t="n">
-        <v>106.29</v>
+        <v>106.3</v>
       </c>
       <c r="BE7" t="n">
         <v>62.04</v>
@@ -2056,7 +2064,7 @@
         <v>101.51</v>
       </c>
       <c r="BJ7" t="n">
-        <v>149.17</v>
+        <v>149.16</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2318,7 +2326,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15145724236707</v>
+        <v>-43.15146077270641</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -2500,7 +2508,7 @@
         <v>18.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>35.33</v>
+        <v>35.32</v>
       </c>
       <c r="BE9" t="n">
         <v>22.8</v>
@@ -2539,7 +2547,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ9" t="n">
@@ -2562,7 +2570,7 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-1.3%))</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2970,7 @@
         <v>19.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>59.96</v>
+        <v>59.97</v>
       </c>
       <c r="BE11" t="n">
         <v>37.67</v>
@@ -2971,7 +2979,7 @@
         <v>40.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>36.74</v>
+        <v>36.73</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -3232,7 +3240,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ12" t="n">
@@ -3255,7 +3263,7 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -3463,10 +3471,10 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="BR13" t="n">
-        <v>-5.87286813587281</v>
+        <v>-5.063880008850452</v>
       </c>
       <c r="BS13" t="n">
         <v>-16.85980497860918</v>
@@ -3482,7 +3490,7 @@
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
         </is>
       </c>
     </row>
@@ -3694,10 +3702,10 @@
         </is>
       </c>
       <c r="BQ14" t="n">
-        <v>7.699999809265137</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="BR14" t="n">
-        <v>-8.831166820555026</v>
+        <v>-11.47540816028945</v>
       </c>
       <c r="BS14" t="n">
         <v>-59.61021964227024</v>
@@ -3713,7 +3721,7 @@
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
         </is>
       </c>
     </row>
@@ -3925,10 +3933,10 @@
         </is>
       </c>
       <c r="BQ15" t="n">
-        <v>8.220000267028809</v>
+        <v>8.420000076293945</v>
       </c>
       <c r="BR15" t="n">
-        <v>-5.596107338245182</v>
+        <v>-7.83847792674377</v>
       </c>
       <c r="BS15" t="n">
         <v>-28.37008112858783</v>
@@ -3944,7 +3952,7 @@
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4338,7 @@
         <v>45.68999862670898</v>
       </c>
       <c r="AZ17" t="n">
-        <v>121.41</v>
+        <v>121.42</v>
       </c>
       <c r="BA17" t="n">
         <v>176.78</v>
@@ -4383,10 +4391,10 @@
         </is>
       </c>
       <c r="BQ17" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="BR17" t="n">
-        <v>-6.831162777889876</v>
+        <v>-6.180702441633368</v>
       </c>
       <c r="BS17" t="n">
         <v>-16.33828883951265</v>
@@ -4402,7 +4410,7 @@
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4618,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ18" t="n">
@@ -4633,7 +4641,7 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -5076,10 +5084,10 @@
         </is>
       </c>
       <c r="BQ20" t="n">
-        <v>22.84000015258789</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="BR20" t="n">
-        <v>-5.29772759955166</v>
+        <v>-7.366172131063841</v>
       </c>
       <c r="BS20" t="n">
         <v>-39.73503176095192</v>
@@ -5095,7 +5103,7 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5517,7 @@
         <v>75.16</v>
       </c>
       <c r="BJ22" t="n">
-        <v>83.06</v>
+        <v>83.05</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -5722,7 +5730,7 @@
         <v>53.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>56.83</v>
+        <v>56.82</v>
       </c>
       <c r="BE23" t="n">
         <v>46.72</v>
@@ -5996,10 +6004,10 @@
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>29.06999969482422</v>
+        <v>29.21999931335449</v>
       </c>
       <c r="BR24" t="n">
-        <v>-4.403160621720859</v>
+        <v>-4.89390291386349</v>
       </c>
       <c r="BS24" t="n">
         <v>-21.22606264717445</v>
@@ -6015,7 +6023,7 @@
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -6162,10 +6170,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.2</v>
+        <v>19.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="BB25" t="n">
         <v>75.48999999999999</v>
@@ -6174,13 +6182,13 @@
         <v>56.56</v>
       </c>
       <c r="BD25" t="n">
-        <v>99.09999999999999</v>
+        <v>99.09</v>
       </c>
       <c r="BE25" t="n">
         <v>43.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="BG25" t="n">
         <v>32.06</v>
@@ -6192,7 +6200,7 @@
         <v>-36.41</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-13.85</v>
+        <v>-13.84</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -6679,10 +6687,10 @@
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>12.03999996185303</v>
+        <v>12.38000011444092</v>
       </c>
       <c r="BR27" t="n">
-        <v>-3.820598335584846</v>
+        <v>-6.46203702212963</v>
       </c>
       <c r="BS27" t="n">
         <v>-32.90019903655219</v>
@@ -6698,7 +6706,7 @@
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7351,7 @@
         <v>203.13</v>
       </c>
       <c r="BJ30" t="n">
-        <v>243.32</v>
+        <v>243.31</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -7744,7 +7752,7 @@
         <v>11.54</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
       <c r="AR32" t="n">
         <v>13.99</v>
@@ -7777,7 +7785,7 @@
         <v>48.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>73.98999999999999</v>
+        <v>73.98</v>
       </c>
       <c r="BE32" t="n">
         <v>14.24</v>
@@ -7795,7 +7803,7 @@
         <v>-6.81</v>
       </c>
       <c r="BJ32" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -8503,10 +8511,10 @@
         </is>
       </c>
       <c r="BQ35" t="n">
-        <v>9.779999732971191</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="BR35" t="n">
-        <v>-6.134963641897039</v>
+        <v>-8.016024787124209</v>
       </c>
       <c r="BS35" t="n">
         <v>-49.20898677565268</v>
@@ -8522,7 +8530,7 @@
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8748,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62750247023346</v>
+        <v>-19.62749400029969</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -8922,7 +8930,7 @@
         <v>24</v>
       </c>
       <c r="BD37" t="n">
-        <v>24.54</v>
+        <v>24.53</v>
       </c>
       <c r="BE37" t="n">
         <v>19.7</v>
@@ -8937,7 +8945,7 @@
         <v>4</v>
       </c>
       <c r="BI37" t="n">
-        <v>89.45999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="BJ37" t="n">
         <v>92.54000000000001</v>
@@ -8969,7 +8977,7 @@
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ37" t="n">
@@ -9137,10 +9145,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="AZ38" t="n">
-        <v>35.2</v>
+        <v>35.21</v>
       </c>
       <c r="BA38" t="n">
-        <v>51.25</v>
+        <v>51.26</v>
       </c>
       <c r="BB38" t="n">
         <v>49.22</v>
@@ -9150,7 +9158,7 @@
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="n">
-        <v>45.22</v>
+        <v>45.23</v>
       </c>
       <c r="BF38" t="n">
         <v>49.22</v>
@@ -9165,7 +9173,7 @@
         <v>15.41</v>
       </c>
       <c r="BJ38" t="n">
-        <v>17.83</v>
+        <v>17.85</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -9421,10 +9429,10 @@
         </is>
       </c>
       <c r="BQ39" t="n">
-        <v>12.01000022888184</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="BR39" t="n">
-        <v>-10.40799314053285</v>
+        <v>-10.77943735905924</v>
       </c>
       <c r="BS39" t="n">
         <v>-35.14712749925304</v>
@@ -9440,7 +9448,7 @@
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
         </is>
       </c>
     </row>
@@ -9652,13 +9660,13 @@
         </is>
       </c>
       <c r="BQ40" t="n">
-        <v>9.189999580383301</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="BR40" t="n">
-        <v>-5.005441340050498</v>
+        <v>-9.81405715898066</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -9671,7 +9679,7 @@
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9856,7 @@
         <v>-9.66</v>
       </c>
       <c r="BJ41" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
@@ -10548,14 +10556,14 @@
       <c r="BO44" t="inlineStr"/>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ44" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="BR44" t="n">
-        <v>-3.703704326653801</v>
+        <v>-3.191486393612009</v>
       </c>
       <c r="BS44" t="n">
         <v>-18.11425560893279</v>
@@ -10571,7 +10579,7 @@
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10978,7 @@
         <v>28.38</v>
       </c>
       <c r="BG46" t="n">
-        <v>25.55</v>
+        <v>25.54</v>
       </c>
       <c r="BH46" t="n">
         <v>3</v>
@@ -11010,7 +11018,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.7182148933239</v>
+        <v>-19.71820629342497</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -11235,10 +11243,10 @@
         </is>
       </c>
       <c r="BQ47" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="BR47" t="n">
-        <v>-7.444173079810589</v>
+        <v>-6.28140700507328</v>
       </c>
       <c r="BS47" t="n">
         <v>-50.82278080073881</v>
@@ -11254,7 +11262,7 @@
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11314,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -11458,16 +11466,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN48" t="inlineStr">
-        <is>
-          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica operacional robusta no setor de Real Estate, evidenciada por um ROE de 37,6% e um ROIC de 14,4%, ambos posicionados significativamente acima da média dos seus pares setoriais (20,1% e 11,9%, respectivamente), o que sugere uma eficiência superior na alocação de capital e na geração de valor para o acionista. Essa elevada qualidade operacional convive com múltiplos de preço mistos, uma vez que o indicador P/L de 7,12 vezes sinaliza um papel descontado frente à sua capacidade de geração de lucros, enquanto o P/VP de 2,68 revela um prêmio patrimonial exigido pelo mercado. No âmbito financeiro, a rentabilidade de dois dígitos é sustentada por uma estrutura de capital equilibrada, com uma relação de dívida sobre o patrimônio de 0,79 e uma liquidez corrente confortável de 1,96, indicando que o endividamento não compromete a solvência de curto prazo. Por outro lado, o dividend yield de 2,45% mostra-se modesto e reflete uma postura de distribuição contida, coerente com a necessidade de retenção de lucros para fazer frente aos desafios de crescimento e à estrutura de capital, apesar de o pagamento ser sustentável frente à lucratividade atual. O crescimento histórico, contudo, acende um sinal de alerta, visto que a taxa composta anual de receitas nos últimos cinco anos recuou 11,5%, situando-se bem abaixo da média setorial de 3,0% de expansão, o que justifica o atendimento de apenas 4 dos 7 critérios do checklist fundamentalista. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 9,27 pelo método de Bazin e R$ 17,19 pelo modelo de Gordon, até os otimistas R$ 62,58 pelo fluxo de caixa descontado e R$ 89,07 pela fórmula de Lynch. Essa divergência resulta em uma média de R$ 51,34 e uma mediana de R$ 49,55, estabelecendo um preço-teto ajustado com margem de segurança de R$ 44,60 que, comparado à cotação atual de R$ 33,63, projeta um potencial de valorização de 32,6%. Em suma, o investimento em TEND3 coloca em balanço, como pontos positivos, a excelente rentabilidade sobre o capital e o atraente desconto pelo múltiplo de lucros, contrapostos à contração histórica de receita e a um retorno em dividendos ainda tímido para a categoria.</t>
-        </is>
-      </c>
-      <c r="BO48" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="BN48" t="inlineStr"/>
+      <c r="BO48" t="inlineStr"/>
       <c r="BP48" t="inlineStr">
         <is>
           <t>Em Baixa</t>
@@ -11486,14 +11486,14 @@
         <v>1</v>
       </c>
       <c r="BU48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
         </is>
       </c>
     </row>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.56999969482422</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="BR49" t="n">
-        <v>-4.849432091972849</v>
+        <v>-5.44111793018941</v>
       </c>
       <c r="BS49" t="n">
         <v>-20.03706285314828</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188534882304</v>
+        <v>188206235648</v>
       </c>
       <c r="AN51" t="n">
         <v>7.4</v>
@@ -12159,7 +12159,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49890292399284</v>
+        <v>-18.49888798862691</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -13081,7 +13081,7 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ55" t="n">
@@ -13091,7 +13091,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-11.35737468710545</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -13316,10 +13316,10 @@
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>46.86999893188477</v>
+        <v>47.18999862670898</v>
       </c>
       <c r="BR56" t="n">
-        <v>-4.416470539784967</v>
+        <v>-5.064631191355295</v>
       </c>
       <c r="BS56" t="n">
         <v>-15.45867760032158</v>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
         </is>
       </c>
     </row>
@@ -13774,10 +13774,10 @@
         </is>
       </c>
       <c r="BQ58" t="n">
-        <v>29.29000091552734</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="BR58" t="n">
-        <v>-8.193927793995414</v>
+        <v>-8.225255666094988</v>
       </c>
       <c r="BS58" t="n">
         <v>-23.86318934952274</v>
@@ -13922,7 +13922,7 @@
         <v>0.63</v>
       </c>
       <c r="AP59" t="n">
-        <v>27.54</v>
+        <v>26.6</v>
       </c>
       <c r="AQ59" t="n">
         <v>13.22</v>
@@ -13977,7 +13977,7 @@
         <v>5</v>
       </c>
       <c r="BI59" t="n">
-        <v>32.68</v>
+        <v>32.67</v>
       </c>
       <c r="BJ59" t="n">
         <v>72.89</v>
@@ -14005,10 +14005,10 @@
         </is>
       </c>
       <c r="BQ59" t="n">
-        <v>26.3799991607666</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="BR59" t="n">
-        <v>-4.283545097481212</v>
+        <v>-4.896419112682715</v>
       </c>
       <c r="BS59" t="n">
         <v>-12.02090826211568</v>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -14171,10 +14171,10 @@
         <v>40.75</v>
       </c>
       <c r="AZ60" t="n">
-        <v>20.82</v>
+        <v>20.81</v>
       </c>
       <c r="BA60" t="n">
-        <v>38.63</v>
+        <v>38.61</v>
       </c>
       <c r="BB60" t="n">
         <v>56.01</v>
@@ -14183,25 +14183,25 @@
         <v>42.36</v>
       </c>
       <c r="BD60" t="n">
-        <v>59.69</v>
+        <v>59.71</v>
       </c>
       <c r="BE60" t="n">
-        <v>38.49</v>
+        <v>38.48</v>
       </c>
       <c r="BF60" t="n">
-        <v>38.63</v>
+        <v>38.61</v>
       </c>
       <c r="BG60" t="n">
-        <v>34.76</v>
+        <v>34.75</v>
       </c>
       <c r="BH60" t="n">
         <v>3</v>
       </c>
       <c r="BI60" t="n">
-        <v>-14.69</v>
+        <v>-14.72</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-5.55</v>
+        <v>-5.57</v>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32272997776186</v>
+        <v>-16.35820625379285</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -14457,10 +14457,10 @@
         </is>
       </c>
       <c r="BQ61" t="n">
-        <v>17.81902885437012</v>
+        <v>18.00869941711426</v>
       </c>
       <c r="BR61" t="n">
-        <v>-1.846504015123462</v>
+        <v>-2.880272661462469</v>
       </c>
       <c r="BS61" t="n">
         <v>-39.62282580198882</v>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
         <v>15.41</v>
       </c>
       <c r="BA63" t="n">
-        <v>23.76</v>
+        <v>23.75</v>
       </c>
       <c r="BB63" t="n">
         <v>44.61</v>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="BQ63" t="n">
-        <v>37.13999938964844</v>
+        <v>37.22999954223633</v>
       </c>
       <c r="BR63" t="n">
-        <v>-8.346791936095499</v>
+        <v>-8.568355267074413</v>
       </c>
       <c r="BS63" t="n">
         <v>-30.1313627614148</v>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15320,7 @@
         <v>0.3</v>
       </c>
       <c r="AX65" t="n">
-        <v>38.87</v>
+        <v>38.78</v>
       </c>
       <c r="AY65" t="n">
         <v>30.57999992370605</v>
@@ -15387,7 +15387,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82514761546183</v>
+        <v>-25.82515452490343</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -15612,10 +15612,10 @@
         </is>
       </c>
       <c r="BQ66" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="BR66" t="n">
-        <v>-3.739609749070061</v>
+        <v>-3.248254665304118</v>
       </c>
       <c r="BS66" t="n">
         <v>-30.08510558619815</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="AM68" t="n">
-        <v>49176797184</v>
+        <v>49177673728</v>
       </c>
       <c r="AN68" t="n">
         <v>22.15</v>
@@ -16046,7 +16046,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.18</v>
+        <v>-19.17</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -16443,7 +16443,7 @@
         <v>2.81</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.48</v>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
         <v>29.72999954223633</v>
       </c>
       <c r="AZ73" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
       <c r="BA73" t="n">
         <v>23.92</v>
@@ -17223,10 +17223,10 @@
         </is>
       </c>
       <c r="BQ73" t="n">
-        <v>30.34000015258789</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="BR73" t="n">
-        <v>-2.010549134092643</v>
+        <v>-2.20394764704388</v>
       </c>
       <c r="BS73" t="n">
         <v>-23.41079410625997</v>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -18223,11 +18223,19 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation atrativo, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam muito acima dos pares do setor de consumo cíclico (8,4% e 11,4%, respectivamente), sugerindo uma eficiência superior na alocação de capital. Essa rentabilidade robusta convive com múltiplos de preço historicamente baixos, como o P/L de 4,8 e o P/VP de 1,68, indicando que o mercado pode estar subavaliando a capacidade de geração de valor da companhia. A saúde financeira da empresa é sólida, com um endividamento sobre o patrimônio de apenas 0,37 e uma folgada liquidez corrente de 2,96, o que garante que o expressivo dividend yield de 28,86% seja sustentável e coerente com a forte geração de lucro e a baixa alavancagem. No quesito expansão, o crescimento de receita nos últimos cinco anos registrou uma taxa anual composta de 11,2%, superando amplamente a estagnação do setor de 0,0%, o que reforça o perfil de crescimento e eficiência da empresa. O checklist fundamentalista chancela essa solidez ao aprovar 6 dos 7 critérios avaliados, falhando apenas na questão de vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 de Bazin até os otimistas R$ 71,67 de Lynch, mas convergindo para um preço-teto ajustado com margem de segurança de R$ 25,88, o que sinaliza um expressivo potencial de valorização de 84,3% frente ao preço atual de R$ 14,04. Em termos gráficos, o papel exibe uma tendência lateral no curto prazo, embora já configure um pivô de alta que pode indicar reversão positiva. Como balanço final, os prós residem na excepcional rentabilidade, no endividamento sob controle, no dividendo altamente generoso e no forte desconto patrimonial, enquanto os contras limitam-se ao comportamento recente dos insiders e à volatilidade intrínseca ao setor de consumo cíclico.</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ4" t="n">
@@ -18243,14 +18251,14 @@
         <v>1</v>
       </c>
       <c r="BU4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18390,7 @@
         <v>6.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="AR5" t="n">
         <v>27.12</v>
@@ -18407,10 +18415,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.31</v>
+        <v>11.11</v>
       </c>
       <c r="BB5" t="n">
         <v>37.13</v>
@@ -18419,25 +18427,25 @@
         <v>25.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>64.2</v>
+        <v>63.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>24.67</v>
+        <v>34.41</v>
       </c>
       <c r="BF5" t="n">
-        <v>25.58</v>
+        <v>31.36</v>
       </c>
       <c r="BG5" t="n">
-        <v>23.02</v>
+        <v>28.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>113.35</v>
+        <v>161.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>128.67</v>
+        <v>218.93</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -18458,7 +18466,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ5" t="n">
@@ -18468,7 +18476,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76549937388828</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -18481,7 +18489,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18852,7 @@
         <v>15.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>23.93</v>
@@ -18869,10 +18877,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.38</v>
+        <v>16.37</v>
       </c>
       <c r="BA7" t="n">
-        <v>30.38</v>
+        <v>30.36</v>
       </c>
       <c r="BB7" t="n">
         <v>64.44</v>
@@ -18881,7 +18889,7 @@
         <v>47.07</v>
       </c>
       <c r="BD7" t="n">
-        <v>106.29</v>
+        <v>106.3</v>
       </c>
       <c r="BE7" t="n">
         <v>62.04</v>
@@ -18899,7 +18907,7 @@
         <v>101.51</v>
       </c>
       <c r="BJ7" t="n">
-        <v>149.17</v>
+        <v>149.16</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -19161,7 +19169,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15145724236707</v>
+        <v>-43.15146077270641</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -19343,7 +19351,7 @@
         <v>18.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>35.33</v>
+        <v>35.32</v>
       </c>
       <c r="BE9" t="n">
         <v>22.8</v>
@@ -19382,7 +19390,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ9" t="n">
@@ -19405,7 +19413,7 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-1.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-1.3%))</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19813,7 @@
         <v>19.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>59.96</v>
+        <v>59.97</v>
       </c>
       <c r="BE11" t="n">
         <v>37.67</v>
@@ -19814,7 +19822,7 @@
         <v>40.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>36.74</v>
+        <v>36.73</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -20075,7 +20083,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ12" t="n">
@@ -20098,7 +20106,7 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -20306,10 +20314,10 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>43.41999816894531</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="BR13" t="n">
-        <v>-5.87286813587281</v>
+        <v>-5.063880008850452</v>
       </c>
       <c r="BS13" t="n">
         <v>-16.85980497860918</v>
@@ -20325,7 +20333,7 @@
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
         </is>
       </c>
     </row>
@@ -20537,10 +20545,10 @@
         </is>
       </c>
       <c r="BQ14" t="n">
-        <v>7.699999809265137</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="BR14" t="n">
-        <v>-8.831166820555026</v>
+        <v>-11.47540816028945</v>
       </c>
       <c r="BS14" t="n">
         <v>-59.61021964227024</v>
@@ -20556,7 +20564,7 @@
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
         </is>
       </c>
     </row>
@@ -20768,10 +20776,10 @@
         </is>
       </c>
       <c r="BQ15" t="n">
-        <v>8.220000267028809</v>
+        <v>8.420000076293945</v>
       </c>
       <c r="BR15" t="n">
-        <v>-5.596107338245182</v>
+        <v>-7.83847792674377</v>
       </c>
       <c r="BS15" t="n">
         <v>-28.37008112858783</v>
@@ -20787,7 +20795,7 @@
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
         </is>
       </c>
     </row>
@@ -21173,7 +21181,7 @@
         <v>45.68999862670898</v>
       </c>
       <c r="AZ17" t="n">
-        <v>121.41</v>
+        <v>121.42</v>
       </c>
       <c r="BA17" t="n">
         <v>176.78</v>
@@ -21226,10 +21234,10 @@
         </is>
       </c>
       <c r="BQ17" t="n">
-        <v>49.04000091552734</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="BR17" t="n">
-        <v>-6.831162777889876</v>
+        <v>-6.180702441633368</v>
       </c>
       <c r="BS17" t="n">
         <v>-16.33828883951265</v>
@@ -21245,7 +21253,7 @@
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21461,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ18" t="n">
@@ -21476,7 +21484,7 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -21919,10 +21927,10 @@
         </is>
       </c>
       <c r="BQ20" t="n">
-        <v>22.84000015258789</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="BR20" t="n">
-        <v>-5.29772759955166</v>
+        <v>-7.366172131063841</v>
       </c>
       <c r="BS20" t="n">
         <v>-39.73503176095192</v>
@@ -21938,7 +21946,7 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -22352,7 +22360,7 @@
         <v>75.16</v>
       </c>
       <c r="BJ22" t="n">
-        <v>83.06</v>
+        <v>83.05</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -22565,7 +22573,7 @@
         <v>53.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>56.83</v>
+        <v>56.82</v>
       </c>
       <c r="BE23" t="n">
         <v>46.72</v>
@@ -22839,10 +22847,10 @@
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>29.06999969482422</v>
+        <v>29.21999931335449</v>
       </c>
       <c r="BR24" t="n">
-        <v>-4.403160621720859</v>
+        <v>-4.89390291386349</v>
       </c>
       <c r="BS24" t="n">
         <v>-21.22606264717445</v>
@@ -22858,7 +22866,7 @@
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -23005,10 +23013,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.2</v>
+        <v>19.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="BB25" t="n">
         <v>75.48999999999999</v>
@@ -23017,13 +23025,13 @@
         <v>56.56</v>
       </c>
       <c r="BD25" t="n">
-        <v>99.09999999999999</v>
+        <v>99.09</v>
       </c>
       <c r="BE25" t="n">
         <v>43.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="BG25" t="n">
         <v>32.06</v>
@@ -23035,7 +23043,7 @@
         <v>-36.41</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-13.85</v>
+        <v>-13.84</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -23522,10 +23530,10 @@
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>12.03999996185303</v>
+        <v>12.38000011444092</v>
       </c>
       <c r="BR27" t="n">
-        <v>-3.820598335584846</v>
+        <v>-6.46203702212963</v>
       </c>
       <c r="BS27" t="n">
         <v>-32.90019903655219</v>
@@ -23541,7 +23549,7 @@
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
         </is>
       </c>
     </row>
@@ -24186,7 +24194,7 @@
         <v>203.13</v>
       </c>
       <c r="BJ30" t="n">
-        <v>243.32</v>
+        <v>243.31</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -24587,7 +24595,7 @@
         <v>11.54</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
       <c r="AR32" t="n">
         <v>13.99</v>
@@ -24620,7 +24628,7 @@
         <v>48.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>73.98999999999999</v>
+        <v>73.98</v>
       </c>
       <c r="BE32" t="n">
         <v>14.24</v>
@@ -24638,7 +24646,7 @@
         <v>-6.81</v>
       </c>
       <c r="BJ32" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -25346,10 +25354,10 @@
         </is>
       </c>
       <c r="BQ35" t="n">
-        <v>9.779999732971191</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="BR35" t="n">
-        <v>-6.134963641897039</v>
+        <v>-8.016024787124209</v>
       </c>
       <c r="BS35" t="n">
         <v>-49.20898677565268</v>
@@ -25365,7 +25373,7 @@
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
         </is>
       </c>
     </row>
@@ -25583,7 +25591,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62750247023346</v>
+        <v>-19.62749400029969</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -25765,7 +25773,7 @@
         <v>24</v>
       </c>
       <c r="BD37" t="n">
-        <v>24.54</v>
+        <v>24.53</v>
       </c>
       <c r="BE37" t="n">
         <v>19.7</v>
@@ -25780,7 +25788,7 @@
         <v>4</v>
       </c>
       <c r="BI37" t="n">
-        <v>89.45999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="BJ37" t="n">
         <v>92.54000000000001</v>
@@ -25812,7 +25820,7 @@
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ37" t="n">
@@ -25980,10 +25988,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="AZ38" t="n">
-        <v>35.2</v>
+        <v>35.21</v>
       </c>
       <c r="BA38" t="n">
-        <v>51.25</v>
+        <v>51.26</v>
       </c>
       <c r="BB38" t="n">
         <v>49.22</v>
@@ -25993,7 +26001,7 @@
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="n">
-        <v>45.22</v>
+        <v>45.23</v>
       </c>
       <c r="BF38" t="n">
         <v>49.22</v>
@@ -26008,7 +26016,7 @@
         <v>15.41</v>
       </c>
       <c r="BJ38" t="n">
-        <v>17.83</v>
+        <v>17.85</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -26264,10 +26272,10 @@
         </is>
       </c>
       <c r="BQ39" t="n">
-        <v>12.01000022888184</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="BR39" t="n">
-        <v>-10.40799314053285</v>
+        <v>-10.77943735905924</v>
       </c>
       <c r="BS39" t="n">
         <v>-35.14712749925304</v>
@@ -26283,7 +26291,7 @@
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
         </is>
       </c>
     </row>
@@ -26495,13 +26503,13 @@
         </is>
       </c>
       <c r="BQ40" t="n">
-        <v>9.189999580383301</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="BR40" t="n">
-        <v>-5.005441340050498</v>
+        <v>-9.81405715898066</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -26514,7 +26522,7 @@
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26699,7 @@
         <v>-9.66</v>
       </c>
       <c r="BJ41" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
@@ -27391,14 +27399,14 @@
       <c r="BO44" t="inlineStr"/>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ44" t="n">
-        <v>11.34000015258789</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="BR44" t="n">
-        <v>-3.703704326653801</v>
+        <v>-3.191486393612009</v>
       </c>
       <c r="BS44" t="n">
         <v>-18.11425560893279</v>
@@ -27414,7 +27422,7 @@
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -27813,7 +27821,7 @@
         <v>28.38</v>
       </c>
       <c r="BG46" t="n">
-        <v>25.55</v>
+        <v>25.54</v>
       </c>
       <c r="BH46" t="n">
         <v>3</v>
@@ -27853,7 +27861,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.7182148933239</v>
+        <v>-19.71820629342497</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -28078,10 +28086,10 @@
         </is>
       </c>
       <c r="BQ47" t="n">
-        <v>4.03000020980835</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="BR47" t="n">
-        <v>-7.444173079810589</v>
+        <v>-6.28140700507328</v>
       </c>
       <c r="BS47" t="n">
         <v>-50.82278080073881</v>
@@ -28097,7 +28105,7 @@
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
         </is>
       </c>
     </row>
@@ -28149,7 +28157,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -28301,16 +28309,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN48" t="inlineStr">
-        <is>
-          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica operacional robusta no setor de Real Estate, evidenciada por um ROE de 37,6% e um ROIC de 14,4%, ambos posicionados significativamente acima da média dos seus pares setoriais (20,1% e 11,9%, respectivamente), o que sugere uma eficiência superior na alocação de capital e na geração de valor para o acionista. Essa elevada qualidade operacional convive com múltiplos de preço mistos, uma vez que o indicador P/L de 7,12 vezes sinaliza um papel descontado frente à sua capacidade de geração de lucros, enquanto o P/VP de 2,68 revela um prêmio patrimonial exigido pelo mercado. No âmbito financeiro, a rentabilidade de dois dígitos é sustentada por uma estrutura de capital equilibrada, com uma relação de dívida sobre o patrimônio de 0,79 e uma liquidez corrente confortável de 1,96, indicando que o endividamento não compromete a solvência de curto prazo. Por outro lado, o dividend yield de 2,45% mostra-se modesto e reflete uma postura de distribuição contida, coerente com a necessidade de retenção de lucros para fazer frente aos desafios de crescimento e à estrutura de capital, apesar de o pagamento ser sustentável frente à lucratividade atual. O crescimento histórico, contudo, acende um sinal de alerta, visto que a taxa composta anual de receitas nos últimos cinco anos recuou 11,5%, situando-se bem abaixo da média setorial de 3,0% de expansão, o que justifica o atendimento de apenas 4 dos 7 critérios do checklist fundamentalista. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 9,27 pelo método de Bazin e R$ 17,19 pelo modelo de Gordon, até os otimistas R$ 62,58 pelo fluxo de caixa descontado e R$ 89,07 pela fórmula de Lynch. Essa divergência resulta em uma média de R$ 51,34 e uma mediana de R$ 49,55, estabelecendo um preço-teto ajustado com margem de segurança de R$ 44,60 que, comparado à cotação atual de R$ 33,63, projeta um potencial de valorização de 32,6%. Em suma, o investimento em TEND3 coloca em balanço, como pontos positivos, a excelente rentabilidade sobre o capital e o atraente desconto pelo múltiplo de lucros, contrapostos à contração histórica de receita e a um retorno em dividendos ainda tímido para a categoria.</t>
-        </is>
-      </c>
-      <c r="BO48" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="BN48" t="inlineStr"/>
+      <c r="BO48" t="inlineStr"/>
       <c r="BP48" t="inlineStr">
         <is>
           <t>Em Baixa</t>
@@ -28329,14 +28329,14 @@
         <v>1</v>
       </c>
       <c r="BU48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
         </is>
       </c>
     </row>
@@ -28544,10 +28544,10 @@
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.56999969482422</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="BR49" t="n">
-        <v>-4.849432091972849</v>
+        <v>-5.44111793018941</v>
       </c>
       <c r="BS49" t="n">
         <v>-20.03706285314828</v>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
         </is>
       </c>
     </row>
@@ -28908,7 +28908,7 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188534882304</v>
+        <v>188206235648</v>
       </c>
       <c r="AN51" t="n">
         <v>7.4</v>
@@ -29002,7 +29002,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49890292399284</v>
+        <v>-18.49888798862691</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -29924,7 +29924,7 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ55" t="n">
@@ -29934,7 +29934,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-11.35737468710545</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -30159,10 +30159,10 @@
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>46.86999893188477</v>
+        <v>47.18999862670898</v>
       </c>
       <c r="BR56" t="n">
-        <v>-4.416470539784967</v>
+        <v>-5.064631191355295</v>
       </c>
       <c r="BS56" t="n">
         <v>-15.45867760032158</v>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
         </is>
       </c>
     </row>
@@ -30617,10 +30617,10 @@
         </is>
       </c>
       <c r="BQ58" t="n">
-        <v>29.29000091552734</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="BR58" t="n">
-        <v>-8.193927793995414</v>
+        <v>-8.225255666094988</v>
       </c>
       <c r="BS58" t="n">
         <v>-23.86318934952274</v>
@@ -30765,7 +30765,7 @@
         <v>0.63</v>
       </c>
       <c r="AP59" t="n">
-        <v>27.54</v>
+        <v>26.6</v>
       </c>
       <c r="AQ59" t="n">
         <v>13.22</v>
@@ -30820,7 +30820,7 @@
         <v>5</v>
       </c>
       <c r="BI59" t="n">
-        <v>32.68</v>
+        <v>32.67</v>
       </c>
       <c r="BJ59" t="n">
         <v>72.89</v>
@@ -30848,10 +30848,10 @@
         </is>
       </c>
       <c r="BQ59" t="n">
-        <v>26.3799991607666</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="BR59" t="n">
-        <v>-4.283545097481212</v>
+        <v>-4.896419112682715</v>
       </c>
       <c r="BS59" t="n">
         <v>-12.02090826211568</v>
@@ -30867,7 +30867,7 @@
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -31014,10 +31014,10 @@
         <v>40.75</v>
       </c>
       <c r="AZ60" t="n">
-        <v>20.82</v>
+        <v>20.81</v>
       </c>
       <c r="BA60" t="n">
-        <v>38.63</v>
+        <v>38.61</v>
       </c>
       <c r="BB60" t="n">
         <v>56.01</v>
@@ -31026,25 +31026,25 @@
         <v>42.36</v>
       </c>
       <c r="BD60" t="n">
-        <v>59.69</v>
+        <v>59.71</v>
       </c>
       <c r="BE60" t="n">
-        <v>38.49</v>
+        <v>38.48</v>
       </c>
       <c r="BF60" t="n">
-        <v>38.63</v>
+        <v>38.61</v>
       </c>
       <c r="BG60" t="n">
-        <v>34.76</v>
+        <v>34.75</v>
       </c>
       <c r="BH60" t="n">
         <v>3</v>
       </c>
       <c r="BI60" t="n">
-        <v>-14.69</v>
+        <v>-14.72</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-5.55</v>
+        <v>-5.57</v>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32272997776186</v>
+        <v>-16.35820625379285</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -31300,10 +31300,10 @@
         </is>
       </c>
       <c r="BQ61" t="n">
-        <v>17.81902885437012</v>
+        <v>18.00869941711426</v>
       </c>
       <c r="BR61" t="n">
-        <v>-1.846504015123462</v>
+        <v>-2.880272661462469</v>
       </c>
       <c r="BS61" t="n">
         <v>-39.62282580198882</v>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
         </is>
       </c>
     </row>
@@ -31710,7 +31710,7 @@
         <v>15.41</v>
       </c>
       <c r="BA63" t="n">
-        <v>23.76</v>
+        <v>23.75</v>
       </c>
       <c r="BB63" t="n">
         <v>44.61</v>
@@ -31762,10 +31762,10 @@
         </is>
       </c>
       <c r="BQ63" t="n">
-        <v>37.13999938964844</v>
+        <v>37.22999954223633</v>
       </c>
       <c r="BR63" t="n">
-        <v>-8.346791936095499</v>
+        <v>-8.568355267074413</v>
       </c>
       <c r="BS63" t="n">
         <v>-30.1313627614148</v>
@@ -31781,7 +31781,7 @@
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
         </is>
       </c>
     </row>
@@ -32163,7 +32163,7 @@
         <v>0.3</v>
       </c>
       <c r="AX65" t="n">
-        <v>38.87</v>
+        <v>38.78</v>
       </c>
       <c r="AY65" t="n">
         <v>30.57999992370605</v>
@@ -32230,7 +32230,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82514761546183</v>
+        <v>-25.82515452490343</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -32455,10 +32455,10 @@
         </is>
       </c>
       <c r="BQ66" t="n">
-        <v>43.31999969482422</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="BR66" t="n">
-        <v>-3.739609749070061</v>
+        <v>-3.248254665304118</v>
       </c>
       <c r="BS66" t="n">
         <v>-30.08510558619815</v>
@@ -32474,7 +32474,7 @@
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -32825,7 +32825,7 @@
         <v>1</v>
       </c>
       <c r="AM68" t="n">
-        <v>49176797184</v>
+        <v>49177673728</v>
       </c>
       <c r="AN68" t="n">
         <v>22.15</v>
@@ -32889,7 +32889,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.18</v>
+        <v>-19.17</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -33286,7 +33286,7 @@
         <v>2.81</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.48</v>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
         <v>29.72999954223633</v>
       </c>
       <c r="AZ73" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
       <c r="BA73" t="n">
         <v>23.92</v>
@@ -34066,10 +34066,10 @@
         </is>
       </c>
       <c r="BQ73" t="n">
-        <v>30.34000015258789</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="BR73" t="n">
-        <v>-2.010549134092643</v>
+        <v>-2.20394764704388</v>
       </c>
       <c r="BS73" t="n">
         <v>-23.41079410625997</v>
@@ -34085,7 +34085,7 @@
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
         <v>1</v>
       </c>
       <c r="AM74" t="n">
-        <v>14560741376</v>
+        <v>14564848640</v>
       </c>
       <c r="AN74" t="n">
         <v>18.33</v>
@@ -34520,10 +34520,10 @@
         </is>
       </c>
       <c r="BQ75" t="n">
-        <v>9.710000038146973</v>
+        <v>10.03999996185303</v>
       </c>
       <c r="BR75" t="n">
-        <v>-5.561276619274647</v>
+        <v>-8.665337538492491</v>
       </c>
       <c r="BS75" t="n">
         <v>-40.00475990261403</v>
@@ -34539,7 +34539,7 @@
       </c>
       <c r="BW75" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
@@ -34935,7 +34935,7 @@
         <v>20.23</v>
       </c>
       <c r="BD77" t="n">
-        <v>24.6</v>
+        <v>24.61</v>
       </c>
       <c r="BE77" t="n">
         <v>19.97</v>
@@ -34974,10 +34974,10 @@
         </is>
       </c>
       <c r="BQ77" t="n">
-        <v>35.77999877929688</v>
+        <v>35.86999893188477</v>
       </c>
       <c r="BR77" t="n">
-        <v>-5.198436763021363</v>
+        <v>-5.436300030681352</v>
       </c>
       <c r="BS77" t="n">
         <v>-24.54173690556859</v>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="BW77" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
         </is>
       </c>
     </row>
@@ -35173,7 +35173,7 @@
         <v>4</v>
       </c>
       <c r="BI78" t="n">
-        <v>-36.06</v>
+        <v>-36.05</v>
       </c>
       <c r="BJ78" t="n">
         <v>-23.04</v>
@@ -35563,7 +35563,7 @@
         <v>1</v>
       </c>
       <c r="AM80" t="n">
-        <v>45855367168</v>
+        <v>45849899008</v>
       </c>
       <c r="AN80" t="n">
         <v>12.96</v>
@@ -35651,10 +35651,10 @@
         </is>
       </c>
       <c r="BQ80" t="n">
-        <v>60.84999847412109</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="BR80" t="n">
-        <v>-5.587506649860686</v>
+        <v>-5.104063603995368</v>
       </c>
       <c r="BS80" t="n">
         <v>-21.27980526122939</v>
@@ -35670,7 +35670,7 @@
       </c>
       <c r="BW80" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
         </is>
       </c>
     </row>
@@ -36101,7 +36101,7 @@
       <c r="BO82" t="inlineStr"/>
       <c r="BP82" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ82" t="n">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="BW82" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.2%))</t>
         </is>
       </c>
     </row>
@@ -36332,10 +36332,10 @@
         </is>
       </c>
       <c r="BQ83" t="n">
-        <v>3.660000085830688</v>
+        <v>3.670000076293945</v>
       </c>
       <c r="BR83" t="n">
-        <v>-6.010929602486536</v>
+        <v>-6.267030362183146</v>
       </c>
       <c r="BS83" t="n">
         <v>-52.97216216294481</v>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="BW83" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
         </is>
       </c>
     </row>
@@ -36956,7 +36956,7 @@
         <v>26.94000053405762</v>
       </c>
       <c r="AZ86" t="n">
-        <v>11.72</v>
+        <v>11.71</v>
       </c>
       <c r="BA86" t="n">
         <v>12.57</v>
@@ -36974,7 +36974,7 @@
         <v>12.83</v>
       </c>
       <c r="BF86" t="n">
-        <v>12.71</v>
+        <v>12.7</v>
       </c>
       <c r="BG86" t="n">
         <v>11.43</v>
@@ -36986,7 +36986,7 @@
         <v>-57.56</v>
       </c>
       <c r="BJ86" t="n">
-        <v>-52.36</v>
+        <v>-52.37</v>
       </c>
       <c r="BK86" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
       <c r="BO88" t="inlineStr"/>
       <c r="BP88" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ88" t="n">
@@ -37476,7 +37476,7 @@
       </c>
       <c r="BW88" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
         </is>
       </c>
     </row>
@@ -38286,7 +38286,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92" t="n">
-        <v>5.84</v>
+        <v>4.45</v>
       </c>
       <c r="AQ92" t="n">
         <v>8.890000000000001</v>
@@ -38574,7 +38574,7 @@
       <c r="BO93" t="inlineStr"/>
       <c r="BP93" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ93" t="n">
@@ -38597,7 +38597,7 @@
       </c>
       <c r="BW93" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
         </is>
       </c>
     </row>
@@ -39437,7 +39437,7 @@
         <v>18.29</v>
       </c>
       <c r="BB97" t="n">
-        <v>22.09</v>
+        <v>22.08</v>
       </c>
       <c r="BC97" t="n">
         <v>31.97</v>
@@ -39452,7 +39452,7 @@
         <v>21.17</v>
       </c>
       <c r="BG97" t="n">
-        <v>19.06</v>
+        <v>19.05</v>
       </c>
       <c r="BH97" t="n">
         <v>5</v>
@@ -39699,10 +39699,10 @@
         </is>
       </c>
       <c r="BQ98" t="n">
-        <v>21.35000038146973</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="BR98" t="n">
-        <v>-6.042158746971138</v>
+        <v>-5.688768057264582</v>
       </c>
       <c r="BS98" t="n">
         <v>-27.1670659463897</v>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.0%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.7%))</t>
         </is>
       </c>
     </row>
@@ -39926,14 +39926,14 @@
       </c>
       <c r="BP99" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ99" t="n">
-        <v>21.17000007629395</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="BR99" t="n">
-        <v>-3.542749160590919</v>
+        <v>-3.13092907875151</v>
       </c>
       <c r="BS99" t="n">
         <v>-18.72166979656401</v>
@@ -40739,7 +40739,7 @@
       <c r="AV103" t="inlineStr"/>
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="n">
-        <v>20.27</v>
+        <v>20.25</v>
       </c>
       <c r="AY103" t="n">
         <v>13</v>
@@ -40796,10 +40796,10 @@
         </is>
       </c>
       <c r="BQ103" t="n">
-        <v>14.72000026702881</v>
+        <v>14.73999977111816</v>
       </c>
       <c r="BR103" t="n">
-        <v>-11.68478421078172</v>
+        <v>-11.80461192765792</v>
       </c>
       <c r="BS103" t="n">
         <v>-39.52341924380666</v>
@@ -40815,7 +40815,7 @@
       </c>
       <c r="BW103" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.8%))</t>
         </is>
       </c>
     </row>
@@ -41162,7 +41162,7 @@
         <v>1</v>
       </c>
       <c r="AM105" t="n">
-        <v>3136304384</v>
+        <v>3112041728</v>
       </c>
       <c r="AN105" t="n">
         <v>8.56</v>
@@ -42142,10 +42142,10 @@
         </is>
       </c>
       <c r="BQ109" t="n">
-        <v>3.799999952316284</v>
+        <v>3.880000114440918</v>
       </c>
       <c r="BR109" t="n">
-        <v>-7.105262745120189</v>
+        <v>-9.020621977522293</v>
       </c>
       <c r="BS109" t="n">
         <v>-26.45833685166292</v>
@@ -42161,7 +42161,7 @@
       </c>
       <c r="BW109" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.0%))</t>
         </is>
       </c>
     </row>
@@ -42991,7 +42991,7 @@
         <v>-92.73999999999999</v>
       </c>
       <c r="BJ113" t="n">
-        <v>-91.94</v>
+        <v>-91.93000000000001</v>
       </c>
       <c r="BK113" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
       <c r="BO114" t="inlineStr"/>
       <c r="BP114" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ114" t="n">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="BW114" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -43435,7 +43435,7 @@
         <v>-75.77</v>
       </c>
       <c r="BJ115" t="n">
-        <v>-73.06999999999999</v>
+        <v>-73.08</v>
       </c>
       <c r="BK115" t="inlineStr">
         <is>
@@ -43456,10 +43456,10 @@
         </is>
       </c>
       <c r="BQ115" t="n">
-        <v>3.920000076293945</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="BR115" t="n">
-        <v>-1.020407170268323</v>
+        <v>-1.522841165181832</v>
       </c>
       <c r="BS115" t="n">
         <v>-19.23016222053626</v>
@@ -43475,7 +43475,7 @@
       </c>
       <c r="BW115" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.5%))</t>
         </is>
       </c>
     </row>
@@ -43698,7 +43698,7 @@
       </c>
       <c r="BW116" t="inlineStr">
         <is>
-          <t>Rompimento (vol x2.5, +0.6% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x2.4, +0.6% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -44297,10 +44297,10 @@
         <v>52.13999938964844</v>
       </c>
       <c r="AZ119" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="BA119" t="n">
-        <v>15.86</v>
+        <v>15.87</v>
       </c>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr"/>
@@ -44318,7 +44318,7 @@
         <v>2</v>
       </c>
       <c r="BI119" t="n">
-        <v>-76.91</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="BJ119" t="n">
         <v>-74.34</v>
@@ -44342,10 +44342,10 @@
         </is>
       </c>
       <c r="BQ119" t="n">
-        <v>57</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="BR119" t="n">
-        <v>-8.526316860265904</v>
+        <v>-9.242822111007619</v>
       </c>
       <c r="BS119" t="n">
         <v>-19.44250955845246</v>
@@ -44361,7 +44361,7 @@
       </c>
       <c r="BW119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-9.2%))</t>
         </is>
       </c>
     </row>
@@ -44413,7 +44413,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -44521,7 +44521,7 @@
         <v>1.21</v>
       </c>
       <c r="BA120" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BB120" t="n">
         <v>1.3</v>
@@ -44545,10 +44545,10 @@
         <v>4</v>
       </c>
       <c r="BI120" t="n">
-        <v>-68.20999999999999</v>
+        <v>-68.22</v>
       </c>
       <c r="BJ120" t="n">
-        <v>-64.28</v>
+        <v>-64.29000000000001</v>
       </c>
       <c r="BK120" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
       <c r="BN120" t="inlineStr"/>
       <c r="BO120" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="BP120" t="inlineStr">
@@ -44573,10 +44573,10 @@
         </is>
       </c>
       <c r="BQ120" t="n">
-        <v>3.559999942779541</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="BR120" t="n">
-        <v>-0.2808986130333757</v>
+        <v>0.2824856093507577</v>
       </c>
       <c r="BS120" t="n">
         <v>-43.65079611367132</v>
@@ -44592,7 +44592,7 @@
       </c>
       <c r="BW120" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Rompimento (vol x1.7, +0.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="BQ121" t="n">
-        <v>4.739999771118164</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="BR121" t="n">
-        <v>-5.907167647502643</v>
+        <v>-7.85124178638169</v>
       </c>
       <c r="BS121" t="n">
         <v>-57.64482287514247</v>
@@ -44813,7 +44813,7 @@
       </c>
       <c r="BW121" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
         </is>
       </c>
     </row>
@@ -44993,7 +44993,7 @@
       <c r="BO122" t="inlineStr"/>
       <c r="BP122" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ122" t="n">
@@ -45016,7 +45016,7 @@
       </c>
       <c r="BW122" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (+9.0%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (+9.0%))</t>
         </is>
       </c>
     </row>
@@ -45498,7 +45498,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -45597,7 +45597,7 @@
         <v>1.37</v>
       </c>
       <c r="AX125" t="n">
-        <v>41.01</v>
+        <v>41</v>
       </c>
       <c r="AY125" t="n">
         <v>1.610000014305115</v>
@@ -45630,7 +45630,7 @@
         <v>3</v>
       </c>
       <c r="BI125" t="n">
-        <v>-91.98</v>
+        <v>-91.98999999999999</v>
       </c>
       <c r="BJ125" t="n">
         <v>-91.68000000000001</v>
@@ -45647,21 +45647,17 @@
       </c>
       <c r="BM125" t="inlineStr"/>
       <c r="BN125" t="inlineStr"/>
-      <c r="BO125" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="BO125" t="inlineStr"/>
       <c r="BP125" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ125" t="n">
-        <v>1.600000023841858</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="BR125" t="n">
-        <v>0.6249993946403354</v>
+        <v>-1.829266564112753</v>
       </c>
       <c r="BS125" t="n">
         <v>-42.61824784986528</v>
@@ -45670,14 +45666,14 @@
         <v>0</v>
       </c>
       <c r="BU125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV125" t="b">
         <v>0</v>
       </c>
       <c r="BW125" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.6, +0.6% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -45881,10 +45877,10 @@
         </is>
       </c>
       <c r="BQ126" t="n">
-        <v>2.029999971389771</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="BR126" t="n">
-        <v>-5.418719992877974</v>
+        <v>-7.69230636971937</v>
       </c>
       <c r="BS126" t="n">
         <v>-54.87060603413229</v>
@@ -45900,7 +45896,7 @@
       </c>
       <c r="BW126" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-7.7%))</t>
         </is>
       </c>
     </row>
@@ -46108,10 +46104,10 @@
         </is>
       </c>
       <c r="BQ127" t="n">
-        <v>20.6200008392334</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="BR127" t="n">
-        <v>-11.97866692615981</v>
+        <v>-12.86606008157372</v>
       </c>
       <c r="BS127" t="n">
         <v>-31.2598598602242</v>
@@ -46127,7 +46123,7 @@
       </c>
       <c r="BW127" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-12.9%))</t>
         </is>
       </c>
     </row>
@@ -46331,14 +46327,14 @@
       <c r="BO128" t="inlineStr"/>
       <c r="BP128" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ128" t="n">
-        <v>14.4399995803833</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="BR128" t="n">
-        <v>-5.886422801217616</v>
+        <v>-4.831929924971612</v>
       </c>
       <c r="BS128" t="n">
         <v>-21.57503186501287</v>
@@ -46354,7 +46350,7 @@
       </c>
       <c r="BW128" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.9%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -46532,7 +46528,7 @@
         <v>2</v>
       </c>
       <c r="BI129" t="n">
-        <v>-79.5</v>
+        <v>-79.51000000000001</v>
       </c>
       <c r="BJ129" t="n">
         <v>-77.23</v>
@@ -46702,7 +46698,7 @@
         <v>2.22</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ130" t="n">
         <v>6.04</v>
@@ -47137,7 +47133,7 @@
         <v>1</v>
       </c>
       <c r="AM132" t="n">
-        <v>2167328768</v>
+        <v>2160784384</v>
       </c>
       <c r="AN132" t="n">
         <v>35.2</v>
@@ -47874,10 +47870,10 @@
         </is>
       </c>
       <c r="BQ135" t="n">
-        <v>1.049999952316284</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="BR135" t="n">
-        <v>-31.42856558974881</v>
+        <v>-32.71028099856381</v>
       </c>
       <c r="BS135" t="n">
         <v>-86.86131339225869</v>
@@ -47893,7 +47889,7 @@
       </c>
       <c r="BW135" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-31.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-32.7%))</t>
         </is>
       </c>
     </row>
@@ -48101,10 +48097,10 @@
         </is>
       </c>
       <c r="BQ136" t="n">
-        <v>8.609999656677246</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="BR136" t="n">
-        <v>-7.549357078384833</v>
+        <v>-9.954752253972533</v>
       </c>
       <c r="BS136" t="n">
         <v>-47.939829574844</v>
@@ -48120,7 +48116,7 @@
       </c>
       <c r="BW136" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.0%))</t>
         </is>
       </c>
     </row>
@@ -48328,10 +48324,10 @@
         </is>
       </c>
       <c r="BQ137" t="n">
-        <v>39.5</v>
+        <v>39.84999847412109</v>
       </c>
       <c r="BR137" t="n">
-        <v>-5.620256254944622</v>
+        <v>-6.449183922787849</v>
       </c>
       <c r="BS137" t="n">
         <v>-19.51640970441861</v>
@@ -48347,7 +48343,7 @@
       </c>
       <c r="BW137" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -48467,7 +48463,7 @@
         <v>1</v>
       </c>
       <c r="AM138" t="n">
-        <v>50082459648</v>
+        <v>49977982976</v>
       </c>
       <c r="AN138" t="n">
         <v>39.13</v>
@@ -48907,7 +48903,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AR140" t="n">
         <v>0.79</v>
@@ -48926,7 +48922,7 @@
         <v>0.76</v>
       </c>
       <c r="AX140" t="n">
-        <v>473.91</v>
+        <v>471.81</v>
       </c>
       <c r="AY140" t="n">
         <v>4.400000095367432</v>
@@ -48959,10 +48955,10 @@
         <v>3</v>
       </c>
       <c r="BI140" t="n">
-        <v>-84.95</v>
+        <v>-84.95999999999999</v>
       </c>
       <c r="BJ140" t="n">
-        <v>-82.67</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="BK140" t="inlineStr">
         <is>
@@ -49204,10 +49200,10 @@
         </is>
       </c>
       <c r="BQ141" t="n">
-        <v>11.59000015258789</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="BR141" t="n">
-        <v>-6.729937210544623</v>
+        <v>-8.078229513397417</v>
       </c>
       <c r="BS141" t="n">
         <v>-26.26193361437886</v>
@@ -49223,7 +49219,7 @@
       </c>
       <c r="BW141" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.1%))</t>
         </is>
       </c>
     </row>
@@ -49881,10 +49877,10 @@
         </is>
       </c>
       <c r="BQ144" t="n">
-        <v>19.73999977111816</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="BR144" t="n">
-        <v>-6.788248065475977</v>
+        <v>-6.598990325192277</v>
       </c>
       <c r="BS144" t="n">
         <v>-16.70439342946463</v>
@@ -49900,7 +49896,7 @@
       </c>
       <c r="BW144" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.6%))</t>
         </is>
       </c>
     </row>
@@ -50292,7 +50288,7 @@
         <v>34.54</v>
       </c>
       <c r="BD146" t="n">
-        <v>17.64</v>
+        <v>17.63</v>
       </c>
       <c r="BE146" t="n">
         <v>22.82</v>
@@ -50479,7 +50475,7 @@
         <v>2.37</v>
       </c>
       <c r="AP147" t="n">
-        <v>7.83</v>
+        <v>6.45</v>
       </c>
       <c r="AQ147" t="n">
         <v>7.09</v>
@@ -50777,10 +50773,10 @@
         </is>
       </c>
       <c r="BQ148" t="n">
-        <v>73.62000274658203</v>
+        <v>74.15000152587891</v>
       </c>
       <c r="BR148" t="n">
-        <v>-7.837549656609899</v>
+        <v>-8.496295242231467</v>
       </c>
       <c r="BS148" t="n">
         <v>-20.08245317470424</v>
@@ -50796,7 +50792,7 @@
       </c>
       <c r="BW148" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
         </is>
       </c>
     </row>
@@ -50982,10 +50978,10 @@
         </is>
       </c>
       <c r="BQ149" t="n">
-        <v>0.4099999964237213</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="BR149" t="n">
-        <v>-43.90243751743164</v>
+        <v>-47.7272714957718</v>
       </c>
       <c r="BS149" t="n">
         <v>-98.71937630347001</v>
@@ -51001,7 +50997,7 @@
       </c>
       <c r="BW149" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-43.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-47.7%))</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1380,19 +1380,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation atrativo, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam muito acima dos pares do setor de consumo cíclico (8,4% e 11,4%, respectivamente), sugerindo uma eficiência superior na alocação de capital. Essa rentabilidade robusta convive com múltiplos de preço historicamente baixos, como o P/L de 4,8 e o P/VP de 1,68, indicando que o mercado pode estar subavaliando a capacidade de geração de valor da companhia. A saúde financeira da empresa é sólida, com um endividamento sobre o patrimônio de apenas 0,37 e uma folgada liquidez corrente de 2,96, o que garante que o expressivo dividend yield de 28,86% seja sustentável e coerente com a forte geração de lucro e a baixa alavancagem. No quesito expansão, o crescimento de receita nos últimos cinco anos registrou uma taxa anual composta de 11,2%, superando amplamente a estagnação do setor de 0,0%, o que reforça o perfil de crescimento e eficiência da empresa. O checklist fundamentalista chancela essa solidez ao aprovar 6 dos 7 critérios avaliados, falhando apenas na questão de vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 de Bazin até os otimistas R$ 71,67 de Lynch, mas convergindo para um preço-teto ajustado com margem de segurança de R$ 25,88, o que sinaliza um expressivo potencial de valorização de 84,3% frente ao preço atual de R$ 14,04. Em termos gráficos, o papel exibe uma tendência lateral no curto prazo, embora já configure um pivô de alta que pode indicar reversão positiva. Como balanço final, os prós residem na excepcional rentabilidade, no endividamento sob controle, no dividendo altamente generoso e no forte desconto patrimonial, enquanto os contras limitam-se ao comportamento recente dos insiders e à volatilidade intrínseca ao setor de consumo cíclico.</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ4" t="n">
@@ -1408,14 +1400,14 @@
         <v>1</v>
       </c>
       <c r="BU4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1539,7 @@
         <v>6.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.77</v>
+        <v>7.91</v>
       </c>
       <c r="AR5" t="n">
         <v>27.12</v>
@@ -1572,10 +1564,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.99</v>
+        <v>6.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.11</v>
+        <v>11.31</v>
       </c>
       <c r="BB5" t="n">
         <v>37.13</v>
@@ -1584,25 +1576,25 @@
         <v>25.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>63.83</v>
+        <v>64.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>34.41</v>
+        <v>24.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>31.36</v>
+        <v>25.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>28.22</v>
+        <v>23.02</v>
       </c>
       <c r="BH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI5" t="n">
-        <v>161.54</v>
+        <v>113.35</v>
       </c>
       <c r="BJ5" t="n">
-        <v>218.93</v>
+        <v>128.67</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -1623,7 +1615,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ5" t="n">
@@ -1633,7 +1625,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76549937388828</v>
+        <v>-23.76550987166468</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -1646,7 +1638,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2001,7 @@
         <v>15.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>23.93</v>
@@ -2034,10 +2026,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.37</v>
+        <v>16.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>30.36</v>
+        <v>30.38</v>
       </c>
       <c r="BB7" t="n">
         <v>64.44</v>
@@ -2046,7 +2038,7 @@
         <v>47.07</v>
       </c>
       <c r="BD7" t="n">
-        <v>106.3</v>
+        <v>106.29</v>
       </c>
       <c r="BE7" t="n">
         <v>62.04</v>
@@ -2064,7 +2056,7 @@
         <v>101.51</v>
       </c>
       <c r="BJ7" t="n">
-        <v>149.16</v>
+        <v>149.17</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2326,7 +2318,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -2508,7 +2500,7 @@
         <v>18.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>35.32</v>
+        <v>35.33</v>
       </c>
       <c r="BE9" t="n">
         <v>22.8</v>
@@ -2547,7 +2539,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ9" t="n">
@@ -2570,7 +2562,7 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.3%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.3%))</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2962,7 @@
         <v>19.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>59.97</v>
+        <v>59.96</v>
       </c>
       <c r="BE11" t="n">
         <v>37.67</v>
@@ -2979,7 +2971,7 @@
         <v>40.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>36.73</v>
+        <v>36.74</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -3240,7 +3232,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ12" t="n">
@@ -3263,7 +3255,7 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -3471,10 +3463,10 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="BR13" t="n">
-        <v>-5.063880008850452</v>
+        <v>-5.87286813587281</v>
       </c>
       <c r="BS13" t="n">
         <v>-16.85980497860918</v>
@@ -3490,7 +3482,7 @@
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -3702,10 +3694,10 @@
         </is>
       </c>
       <c r="BQ14" t="n">
-        <v>7.929999828338623</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="BR14" t="n">
-        <v>-11.47540816028945</v>
+        <v>-8.831166820555026</v>
       </c>
       <c r="BS14" t="n">
         <v>-59.61021964227024</v>
@@ -3721,7 +3713,7 @@
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
         </is>
       </c>
     </row>
@@ -3933,10 +3925,10 @@
         </is>
       </c>
       <c r="BQ15" t="n">
-        <v>8.420000076293945</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="BR15" t="n">
-        <v>-7.83847792674377</v>
+        <v>-5.596107338245182</v>
       </c>
       <c r="BS15" t="n">
         <v>-28.37008112858783</v>
@@ -3952,7 +3944,7 @@
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4330,7 @@
         <v>45.68999862670898</v>
       </c>
       <c r="AZ17" t="n">
-        <v>121.42</v>
+        <v>121.41</v>
       </c>
       <c r="BA17" t="n">
         <v>176.78</v>
@@ -4391,10 +4383,10 @@
         </is>
       </c>
       <c r="BQ17" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="BR17" t="n">
-        <v>-6.180702441633368</v>
+        <v>-6.831162777889876</v>
       </c>
       <c r="BS17" t="n">
         <v>-16.33828883951265</v>
@@ -4410,7 +4402,7 @@
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4610,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ18" t="n">
@@ -4641,7 +4633,7 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -5084,10 +5076,10 @@
         </is>
       </c>
       <c r="BQ20" t="n">
-        <v>23.35000038146973</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="BR20" t="n">
-        <v>-7.366172131063841</v>
+        <v>-5.29772759955166</v>
       </c>
       <c r="BS20" t="n">
         <v>-39.73503176095192</v>
@@ -5103,7 +5095,7 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5509,7 @@
         <v>75.16</v>
       </c>
       <c r="BJ22" t="n">
-        <v>83.05</v>
+        <v>83.06</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -5730,7 +5722,7 @@
         <v>53.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>56.82</v>
+        <v>56.83</v>
       </c>
       <c r="BE23" t="n">
         <v>46.72</v>
@@ -6004,10 +5996,10 @@
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>29.21999931335449</v>
+        <v>29.06999969482422</v>
       </c>
       <c r="BR24" t="n">
-        <v>-4.89390291386349</v>
+        <v>-4.403160621720859</v>
       </c>
       <c r="BS24" t="n">
         <v>-21.22606264717445</v>
@@ -6023,7 +6015,7 @@
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -6170,10 +6162,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.21</v>
+        <v>19.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="BB25" t="n">
         <v>75.48999999999999</v>
@@ -6182,13 +6174,13 @@
         <v>56.56</v>
       </c>
       <c r="BD25" t="n">
-        <v>99.09</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="BE25" t="n">
         <v>43.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="BG25" t="n">
         <v>32.06</v>
@@ -6200,7 +6192,7 @@
         <v>-36.41</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -6687,10 +6679,10 @@
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>12.38000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="BR27" t="n">
-        <v>-6.46203702212963</v>
+        <v>-3.820598335584846</v>
       </c>
       <c r="BS27" t="n">
         <v>-32.90019903655219</v>
@@ -6706,7 +6698,7 @@
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7343,7 @@
         <v>203.13</v>
       </c>
       <c r="BJ30" t="n">
-        <v>243.31</v>
+        <v>243.32</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -7752,7 +7744,7 @@
         <v>11.54</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.15</v>
+        <v>10.16</v>
       </c>
       <c r="AR32" t="n">
         <v>13.99</v>
@@ -7785,7 +7777,7 @@
         <v>48.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>73.98</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="BE32" t="n">
         <v>14.24</v>
@@ -7803,7 +7795,7 @@
         <v>-6.81</v>
       </c>
       <c r="BJ32" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -8286,7 +8278,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS34" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="BT34" t="b">
         <v>1</v>
@@ -8511,10 +8503,10 @@
         </is>
       </c>
       <c r="BQ35" t="n">
-        <v>9.979999542236328</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="BR35" t="n">
-        <v>-8.016024787124209</v>
+        <v>-6.134963641897039</v>
       </c>
       <c r="BS35" t="n">
         <v>-49.20898677565268</v>
@@ -8530,7 +8522,7 @@
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8740,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62749400029969</v>
+        <v>-19.62750247023346</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -8930,7 +8922,7 @@
         <v>24</v>
       </c>
       <c r="BD37" t="n">
-        <v>24.53</v>
+        <v>24.54</v>
       </c>
       <c r="BE37" t="n">
         <v>19.7</v>
@@ -8945,7 +8937,7 @@
         <v>4</v>
       </c>
       <c r="BI37" t="n">
-        <v>89.47</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="BJ37" t="n">
         <v>92.54000000000001</v>
@@ -8977,7 +8969,7 @@
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ37" t="n">
@@ -9145,10 +9137,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="AZ38" t="n">
-        <v>35.21</v>
+        <v>35.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>51.26</v>
+        <v>51.25</v>
       </c>
       <c r="BB38" t="n">
         <v>49.22</v>
@@ -9158,7 +9150,7 @@
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="n">
-        <v>45.23</v>
+        <v>45.22</v>
       </c>
       <c r="BF38" t="n">
         <v>49.22</v>
@@ -9173,7 +9165,7 @@
         <v>15.41</v>
       </c>
       <c r="BJ38" t="n">
-        <v>17.85</v>
+        <v>17.83</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -9429,10 +9421,10 @@
         </is>
       </c>
       <c r="BQ39" t="n">
-        <v>12.0600004196167</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="BR39" t="n">
-        <v>-10.77943735905924</v>
+        <v>-10.40799314053285</v>
       </c>
       <c r="BS39" t="n">
         <v>-35.14712749925304</v>
@@ -9448,7 +9440,7 @@
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
         </is>
       </c>
     </row>
@@ -9660,13 +9652,13 @@
         </is>
       </c>
       <c r="BQ40" t="n">
-        <v>9.680000305175781</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="BR40" t="n">
-        <v>-9.81405715898066</v>
+        <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866417350647</v>
+        <v>-38.87866842765243</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -9679,7 +9671,7 @@
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9848,7 @@
         <v>-9.66</v>
       </c>
       <c r="BJ41" t="n">
-        <v>-1.1</v>
+        <v>-1.11</v>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
@@ -10108,7 +10100,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.71342624530195</v>
+        <v>-16.7134172222279</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -10556,14 +10548,14 @@
       <c r="BO44" t="inlineStr"/>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ44" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="BR44" t="n">
-        <v>-3.191486393612009</v>
+        <v>-3.703704326653801</v>
       </c>
       <c r="BS44" t="n">
         <v>-18.11425560893279</v>
@@ -10579,7 +10571,7 @@
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10970,7 @@
         <v>28.38</v>
       </c>
       <c r="BG46" t="n">
-        <v>25.54</v>
+        <v>25.55</v>
       </c>
       <c r="BH46" t="n">
         <v>3</v>
@@ -11243,10 +11235,10 @@
         </is>
       </c>
       <c r="BQ47" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="BR47" t="n">
-        <v>-6.28140700507328</v>
+        <v>-7.444173079810589</v>
       </c>
       <c r="BS47" t="n">
         <v>-50.82278080073881</v>
@@ -11262,7 +11254,7 @@
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11306,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -11466,8 +11458,16 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN48" t="inlineStr"/>
-      <c r="BO48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr">
+        <is>
+          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica operacional robusta no setor de Real Estate, evidenciada por um ROE de 37,6% e um ROIC de 14,4%, ambos posicionados significativamente acima da média dos seus pares setoriais (20,1% e 11,9%, respectivamente), o que sugere uma eficiência superior na alocação de capital e na geração de valor para o acionista. Essa elevada qualidade operacional convive com múltiplos de preço mistos, uma vez que o indicador P/L de 7,12 vezes sinaliza um papel descontado frente à sua capacidade de geração de lucros, enquanto o P/VP de 2,68 revela um prêmio patrimonial exigido pelo mercado. No âmbito financeiro, a rentabilidade de dois dígitos é sustentada por uma estrutura de capital equilibrada, com uma relação de dívida sobre o patrimônio de 0,79 e uma liquidez corrente confortável de 1,96, indicando que o endividamento não compromete a solvência de curto prazo. Por outro lado, o dividend yield de 2,45% mostra-se modesto e reflete uma postura de distribuição contida, coerente com a necessidade de retenção de lucros para fazer frente aos desafios de crescimento e à estrutura de capital, apesar de o pagamento ser sustentável frente à lucratividade atual. O crescimento histórico, contudo, acende um sinal de alerta, visto que a taxa composta anual de receitas nos últimos cinco anos recuou 11,5%, situando-se bem abaixo da média setorial de 3,0% de expansão, o que justifica o atendimento de apenas 4 dos 7 critérios do checklist fundamentalista. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 9,27 pelo método de Bazin e R$ 17,19 pelo modelo de Gordon, até os otimistas R$ 62,58 pelo fluxo de caixa descontado e R$ 89,07 pela fórmula de Lynch. Essa divergência resulta em uma média de R$ 51,34 e uma mediana de R$ 49,55, estabelecendo um preço-teto ajustado com margem de segurança de R$ 44,60 que, comparado à cotação atual de R$ 33,63, projeta um potencial de valorização de 32,6%. Em suma, o investimento em TEND3 coloca em balanço, como pontos positivos, a excelente rentabilidade sobre o capital e o atraente desconto pelo múltiplo de lucros, contrapostos à contração histórica de receita e a um retorno em dividendos ainda tímido para a categoria.</t>
+        </is>
+      </c>
+      <c r="BO48" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BP48" t="inlineStr">
         <is>
           <t>Em Baixa</t>
@@ -11486,14 +11486,14 @@
         <v>1</v>
       </c>
       <c r="BU48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
+          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.72999954223633</v>
+        <v>25.56999969482422</v>
       </c>
       <c r="BR49" t="n">
-        <v>-5.44111793018941</v>
+        <v>-4.849432091972849</v>
       </c>
       <c r="BS49" t="n">
         <v>-20.03706285314828</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188206235648</v>
+        <v>188534882304</v>
       </c>
       <c r="AN51" t="n">
         <v>7.4</v>
@@ -12159,7 +12159,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49888798862691</v>
+        <v>-18.49889545631056</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -12398,7 +12398,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41669381125899</v>
+        <v>-19.41668752521939</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
@@ -13081,7 +13081,7 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ55" t="n">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -13316,10 +13316,10 @@
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>47.18999862670898</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="BR56" t="n">
-        <v>-5.064631191355295</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="BS56" t="n">
         <v>-15.45867760032158</v>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -13774,10 +13774,10 @@
         </is>
       </c>
       <c r="BQ58" t="n">
-        <v>29.29999923706055</v>
+        <v>29.29000091552734</v>
       </c>
       <c r="BR58" t="n">
-        <v>-8.225255666094988</v>
+        <v>-8.193927793995414</v>
       </c>
       <c r="BS58" t="n">
         <v>-23.86318934952274</v>
@@ -13977,7 +13977,7 @@
         <v>5</v>
       </c>
       <c r="BI59" t="n">
-        <v>32.67</v>
+        <v>32.68</v>
       </c>
       <c r="BJ59" t="n">
         <v>72.89</v>
@@ -14005,10 +14005,10 @@
         </is>
       </c>
       <c r="BQ59" t="n">
-        <v>26.54999923706055</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="BR59" t="n">
-        <v>-4.896419112682715</v>
+        <v>-4.283545097481212</v>
       </c>
       <c r="BS59" t="n">
         <v>-12.02090826211568</v>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -14171,10 +14171,10 @@
         <v>40.75</v>
       </c>
       <c r="AZ60" t="n">
-        <v>20.81</v>
+        <v>20.82</v>
       </c>
       <c r="BA60" t="n">
-        <v>38.61</v>
+        <v>38.63</v>
       </c>
       <c r="BB60" t="n">
         <v>56.01</v>
@@ -14183,25 +14183,25 @@
         <v>42.36</v>
       </c>
       <c r="BD60" t="n">
-        <v>59.71</v>
+        <v>59.69</v>
       </c>
       <c r="BE60" t="n">
-        <v>38.48</v>
+        <v>38.49</v>
       </c>
       <c r="BF60" t="n">
-        <v>38.61</v>
+        <v>38.63</v>
       </c>
       <c r="BG60" t="n">
-        <v>34.75</v>
+        <v>34.76</v>
       </c>
       <c r="BH60" t="n">
         <v>3</v>
       </c>
       <c r="BI60" t="n">
-        <v>-14.72</v>
+        <v>-14.69</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-5.57</v>
+        <v>-5.55</v>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.35820625379285</v>
+        <v>-16.32273657221009</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -14457,13 +14457,13 @@
         </is>
       </c>
       <c r="BQ61" t="n">
-        <v>18.00869941711426</v>
+        <v>17.81902885437012</v>
       </c>
       <c r="BR61" t="n">
-        <v>-2.880272661462469</v>
+        <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.6228216922185</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
         <v>15.41</v>
       </c>
       <c r="BA63" t="n">
-        <v>23.75</v>
+        <v>23.76</v>
       </c>
       <c r="BB63" t="n">
         <v>44.61</v>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="BQ63" t="n">
-        <v>37.22999954223633</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="BR63" t="n">
-        <v>-8.568355267074413</v>
+        <v>-8.346791936095499</v>
       </c>
       <c r="BS63" t="n">
         <v>-30.1313627614148</v>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15320,7 @@
         <v>0.3</v>
       </c>
       <c r="AX65" t="n">
-        <v>38.78</v>
+        <v>38.87</v>
       </c>
       <c r="AY65" t="n">
         <v>30.57999992370605</v>
@@ -15612,10 +15612,10 @@
         </is>
       </c>
       <c r="BQ66" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="BR66" t="n">
-        <v>-3.248254665304118</v>
+        <v>-3.739609749070061</v>
       </c>
       <c r="BS66" t="n">
         <v>-30.08510558619815</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="AM68" t="n">
-        <v>49177673728</v>
+        <v>49176797184</v>
       </c>
       <c r="AN68" t="n">
         <v>22.15</v>
@@ -16046,7 +16046,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
         <v>29.72999954223633</v>
       </c>
       <c r="AZ73" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="BA73" t="n">
         <v>23.92</v>
@@ -17223,10 +17223,10 @@
         </is>
       </c>
       <c r="BQ73" t="n">
-        <v>30.39999961853027</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="BR73" t="n">
-        <v>-2.20394764704388</v>
+        <v>-2.010549134092643</v>
       </c>
       <c r="BS73" t="n">
         <v>-23.41079410625997</v>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -18223,19 +18223,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation atrativo, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam muito acima dos pares do setor de consumo cíclico (8,4% e 11,4%, respectivamente), sugerindo uma eficiência superior na alocação de capital. Essa rentabilidade robusta convive com múltiplos de preço historicamente baixos, como o P/L de 4,8 e o P/VP de 1,68, indicando que o mercado pode estar subavaliando a capacidade de geração de valor da companhia. A saúde financeira da empresa é sólida, com um endividamento sobre o patrimônio de apenas 0,37 e uma folgada liquidez corrente de 2,96, o que garante que o expressivo dividend yield de 28,86% seja sustentável e coerente com a forte geração de lucro e a baixa alavancagem. No quesito expansão, o crescimento de receita nos últimos cinco anos registrou uma taxa anual composta de 11,2%, superando amplamente a estagnação do setor de 0,0%, o que reforça o perfil de crescimento e eficiência da empresa. O checklist fundamentalista chancela essa solidez ao aprovar 6 dos 7 critérios avaliados, falhando apenas na questão de vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 de Bazin até os otimistas R$ 71,67 de Lynch, mas convergindo para um preço-teto ajustado com margem de segurança de R$ 25,88, o que sinaliza um expressivo potencial de valorização de 84,3% frente ao preço atual de R$ 14,04. Em termos gráficos, o papel exibe uma tendência lateral no curto prazo, embora já configure um pivô de alta que pode indicar reversão positiva. Como balanço final, os prós residem na excepcional rentabilidade, no endividamento sob controle, no dividendo altamente generoso e no forte desconto patrimonial, enquanto os contras limitam-se ao comportamento recente dos insiders e à volatilidade intrínseca ao setor de consumo cíclico.</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ4" t="n">
@@ -18251,14 +18243,14 @@
         <v>1</v>
       </c>
       <c r="BU4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18382,7 @@
         <v>6.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.77</v>
+        <v>7.91</v>
       </c>
       <c r="AR5" t="n">
         <v>27.12</v>
@@ -18415,10 +18407,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.99</v>
+        <v>6.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.11</v>
+        <v>11.31</v>
       </c>
       <c r="BB5" t="n">
         <v>37.13</v>
@@ -18427,25 +18419,25 @@
         <v>25.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>63.83</v>
+        <v>64.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>34.41</v>
+        <v>24.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>31.36</v>
+        <v>25.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>28.22</v>
+        <v>23.02</v>
       </c>
       <c r="BH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI5" t="n">
-        <v>161.54</v>
+        <v>113.35</v>
       </c>
       <c r="BJ5" t="n">
-        <v>218.93</v>
+        <v>128.67</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -18466,7 +18458,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ5" t="n">
@@ -18476,7 +18468,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76549937388828</v>
+        <v>-23.76550987166468</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -18489,7 +18481,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18844,7 @@
         <v>15.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>23.93</v>
@@ -18877,10 +18869,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.37</v>
+        <v>16.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>30.36</v>
+        <v>30.38</v>
       </c>
       <c r="BB7" t="n">
         <v>64.44</v>
@@ -18889,7 +18881,7 @@
         <v>47.07</v>
       </c>
       <c r="BD7" t="n">
-        <v>106.3</v>
+        <v>106.29</v>
       </c>
       <c r="BE7" t="n">
         <v>62.04</v>
@@ -18907,7 +18899,7 @@
         <v>101.51</v>
       </c>
       <c r="BJ7" t="n">
-        <v>149.16</v>
+        <v>149.17</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -19169,7 +19161,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -19351,7 +19343,7 @@
         <v>18.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>35.32</v>
+        <v>35.33</v>
       </c>
       <c r="BE9" t="n">
         <v>22.8</v>
@@ -19390,7 +19382,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ9" t="n">
@@ -19413,7 +19405,7 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-1.3%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-1.3%))</t>
         </is>
       </c>
     </row>
@@ -19813,7 +19805,7 @@
         <v>19.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>59.97</v>
+        <v>59.96</v>
       </c>
       <c r="BE11" t="n">
         <v>37.67</v>
@@ -19822,7 +19814,7 @@
         <v>40.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>36.73</v>
+        <v>36.74</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -20083,7 +20075,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ12" t="n">
@@ -20106,7 +20098,7 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -20314,10 +20306,10 @@
         </is>
       </c>
       <c r="BQ13" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="BR13" t="n">
-        <v>-5.063880008850452</v>
+        <v>-5.87286813587281</v>
       </c>
       <c r="BS13" t="n">
         <v>-16.85980497860918</v>
@@ -20333,7 +20325,7 @@
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -20545,10 +20537,10 @@
         </is>
       </c>
       <c r="BQ14" t="n">
-        <v>7.929999828338623</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="BR14" t="n">
-        <v>-11.47540816028945</v>
+        <v>-8.831166820555026</v>
       </c>
       <c r="BS14" t="n">
         <v>-59.61021964227024</v>
@@ -20564,7 +20556,7 @@
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
         </is>
       </c>
     </row>
@@ -20776,10 +20768,10 @@
         </is>
       </c>
       <c r="BQ15" t="n">
-        <v>8.420000076293945</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="BR15" t="n">
-        <v>-7.83847792674377</v>
+        <v>-5.596107338245182</v>
       </c>
       <c r="BS15" t="n">
         <v>-28.37008112858783</v>
@@ -20795,7 +20787,7 @@
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -21181,7 +21173,7 @@
         <v>45.68999862670898</v>
       </c>
       <c r="AZ17" t="n">
-        <v>121.42</v>
+        <v>121.41</v>
       </c>
       <c r="BA17" t="n">
         <v>176.78</v>
@@ -21234,10 +21226,10 @@
         </is>
       </c>
       <c r="BQ17" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="BR17" t="n">
-        <v>-6.180702441633368</v>
+        <v>-6.831162777889876</v>
       </c>
       <c r="BS17" t="n">
         <v>-16.33828883951265</v>
@@ -21253,7 +21245,7 @@
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -21461,7 +21453,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ18" t="n">
@@ -21484,7 +21476,7 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -21927,10 +21919,10 @@
         </is>
       </c>
       <c r="BQ20" t="n">
-        <v>23.35000038146973</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="BR20" t="n">
-        <v>-7.366172131063841</v>
+        <v>-5.29772759955166</v>
       </c>
       <c r="BS20" t="n">
         <v>-39.73503176095192</v>
@@ -21946,7 +21938,7 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22352,7 @@
         <v>75.16</v>
       </c>
       <c r="BJ22" t="n">
-        <v>83.05</v>
+        <v>83.06</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -22573,7 +22565,7 @@
         <v>53.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>56.82</v>
+        <v>56.83</v>
       </c>
       <c r="BE23" t="n">
         <v>46.72</v>
@@ -22847,10 +22839,10 @@
         </is>
       </c>
       <c r="BQ24" t="n">
-        <v>29.21999931335449</v>
+        <v>29.06999969482422</v>
       </c>
       <c r="BR24" t="n">
-        <v>-4.89390291386349</v>
+        <v>-4.403160621720859</v>
       </c>
       <c r="BS24" t="n">
         <v>-21.22606264717445</v>
@@ -22866,7 +22858,7 @@
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -23013,10 +23005,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.21</v>
+        <v>19.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="BB25" t="n">
         <v>75.48999999999999</v>
@@ -23025,13 +23017,13 @@
         <v>56.56</v>
       </c>
       <c r="BD25" t="n">
-        <v>99.09</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="BE25" t="n">
         <v>43.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="BG25" t="n">
         <v>32.06</v>
@@ -23043,7 +23035,7 @@
         <v>-36.41</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -23530,10 +23522,10 @@
         </is>
       </c>
       <c r="BQ27" t="n">
-        <v>12.38000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="BR27" t="n">
-        <v>-6.46203702212963</v>
+        <v>-3.820598335584846</v>
       </c>
       <c r="BS27" t="n">
         <v>-32.90019903655219</v>
@@ -23549,7 +23541,7 @@
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24186,7 @@
         <v>203.13</v>
       </c>
       <c r="BJ30" t="n">
-        <v>243.31</v>
+        <v>243.32</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -24595,7 +24587,7 @@
         <v>11.54</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.15</v>
+        <v>10.16</v>
       </c>
       <c r="AR32" t="n">
         <v>13.99</v>
@@ -24628,7 +24620,7 @@
         <v>48.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>73.98</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="BE32" t="n">
         <v>14.24</v>
@@ -24646,7 +24638,7 @@
         <v>-6.81</v>
       </c>
       <c r="BJ32" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -25129,7 +25121,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS34" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="BT34" t="b">
         <v>1</v>
@@ -25354,10 +25346,10 @@
         </is>
       </c>
       <c r="BQ35" t="n">
-        <v>9.979999542236328</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="BR35" t="n">
-        <v>-8.016024787124209</v>
+        <v>-6.134963641897039</v>
       </c>
       <c r="BS35" t="n">
         <v>-49.20898677565268</v>
@@ -25373,7 +25365,7 @@
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25583,7 @@
         <v>-2.664893844804339</v>
       </c>
       <c r="BS36" t="n">
-        <v>-19.62749400029969</v>
+        <v>-19.62750247023346</v>
       </c>
       <c r="BT36" t="b">
         <v>1</v>
@@ -25773,7 +25765,7 @@
         <v>24</v>
       </c>
       <c r="BD37" t="n">
-        <v>24.53</v>
+        <v>24.54</v>
       </c>
       <c r="BE37" t="n">
         <v>19.7</v>
@@ -25788,7 +25780,7 @@
         <v>4</v>
       </c>
       <c r="BI37" t="n">
-        <v>89.47</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="BJ37" t="n">
         <v>92.54000000000001</v>
@@ -25820,7 +25812,7 @@
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ37" t="n">
@@ -25988,10 +25980,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="AZ38" t="n">
-        <v>35.21</v>
+        <v>35.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>51.26</v>
+        <v>51.25</v>
       </c>
       <c r="BB38" t="n">
         <v>49.22</v>
@@ -26001,7 +25993,7 @@
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="n">
-        <v>45.23</v>
+        <v>45.22</v>
       </c>
       <c r="BF38" t="n">
         <v>49.22</v>
@@ -26016,7 +26008,7 @@
         <v>15.41</v>
       </c>
       <c r="BJ38" t="n">
-        <v>17.85</v>
+        <v>17.83</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -26272,10 +26264,10 @@
         </is>
       </c>
       <c r="BQ39" t="n">
-        <v>12.0600004196167</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="BR39" t="n">
-        <v>-10.77943735905924</v>
+        <v>-10.40799314053285</v>
       </c>
       <c r="BS39" t="n">
         <v>-35.14712749925304</v>
@@ -26291,7 +26283,7 @@
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
         </is>
       </c>
     </row>
@@ -26503,13 +26495,13 @@
         </is>
       </c>
       <c r="BQ40" t="n">
-        <v>9.680000305175781</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="BR40" t="n">
-        <v>-9.81405715898066</v>
+        <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866417350647</v>
+        <v>-38.87866842765243</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -26522,7 +26514,7 @@
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
         </is>
       </c>
     </row>
@@ -26699,7 +26691,7 @@
         <v>-9.66</v>
       </c>
       <c r="BJ41" t="n">
-        <v>-1.1</v>
+        <v>-1.11</v>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
@@ -26951,7 +26943,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.71342624530195</v>
+        <v>-16.7134172222279</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -27399,14 +27391,14 @@
       <c r="BO44" t="inlineStr"/>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ44" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="BR44" t="n">
-        <v>-3.191486393612009</v>
+        <v>-3.703704326653801</v>
       </c>
       <c r="BS44" t="n">
         <v>-18.11425560893279</v>
@@ -27422,7 +27414,7 @@
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -27821,7 +27813,7 @@
         <v>28.38</v>
       </c>
       <c r="BG46" t="n">
-        <v>25.54</v>
+        <v>25.55</v>
       </c>
       <c r="BH46" t="n">
         <v>3</v>
@@ -28086,10 +28078,10 @@
         </is>
       </c>
       <c r="BQ47" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="BR47" t="n">
-        <v>-6.28140700507328</v>
+        <v>-7.444173079810589</v>
       </c>
       <c r="BS47" t="n">
         <v>-50.82278080073881</v>
@@ -28105,7 +28097,7 @@
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -28157,7 +28149,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -28309,8 +28301,16 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN48" t="inlineStr"/>
-      <c r="BO48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr">
+        <is>
+          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica operacional robusta no setor de Real Estate, evidenciada por um ROE de 37,6% e um ROIC de 14,4%, ambos posicionados significativamente acima da média dos seus pares setoriais (20,1% e 11,9%, respectivamente), o que sugere uma eficiência superior na alocação de capital e na geração de valor para o acionista. Essa elevada qualidade operacional convive com múltiplos de preço mistos, uma vez que o indicador P/L de 7,12 vezes sinaliza um papel descontado frente à sua capacidade de geração de lucros, enquanto o P/VP de 2,68 revela um prêmio patrimonial exigido pelo mercado. No âmbito financeiro, a rentabilidade de dois dígitos é sustentada por uma estrutura de capital equilibrada, com uma relação de dívida sobre o patrimônio de 0,79 e uma liquidez corrente confortável de 1,96, indicando que o endividamento não compromete a solvência de curto prazo. Por outro lado, o dividend yield de 2,45% mostra-se modesto e reflete uma postura de distribuição contida, coerente com a necessidade de retenção de lucros para fazer frente aos desafios de crescimento e à estrutura de capital, apesar de o pagamento ser sustentável frente à lucratividade atual. O crescimento histórico, contudo, acende um sinal de alerta, visto que a taxa composta anual de receitas nos últimos cinco anos recuou 11,5%, situando-se bem abaixo da média setorial de 3,0% de expansão, o que justifica o atendimento de apenas 4 dos 7 critérios do checklist fundamentalista. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 9,27 pelo método de Bazin e R$ 17,19 pelo modelo de Gordon, até os otimistas R$ 62,58 pelo fluxo de caixa descontado e R$ 89,07 pela fórmula de Lynch. Essa divergência resulta em uma média de R$ 51,34 e uma mediana de R$ 49,55, estabelecendo um preço-teto ajustado com margem de segurança de R$ 44,60 que, comparado à cotação atual de R$ 33,63, projeta um potencial de valorização de 32,6%. Em suma, o investimento em TEND3 coloca em balanço, como pontos positivos, a excelente rentabilidade sobre o capital e o atraente desconto pelo múltiplo de lucros, contrapostos à contração histórica de receita e a um retorno em dividendos ainda tímido para a categoria.</t>
+        </is>
+      </c>
+      <c r="BO48" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BP48" t="inlineStr">
         <is>
           <t>Em Baixa</t>
@@ -28329,14 +28329,14 @@
         <v>1</v>
       </c>
       <c r="BU48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
+          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -28544,10 +28544,10 @@
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.72999954223633</v>
+        <v>25.56999969482422</v>
       </c>
       <c r="BR49" t="n">
-        <v>-5.44111793018941</v>
+        <v>-4.849432091972849</v>
       </c>
       <c r="BS49" t="n">
         <v>-20.03706285314828</v>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -28908,7 +28908,7 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188206235648</v>
+        <v>188534882304</v>
       </c>
       <c r="AN51" t="n">
         <v>7.4</v>
@@ -29002,7 +29002,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49888798862691</v>
+        <v>-18.49889545631056</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -29241,7 +29241,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41669381125899</v>
+        <v>-19.41668752521939</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
@@ -29924,7 +29924,7 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ55" t="n">
@@ -29947,7 +29947,7 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -30159,10 +30159,10 @@
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>47.18999862670898</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="BR56" t="n">
-        <v>-5.064631191355295</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="BS56" t="n">
         <v>-15.45867760032158</v>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -30617,10 +30617,10 @@
         </is>
       </c>
       <c r="BQ58" t="n">
-        <v>29.29999923706055</v>
+        <v>29.29000091552734</v>
       </c>
       <c r="BR58" t="n">
-        <v>-8.225255666094988</v>
+        <v>-8.193927793995414</v>
       </c>
       <c r="BS58" t="n">
         <v>-23.86318934952274</v>
@@ -30820,7 +30820,7 @@
         <v>5</v>
       </c>
       <c r="BI59" t="n">
-        <v>32.67</v>
+        <v>32.68</v>
       </c>
       <c r="BJ59" t="n">
         <v>72.89</v>
@@ -30848,10 +30848,10 @@
         </is>
       </c>
       <c r="BQ59" t="n">
-        <v>26.54999923706055</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="BR59" t="n">
-        <v>-4.896419112682715</v>
+        <v>-4.283545097481212</v>
       </c>
       <c r="BS59" t="n">
         <v>-12.02090826211568</v>
@@ -30867,7 +30867,7 @@
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -31014,10 +31014,10 @@
         <v>40.75</v>
       </c>
       <c r="AZ60" t="n">
-        <v>20.81</v>
+        <v>20.82</v>
       </c>
       <c r="BA60" t="n">
-        <v>38.61</v>
+        <v>38.63</v>
       </c>
       <c r="BB60" t="n">
         <v>56.01</v>
@@ -31026,25 +31026,25 @@
         <v>42.36</v>
       </c>
       <c r="BD60" t="n">
-        <v>59.71</v>
+        <v>59.69</v>
       </c>
       <c r="BE60" t="n">
-        <v>38.48</v>
+        <v>38.49</v>
       </c>
       <c r="BF60" t="n">
-        <v>38.61</v>
+        <v>38.63</v>
       </c>
       <c r="BG60" t="n">
-        <v>34.75</v>
+        <v>34.76</v>
       </c>
       <c r="BH60" t="n">
         <v>3</v>
       </c>
       <c r="BI60" t="n">
-        <v>-14.72</v>
+        <v>-14.69</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-5.57</v>
+        <v>-5.55</v>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.35820625379285</v>
+        <v>-16.32273657221009</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -31300,13 +31300,13 @@
         </is>
       </c>
       <c r="BQ61" t="n">
-        <v>18.00869941711426</v>
+        <v>17.81902885437012</v>
       </c>
       <c r="BR61" t="n">
-        <v>-2.880272661462469</v>
+        <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.6228216922185</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -31710,7 +31710,7 @@
         <v>15.41</v>
       </c>
       <c r="BA63" t="n">
-        <v>23.75</v>
+        <v>23.76</v>
       </c>
       <c r="BB63" t="n">
         <v>44.61</v>
@@ -31762,10 +31762,10 @@
         </is>
       </c>
       <c r="BQ63" t="n">
-        <v>37.22999954223633</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="BR63" t="n">
-        <v>-8.568355267074413</v>
+        <v>-8.346791936095499</v>
       </c>
       <c r="BS63" t="n">
         <v>-30.1313627614148</v>
@@ -31781,7 +31781,7 @@
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
         </is>
       </c>
     </row>
@@ -32163,7 +32163,7 @@
         <v>0.3</v>
       </c>
       <c r="AX65" t="n">
-        <v>38.78</v>
+        <v>38.87</v>
       </c>
       <c r="AY65" t="n">
         <v>30.57999992370605</v>
@@ -32455,10 +32455,10 @@
         </is>
       </c>
       <c r="BQ66" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="BR66" t="n">
-        <v>-3.248254665304118</v>
+        <v>-3.739609749070061</v>
       </c>
       <c r="BS66" t="n">
         <v>-30.08510558619815</v>
@@ -32474,7 +32474,7 @@
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -32825,7 +32825,7 @@
         <v>1</v>
       </c>
       <c r="AM68" t="n">
-        <v>49177673728</v>
+        <v>49176797184</v>
       </c>
       <c r="AN68" t="n">
         <v>22.15</v>
@@ -32889,7 +32889,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
         <v>29.72999954223633</v>
       </c>
       <c r="AZ73" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="BA73" t="n">
         <v>23.92</v>
@@ -34066,10 +34066,10 @@
         </is>
       </c>
       <c r="BQ73" t="n">
-        <v>30.39999961853027</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="BR73" t="n">
-        <v>-2.20394764704388</v>
+        <v>-2.010549134092643</v>
       </c>
       <c r="BS73" t="n">
         <v>-23.41079410625997</v>
@@ -34085,7 +34085,7 @@
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
         <v>1</v>
       </c>
       <c r="AM74" t="n">
-        <v>14564848640</v>
+        <v>14560741376</v>
       </c>
       <c r="AN74" t="n">
         <v>18.33</v>
@@ -34520,10 +34520,10 @@
         </is>
       </c>
       <c r="BQ75" t="n">
-        <v>10.03999996185303</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="BR75" t="n">
-        <v>-8.665337538492491</v>
+        <v>-5.561276619274647</v>
       </c>
       <c r="BS75" t="n">
         <v>-40.00475990261403</v>
@@ -34539,7 +34539,7 @@
       </c>
       <c r="BW75" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -34935,7 +34935,7 @@
         <v>20.23</v>
       </c>
       <c r="BD77" t="n">
-        <v>24.61</v>
+        <v>24.6</v>
       </c>
       <c r="BE77" t="n">
         <v>19.97</v>
@@ -34974,13 +34974,13 @@
         </is>
       </c>
       <c r="BQ77" t="n">
-        <v>35.86999893188477</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="BR77" t="n">
-        <v>-5.436300030681352</v>
+        <v>-5.198436763021363</v>
       </c>
       <c r="BS77" t="n">
-        <v>-24.54173690556859</v>
+        <v>-24.54173046087656</v>
       </c>
       <c r="BT77" t="b">
         <v>0</v>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="BW77" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.2%))</t>
         </is>
       </c>
     </row>
@@ -35173,7 +35173,7 @@
         <v>4</v>
       </c>
       <c r="BI78" t="n">
-        <v>-36.05</v>
+        <v>-36.06</v>
       </c>
       <c r="BJ78" t="n">
         <v>-23.04</v>
@@ -35563,7 +35563,7 @@
         <v>1</v>
       </c>
       <c r="AM80" t="n">
-        <v>45849899008</v>
+        <v>45855367168</v>
       </c>
       <c r="AN80" t="n">
         <v>12.96</v>
@@ -35651,10 +35651,10 @@
         </is>
       </c>
       <c r="BQ80" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="BR80" t="n">
-        <v>-5.104063603995368</v>
+        <v>-5.587506649860686</v>
       </c>
       <c r="BS80" t="n">
         <v>-21.27980526122939</v>
@@ -35670,7 +35670,7 @@
       </c>
       <c r="BW80" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -36101,7 +36101,7 @@
       <c r="BO82" t="inlineStr"/>
       <c r="BP82" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ82" t="n">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="BW82" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-1.2%))</t>
         </is>
       </c>
     </row>
@@ -36332,10 +36332,10 @@
         </is>
       </c>
       <c r="BQ83" t="n">
-        <v>3.670000076293945</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="BR83" t="n">
-        <v>-6.267030362183146</v>
+        <v>-6.010929602486536</v>
       </c>
       <c r="BS83" t="n">
         <v>-52.97216216294481</v>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="BW83" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.0%))</t>
         </is>
       </c>
     </row>
@@ -36956,7 +36956,7 @@
         <v>26.94000053405762</v>
       </c>
       <c r="AZ86" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="BA86" t="n">
         <v>12.57</v>
@@ -36974,7 +36974,7 @@
         <v>12.83</v>
       </c>
       <c r="BF86" t="n">
-        <v>12.7</v>
+        <v>12.71</v>
       </c>
       <c r="BG86" t="n">
         <v>11.43</v>
@@ -36986,7 +36986,7 @@
         <v>-57.56</v>
       </c>
       <c r="BJ86" t="n">
-        <v>-52.37</v>
+        <v>-52.36</v>
       </c>
       <c r="BK86" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
       <c r="BO88" t="inlineStr"/>
       <c r="BP88" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ88" t="n">
@@ -37476,7 +37476,7 @@
       </c>
       <c r="BW88" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.2%))</t>
         </is>
       </c>
     </row>
@@ -38367,7 +38367,7 @@
         <v>-1.900235700265374</v>
       </c>
       <c r="BS92" t="n">
-        <v>-15.22971914757722</v>
+        <v>-15.22972761158513</v>
       </c>
       <c r="BT92" t="b">
         <v>0</v>
@@ -38574,7 +38574,7 @@
       <c r="BO93" t="inlineStr"/>
       <c r="BP93" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ93" t="n">
@@ -38597,7 +38597,7 @@
       </c>
       <c r="BW93" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.0%))</t>
         </is>
       </c>
     </row>
@@ -39437,7 +39437,7 @@
         <v>18.29</v>
       </c>
       <c r="BB97" t="n">
-        <v>22.08</v>
+        <v>22.09</v>
       </c>
       <c r="BC97" t="n">
         <v>31.97</v>
@@ -39452,7 +39452,7 @@
         <v>21.17</v>
       </c>
       <c r="BG97" t="n">
-        <v>19.05</v>
+        <v>19.06</v>
       </c>
       <c r="BH97" t="n">
         <v>5</v>
@@ -39699,10 +39699,10 @@
         </is>
       </c>
       <c r="BQ98" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="BR98" t="n">
-        <v>-5.688768057264582</v>
+        <v>-6.042158746971138</v>
       </c>
       <c r="BS98" t="n">
         <v>-27.1670659463897</v>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.0%))</t>
         </is>
       </c>
     </row>
@@ -39926,14 +39926,14 @@
       </c>
       <c r="BP99" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ99" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="BR99" t="n">
-        <v>-3.13092907875151</v>
+        <v>-3.542749160590919</v>
       </c>
       <c r="BS99" t="n">
         <v>-18.72166979656401</v>
@@ -40739,7 +40739,7 @@
       <c r="AV103" t="inlineStr"/>
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="n">
-        <v>20.25</v>
+        <v>20.27</v>
       </c>
       <c r="AY103" t="n">
         <v>13</v>
@@ -40796,10 +40796,10 @@
         </is>
       </c>
       <c r="BQ103" t="n">
-        <v>14.73999977111816</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="BR103" t="n">
-        <v>-11.80461192765792</v>
+        <v>-11.68478421078172</v>
       </c>
       <c r="BS103" t="n">
         <v>-39.52341924380666</v>
@@ -40815,7 +40815,7 @@
       </c>
       <c r="BW103" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.7%))</t>
         </is>
       </c>
     </row>
@@ -41162,7 +41162,7 @@
         <v>1</v>
       </c>
       <c r="AM105" t="n">
-        <v>3112041728</v>
+        <v>3136304384</v>
       </c>
       <c r="AN105" t="n">
         <v>8.56</v>
@@ -42142,10 +42142,10 @@
         </is>
       </c>
       <c r="BQ109" t="n">
-        <v>3.880000114440918</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="BR109" t="n">
-        <v>-9.020621977522293</v>
+        <v>-7.105262745120189</v>
       </c>
       <c r="BS109" t="n">
         <v>-26.45833685166292</v>
@@ -42161,7 +42161,7 @@
       </c>
       <c r="BW109" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.1%))</t>
         </is>
       </c>
     </row>
@@ -42991,7 +42991,7 @@
         <v>-92.73999999999999</v>
       </c>
       <c r="BJ113" t="n">
-        <v>-91.93000000000001</v>
+        <v>-91.94</v>
       </c>
       <c r="BK113" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
       <c r="BO114" t="inlineStr"/>
       <c r="BP114" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ114" t="n">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="BW114" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -43435,7 +43435,7 @@
         <v>-75.77</v>
       </c>
       <c r="BJ115" t="n">
-        <v>-73.08</v>
+        <v>-73.06999999999999</v>
       </c>
       <c r="BK115" t="inlineStr">
         <is>
@@ -43456,10 +43456,10 @@
         </is>
       </c>
       <c r="BQ115" t="n">
-        <v>3.940000057220459</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="BR115" t="n">
-        <v>-1.522841165181832</v>
+        <v>-1.020407170268323</v>
       </c>
       <c r="BS115" t="n">
         <v>-19.23016222053626</v>
@@ -43475,7 +43475,7 @@
       </c>
       <c r="BW115" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.0%))</t>
         </is>
       </c>
     </row>
@@ -43698,7 +43698,7 @@
       </c>
       <c r="BW116" t="inlineStr">
         <is>
-          <t>Rompimento (vol x2.4, +0.6% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x2.5, +0.6% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -44297,10 +44297,10 @@
         <v>52.13999938964844</v>
       </c>
       <c r="AZ119" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="BA119" t="n">
-        <v>15.87</v>
+        <v>15.86</v>
       </c>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr"/>
@@ -44318,7 +44318,7 @@
         <v>2</v>
       </c>
       <c r="BI119" t="n">
-        <v>-76.90000000000001</v>
+        <v>-76.91</v>
       </c>
       <c r="BJ119" t="n">
         <v>-74.34</v>
@@ -44342,10 +44342,10 @@
         </is>
       </c>
       <c r="BQ119" t="n">
-        <v>57.45000076293945</v>
+        <v>57</v>
       </c>
       <c r="BR119" t="n">
-        <v>-9.242822111007619</v>
+        <v>-8.526316860265904</v>
       </c>
       <c r="BS119" t="n">
         <v>-19.44250955845246</v>
@@ -44361,7 +44361,7 @@
       </c>
       <c r="BW119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
         </is>
       </c>
     </row>
@@ -44413,7 +44413,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -44521,7 +44521,7 @@
         <v>1.21</v>
       </c>
       <c r="BA120" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BB120" t="n">
         <v>1.3</v>
@@ -44545,10 +44545,10 @@
         <v>4</v>
       </c>
       <c r="BI120" t="n">
-        <v>-68.22</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="BJ120" t="n">
-        <v>-64.29000000000001</v>
+        <v>-64.28</v>
       </c>
       <c r="BK120" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
       <c r="BN120" t="inlineStr"/>
       <c r="BO120" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="BP120" t="inlineStr">
@@ -44573,10 +44573,10 @@
         </is>
       </c>
       <c r="BQ120" t="n">
-        <v>3.539999961853027</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="BR120" t="n">
-        <v>0.2824856093507577</v>
+        <v>-0.2808986130333757</v>
       </c>
       <c r="BS120" t="n">
         <v>-43.65079611367132</v>
@@ -44592,7 +44592,7 @@
       </c>
       <c r="BW120" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.7, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="BQ121" t="n">
-        <v>4.840000152587891</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="BR121" t="n">
-        <v>-7.85124178638169</v>
+        <v>-5.907167647502643</v>
       </c>
       <c r="BS121" t="n">
         <v>-57.64482287514247</v>
@@ -44813,7 +44813,7 @@
       </c>
       <c r="BW121" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -44993,7 +44993,7 @@
       <c r="BO122" t="inlineStr"/>
       <c r="BP122" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ122" t="n">
@@ -45016,7 +45016,7 @@
       </c>
       <c r="BW122" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+9.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+9.0%))</t>
         </is>
       </c>
     </row>
@@ -45498,7 +45498,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -45597,7 +45597,7 @@
         <v>1.37</v>
       </c>
       <c r="AX125" t="n">
-        <v>41</v>
+        <v>41.01</v>
       </c>
       <c r="AY125" t="n">
         <v>1.610000014305115</v>
@@ -45630,7 +45630,7 @@
         <v>3</v>
       </c>
       <c r="BI125" t="n">
-        <v>-91.98999999999999</v>
+        <v>-91.98</v>
       </c>
       <c r="BJ125" t="n">
         <v>-91.68000000000001</v>
@@ -45647,17 +45647,21 @@
       </c>
       <c r="BM125" t="inlineStr"/>
       <c r="BN125" t="inlineStr"/>
-      <c r="BO125" t="inlineStr"/>
+      <c r="BO125" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BP125" t="inlineStr">
         <is>
           <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ125" t="n">
-        <v>1.639999985694885</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="BR125" t="n">
-        <v>-1.829266564112753</v>
+        <v>0.6249993946403354</v>
       </c>
       <c r="BS125" t="n">
         <v>-42.61824784986528</v>
@@ -45666,14 +45670,14 @@
         <v>0</v>
       </c>
       <c r="BU125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV125" t="b">
         <v>0</v>
       </c>
       <c r="BW125" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
+          <t>Rompimento (vol x0.6, +0.6% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -45877,13 +45881,13 @@
         </is>
       </c>
       <c r="BQ126" t="n">
-        <v>2.079999923706055</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="BR126" t="n">
-        <v>-7.69230636971937</v>
+        <v>-5.418719992877974</v>
       </c>
       <c r="BS126" t="n">
-        <v>-54.87060603413229</v>
+        <v>-54.87060095233498</v>
       </c>
       <c r="BT126" t="b">
         <v>0</v>
@@ -45896,7 +45900,7 @@
       </c>
       <c r="BW126" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-7.7%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.4%))</t>
         </is>
       </c>
     </row>
@@ -46104,10 +46108,10 @@
         </is>
       </c>
       <c r="BQ127" t="n">
-        <v>20.82999992370605</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="BR127" t="n">
-        <v>-12.86606008157372</v>
+        <v>-11.97866692615981</v>
       </c>
       <c r="BS127" t="n">
         <v>-31.2598598602242</v>
@@ -46123,7 +46127,7 @@
       </c>
       <c r="BW127" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-12.0%))</t>
         </is>
       </c>
     </row>
@@ -46327,14 +46331,14 @@
       <c r="BO128" t="inlineStr"/>
       <c r="BP128" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ128" t="n">
-        <v>14.27999973297119</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="BR128" t="n">
-        <v>-4.831929924971612</v>
+        <v>-5.886422801217616</v>
       </c>
       <c r="BS128" t="n">
         <v>-21.57503186501287</v>
@@ -46350,7 +46354,7 @@
       </c>
       <c r="BW128" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -46528,7 +46532,7 @@
         <v>2</v>
       </c>
       <c r="BI129" t="n">
-        <v>-79.51000000000001</v>
+        <v>-79.5</v>
       </c>
       <c r="BJ129" t="n">
         <v>-77.23</v>
@@ -47133,7 +47137,7 @@
         <v>1</v>
       </c>
       <c r="AM132" t="n">
-        <v>2160784384</v>
+        <v>2167328768</v>
       </c>
       <c r="AN132" t="n">
         <v>35.2</v>
@@ -47870,10 +47874,10 @@
         </is>
       </c>
       <c r="BQ135" t="n">
-        <v>1.070000052452087</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="BR135" t="n">
-        <v>-32.71028099856381</v>
+        <v>-31.42856558974881</v>
       </c>
       <c r="BS135" t="n">
         <v>-86.86131339225869</v>
@@ -47889,7 +47893,7 @@
       </c>
       <c r="BW135" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-32.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-31.4%))</t>
         </is>
       </c>
     </row>
@@ -48097,10 +48101,10 @@
         </is>
       </c>
       <c r="BQ136" t="n">
-        <v>8.840000152587891</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="BR136" t="n">
-        <v>-9.954752253972533</v>
+        <v>-7.549357078384833</v>
       </c>
       <c r="BS136" t="n">
         <v>-47.939829574844</v>
@@ -48116,7 +48120,7 @@
       </c>
       <c r="BW136" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
         </is>
       </c>
     </row>
@@ -48324,10 +48328,10 @@
         </is>
       </c>
       <c r="BQ137" t="n">
-        <v>39.84999847412109</v>
+        <v>39.5</v>
       </c>
       <c r="BR137" t="n">
-        <v>-6.449183922787849</v>
+        <v>-5.620256254944622</v>
       </c>
       <c r="BS137" t="n">
         <v>-19.51640970441861</v>
@@ -48343,7 +48347,7 @@
       </c>
       <c r="BW137" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -48463,7 +48467,7 @@
         <v>1</v>
       </c>
       <c r="AM138" t="n">
-        <v>49977982976</v>
+        <v>50082459648</v>
       </c>
       <c r="AN138" t="n">
         <v>39.13</v>
@@ -48903,7 +48907,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AR140" t="n">
         <v>0.79</v>
@@ -48922,7 +48926,7 @@
         <v>0.76</v>
       </c>
       <c r="AX140" t="n">
-        <v>471.81</v>
+        <v>473.91</v>
       </c>
       <c r="AY140" t="n">
         <v>4.400000095367432</v>
@@ -48955,10 +48959,10 @@
         <v>3</v>
       </c>
       <c r="BI140" t="n">
-        <v>-84.95999999999999</v>
+        <v>-84.95</v>
       </c>
       <c r="BJ140" t="n">
-        <v>-82.68000000000001</v>
+        <v>-82.67</v>
       </c>
       <c r="BK140" t="inlineStr">
         <is>
@@ -49200,10 +49204,10 @@
         </is>
       </c>
       <c r="BQ141" t="n">
-        <v>11.76000022888184</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="BR141" t="n">
-        <v>-8.078229513397417</v>
+        <v>-6.729937210544623</v>
       </c>
       <c r="BS141" t="n">
         <v>-26.26193361437886</v>
@@ -49219,7 +49223,7 @@
       </c>
       <c r="BW141" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.7%))</t>
         </is>
       </c>
     </row>
@@ -49877,10 +49881,10 @@
         </is>
       </c>
       <c r="BQ144" t="n">
-        <v>19.70000076293945</v>
+        <v>19.73999977111816</v>
       </c>
       <c r="BR144" t="n">
-        <v>-6.598990325192277</v>
+        <v>-6.788248065475977</v>
       </c>
       <c r="BS144" t="n">
         <v>-16.70439342946463</v>
@@ -49896,7 +49900,7 @@
       </c>
       <c r="BW144" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -50288,7 +50292,7 @@
         <v>34.54</v>
       </c>
       <c r="BD146" t="n">
-        <v>17.63</v>
+        <v>17.64</v>
       </c>
       <c r="BE146" t="n">
         <v>22.82</v>
@@ -50773,10 +50777,10 @@
         </is>
       </c>
       <c r="BQ148" t="n">
-        <v>74.15000152587891</v>
+        <v>73.62000274658203</v>
       </c>
       <c r="BR148" t="n">
-        <v>-8.496295242231467</v>
+        <v>-7.837549656609899</v>
       </c>
       <c r="BS148" t="n">
         <v>-20.08245317470424</v>
@@ -50792,7 +50796,7 @@
       </c>
       <c r="BW148" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
         </is>
       </c>
     </row>
@@ -50978,10 +50982,10 @@
         </is>
       </c>
       <c r="BQ149" t="n">
-        <v>0.4399999976158142</v>
+        <v>0.4099999964237213</v>
       </c>
       <c r="BR149" t="n">
-        <v>-47.7272714957718</v>
+        <v>-43.90243751743164</v>
       </c>
       <c r="BS149" t="n">
         <v>-98.71937630347001</v>
@@ -50997,7 +51001,7 @@
       </c>
       <c r="BW149" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-47.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-43.9%))</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -1625,7 +1625,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76550462277683</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15145724236707</v>
+        <v>-43.15146077270641</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -9658,7 +9658,7 @@
         <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -10100,7 +10100,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.7134172222279</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -11010,7 +11010,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.71820629342497</v>
+        <v>-19.7182148933239</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -12398,7 +12398,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41668752521939</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
@@ -13091,7 +13091,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35737468710545</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -14232,7 +14232,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32273657221009</v>
+        <v>-16.32272997776186</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -14463,7 +14463,7 @@
         <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.6228216922185</v>
+        <v>-39.62282580198882</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -15387,7 +15387,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82515452490343</v>
+        <v>-25.82514761546183</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -16046,7 +16046,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.18</v>
+        <v>-19.17</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -18468,7 +18468,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="BS5" t="n">
-        <v>-23.76550987166468</v>
+        <v>-23.76550462277683</v>
       </c>
       <c r="BT5" t="b">
         <v>1</v>
@@ -19161,7 +19161,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15145724236707</v>
+        <v>-43.15146077270641</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -26501,7 +26501,7 @@
         <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866842765243</v>
+        <v>-38.87866417350647</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -26943,7 +26943,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="BS42" t="n">
-        <v>-16.7134172222279</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="BT42" t="b">
         <v>1</v>
@@ -27853,7 +27853,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.71820629342497</v>
+        <v>-19.7182148933239</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -29241,7 +29241,7 @@
         <v>-0.2309433623165158</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41668752521939</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
@@ -29934,7 +29934,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35737468710545</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -31075,7 +31075,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32273657221009</v>
+        <v>-16.32272997776186</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -31306,7 +31306,7 @@
         <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.6228216922185</v>
+        <v>-39.62282580198882</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -32230,7 +32230,7 @@
         <v>-14.94578145537126</v>
       </c>
       <c r="BS65" t="n">
-        <v>-25.82515452490343</v>
+        <v>-25.82514761546183</v>
       </c>
       <c r="BT65" t="b">
         <v>1</v>
@@ -32889,7 +32889,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.18</v>
+        <v>-19.17</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -34980,7 +34980,7 @@
         <v>-5.198436763021363</v>
       </c>
       <c r="BS77" t="n">
-        <v>-24.54173046087656</v>
+        <v>-24.54173690556859</v>
       </c>
       <c r="BT77" t="b">
         <v>0</v>
@@ -35173,7 +35173,7 @@
         <v>4</v>
       </c>
       <c r="BI78" t="n">
-        <v>-36.06</v>
+        <v>-36.05</v>
       </c>
       <c r="BJ78" t="n">
         <v>-23.04</v>
@@ -38367,7 +38367,7 @@
         <v>-1.900235700265374</v>
       </c>
       <c r="BS92" t="n">
-        <v>-15.22972761158513</v>
+        <v>-15.22971914757722</v>
       </c>
       <c r="BT92" t="b">
         <v>0</v>
@@ -39699,10 +39699,10 @@
         </is>
       </c>
       <c r="BQ98" t="n">
-        <v>21.35000038146973</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="BR98" t="n">
-        <v>-6.042158746971138</v>
+        <v>-5.688768057264582</v>
       </c>
       <c r="BS98" t="n">
         <v>-27.1670659463897</v>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.0%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.7%))</t>
         </is>
       </c>
     </row>
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="BQ121" t="n">
-        <v>4.739999771118164</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="BR121" t="n">
-        <v>-5.907167647502643</v>
+        <v>-7.85124178638169</v>
       </c>
       <c r="BS121" t="n">
         <v>-57.64482287514247</v>
@@ -44813,7 +44813,7 @@
       </c>
       <c r="BW121" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
         </is>
       </c>
     </row>
@@ -45887,7 +45887,7 @@
         <v>-5.418719992877974</v>
       </c>
       <c r="BS126" t="n">
-        <v>-54.87060095233498</v>
+        <v>-54.87060603413229</v>
       </c>
       <c r="BT126" t="b">
         <v>0</v>
@@ -48101,10 +48101,10 @@
         </is>
       </c>
       <c r="BQ136" t="n">
-        <v>8.609999656677246</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="BR136" t="n">
-        <v>-7.549357078384833</v>
+        <v>-9.954752253972533</v>
       </c>
       <c r="BS136" t="n">
         <v>-47.939829574844</v>
@@ -48120,7 +48120,7 @@
       </c>
       <c r="BW136" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.0%))</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-08.xlsx
+++ b/reports/screener_2026-08-08.xlsx
@@ -2318,7 +2318,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -8278,7 +8278,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS34" t="n">
-        <v>-32.45080650614594</v>
+        <v>-32.45081207696994</v>
       </c>
       <c r="BT34" t="b">
         <v>1</v>
@@ -9658,7 +9658,7 @@
         <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866417350647</v>
+        <v>-38.87866842765243</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -11010,7 +11010,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.7182148933239</v>
+        <v>-19.71820629342497</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -11500,12 +11500,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BOVA11+SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11515,30 +11515,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>58.83</v>
+        <v>59.28</v>
       </c>
       <c r="F49" t="n">
-        <v>57.44</v>
+        <v>55.04</v>
       </c>
       <c r="G49" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>72.81999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>34.82</v>
+        <v>32.69</v>
       </c>
       <c r="K49" t="n">
-        <v>69.09999999999999</v>
+        <v>22.81</v>
       </c>
       <c r="L49" t="n">
-        <v>21.48</v>
+        <v>83.22</v>
       </c>
       <c r="M49" t="n">
         <v>48</v>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -11563,45 +11563,47 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" t="b">
         <v>1</v>
       </c>
       <c r="W49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
         <v>6</v>
       </c>
       <c r="AB49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD49" t="b">
         <v>1</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
+      <c r="AH49" t="b">
+        <v>1</v>
+      </c>
       <c r="AI49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ49" t="b">
         <v>1</v>
@@ -11610,104 +11612,106 @@
       <c r="AL49" t="b">
         <v>1</v>
       </c>
-      <c r="AM49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>51620999168</v>
+      </c>
       <c r="AN49" t="n">
-        <v>11.31</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AO49" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.21</v>
+        <v>8.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.45</v>
+        <v>10.17</v>
       </c>
       <c r="AR49" t="n">
-        <v>12.93</v>
+        <v>23.72</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.16</v>
+        <v>15.33</v>
       </c>
       <c r="AT49" t="n">
-        <v>41.91</v>
+        <v>12.79</v>
       </c>
       <c r="AU49" t="inlineStr"/>
       <c r="AV49" t="n">
-        <v>2.73</v>
+        <v>1.15</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.9</v>
+        <v>1.43</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.21</v>
+        <v>4.26</v>
       </c>
       <c r="AY49" t="n">
-        <v>24.32999992370605</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.26</v>
+        <v>32.55</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.9</v>
+        <v>39.11</v>
       </c>
       <c r="BB49" t="n">
-        <v>28.5</v>
+        <v>42.92</v>
       </c>
       <c r="BC49" t="n">
-        <v>28.4</v>
+        <v>48.76</v>
       </c>
       <c r="BD49" t="n">
-        <v>25.38</v>
+        <v>61.38</v>
       </c>
       <c r="BE49" t="n">
-        <v>27.43</v>
+        <v>44.94</v>
       </c>
       <c r="BF49" t="n">
-        <v>28.4</v>
+        <v>42.92</v>
       </c>
       <c r="BG49" t="n">
-        <v>25.56</v>
+        <v>38.63</v>
       </c>
       <c r="BH49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI49" t="n">
-        <v>5.06</v>
+        <v>-13.78</v>
       </c>
       <c r="BJ49" t="n">
-        <v>12.73</v>
+        <v>0.32</v>
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr"/>
       <c r="BO49" t="inlineStr"/>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.56999969482422</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="BR49" t="n">
-        <v>-4.849432091972849</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="BS49" t="n">
-        <v>-20.03706285314828</v>
+        <v>-15.45867760032158</v>
       </c>
       <c r="BT49" t="b">
         <v>1</v>
@@ -11720,14 +11724,14 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -11742,30 +11746,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>58.81</v>
+        <v>58.83</v>
       </c>
       <c r="F50" t="n">
-        <v>57.42</v>
+        <v>57.44</v>
       </c>
       <c r="G50" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>40.97</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>80.51000000000001</v>
+        <v>34.82</v>
       </c>
       <c r="K50" t="n">
-        <v>76.19</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>36.24</v>
+        <v>21.48</v>
       </c>
       <c r="M50" t="n">
         <v>49</v>
@@ -11779,7 +11783,7 @@
         <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -11814,21 +11818,19 @@
         <v>0</v>
       </c>
       <c r="AC50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="b">
         <v>0</v>
       </c>
@@ -11839,89 +11841,87 @@
       <c r="AL50" t="b">
         <v>1</v>
       </c>
-      <c r="AM50" t="n">
-        <v>3439011840</v>
-      </c>
+      <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="n">
-        <v>4.22</v>
+        <v>11.31</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.44</v>
+        <v>1.46</v>
       </c>
       <c r="AP50" t="n">
-        <v>14.55</v>
+        <v>1.21</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.53</v>
+        <v>2.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>10.39</v>
+        <v>12.93</v>
       </c>
       <c r="AS50" t="n">
-        <v>7.75</v>
+        <v>12.16</v>
       </c>
       <c r="AT50" t="n">
-        <v>7.17</v>
+        <v>41.91</v>
       </c>
       <c r="AU50" t="inlineStr"/>
       <c r="AV50" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.48</v>
+        <v>1.21</v>
       </c>
       <c r="AY50" t="n">
-        <v>17.01000022888184</v>
+        <v>24.32999992370605</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="BA50" t="n">
-        <v>7.96</v>
+        <v>7.9</v>
       </c>
       <c r="BB50" t="n">
-        <v>53.41</v>
+        <v>28.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>59.21</v>
+        <v>28.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>49.87</v>
+        <v>25.38</v>
       </c>
       <c r="BE50" t="n">
-        <v>54.16</v>
+        <v>27.43</v>
       </c>
       <c r="BF50" t="n">
-        <v>53.41</v>
+        <v>28.4</v>
       </c>
       <c r="BG50" t="n">
-        <v>48.07</v>
+        <v>25.56</v>
       </c>
       <c r="BH50" t="n">
         <v>3</v>
       </c>
       <c r="BI50" t="n">
-        <v>182.58</v>
+        <v>5.06</v>
       </c>
       <c r="BJ50" t="n">
-        <v>218.43</v>
+        <v>12.73</v>
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="BM50" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="BN50" t="inlineStr"/>
@@ -11932,13 +11932,13 @@
         </is>
       </c>
       <c r="BQ50" t="n">
-        <v>18.59000015258789</v>
+        <v>25.56999969482422</v>
       </c>
       <c r="BR50" t="n">
-        <v>-8.499192634412678</v>
+        <v>-4.849432091972849</v>
       </c>
       <c r="BS50" t="n">
-        <v>-51.36371256871672</v>
+        <v>-20.03706285314828</v>
       </c>
       <c r="BT50" t="b">
         <v>1</v>
@@ -11951,50 +11951,52 @@
       </c>
       <c r="BW50" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>BOVA11+SMALL11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>BOVA11</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BOVA11</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>58.07</v>
+        <v>58.81</v>
       </c>
       <c r="F51" t="n">
-        <v>54.2</v>
+        <v>57.42</v>
       </c>
       <c r="G51" t="n">
-        <v>80</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>51.13</v>
+        <v>40.97</v>
       </c>
       <c r="J51" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
+        <v>80.51000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>76.19</v>
+      </c>
       <c r="L51" t="n">
-        <v>70.47</v>
+        <v>36.24</v>
       </c>
       <c r="M51" t="n">
         <v>50</v>
@@ -12005,10 +12007,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -12024,9 +12026,11 @@
       <c r="V51" t="b">
         <v>1</v>
       </c>
-      <c r="W51" t="inlineStr"/>
+      <c r="W51" t="b">
+        <v>1</v>
+      </c>
       <c r="X51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -12035,20 +12039,22 @@
         <v>4</v>
       </c>
       <c r="AA51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
-      <c r="AE51" t="inlineStr"/>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
       <c r="AF51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="b">
@@ -12065,84 +12071,88 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188534882304</v>
+        <v>3439011840</v>
       </c>
       <c r="AN51" t="n">
-        <v>7.4</v>
+        <v>4.22</v>
       </c>
       <c r="AO51" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.99</v>
+        <v>14.55</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.32</v>
+        <v>3.53</v>
       </c>
       <c r="AR51" t="n">
-        <v>14.13</v>
+        <v>10.39</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AT51" t="n">
-        <v>26.07</v>
+        <v>7.17</v>
       </c>
       <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
+      <c r="AV51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0.49</v>
+      </c>
       <c r="AX51" t="n">
-        <v>1.36</v>
+        <v>0.48</v>
       </c>
       <c r="AY51" t="n">
-        <v>17.30999946594238</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="AZ51" t="n">
-        <v>10.29</v>
+        <v>4.29</v>
       </c>
       <c r="BA51" t="n">
-        <v>17.72</v>
+        <v>7.96</v>
       </c>
       <c r="BB51" t="n">
-        <v>28.76</v>
+        <v>53.41</v>
       </c>
       <c r="BC51" t="n">
-        <v>29.46</v>
+        <v>59.21</v>
       </c>
       <c r="BD51" t="n">
-        <v>32.16</v>
+        <v>49.87</v>
       </c>
       <c r="BE51" t="n">
-        <v>18.92</v>
+        <v>54.16</v>
       </c>
       <c r="BF51" t="n">
-        <v>17.72</v>
+        <v>53.41</v>
       </c>
       <c r="BG51" t="n">
-        <v>15.95</v>
+        <v>48.07</v>
       </c>
       <c r="BH51" t="n">
         <v>3</v>
       </c>
       <c r="BI51" t="n">
-        <v>-7.88</v>
+        <v>182.58</v>
       </c>
       <c r="BJ51" t="n">
-        <v>9.33</v>
+        <v>218.43</v>
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="BM51" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="BN51" t="inlineStr"/>
@@ -12153,13 +12163,13 @@
         </is>
       </c>
       <c r="BQ51" t="n">
-        <v>18.95059585571289</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="BR51" t="n">
-        <v>-8.657228523376116</v>
+        <v>-8.499192634412678</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49889545631056</v>
+        <v>-51.36371256871672</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -12172,19 +12182,19 @@
       </c>
       <c r="BW51" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BOVA11+SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12194,44 +12204,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>57.66</v>
+        <v>58.07</v>
       </c>
       <c r="F52" t="n">
-        <v>56.07</v>
+        <v>54.2</v>
       </c>
       <c r="G52" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>61.02</v>
+        <v>51.13</v>
       </c>
       <c r="J52" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="K52" t="n">
-        <v>66.41</v>
-      </c>
+        <v>53.24</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>40.94</v>
+        <v>70.47</v>
       </c>
       <c r="M52" t="n">
         <v>51</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -12247,35 +12255,31 @@
       <c r="V52" t="b">
         <v>1</v>
       </c>
-      <c r="W52" t="b">
-        <v>1</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="b">
         <v>1</v>
       </c>
       <c r="Y52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>4</v>
       </c>
       <c r="AA52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
-      <c r="AE52" t="b">
-        <v>1</v>
-      </c>
+      <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="b">
@@ -12292,133 +12296,121 @@
         <v>1</v>
       </c>
       <c r="AM52" t="n">
-        <v>15206233088</v>
+        <v>188534882304</v>
       </c>
       <c r="AN52" t="n">
-        <v>8.710000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AO52" t="n">
         <v>1.05</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.87</v>
+        <v>8.99</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.87</v>
+        <v>8.32</v>
       </c>
       <c r="AR52" t="n">
-        <v>12.1</v>
+        <v>14.13</v>
       </c>
       <c r="AS52" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>19.49</v>
+        <v>26.07</v>
       </c>
       <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AY52" t="n">
-        <v>21.60000038146973</v>
+        <v>17.30999946594238</v>
       </c>
       <c r="AZ52" t="n">
-        <v>5.97</v>
+        <v>10.29</v>
       </c>
       <c r="BA52" t="n">
-        <v>11.08</v>
+        <v>17.72</v>
       </c>
       <c r="BB52" t="n">
-        <v>32.86</v>
+        <v>28.76</v>
       </c>
       <c r="BC52" t="n">
-        <v>33.88</v>
+        <v>29.46</v>
       </c>
       <c r="BD52" t="n">
-        <v>29.49</v>
+        <v>32.16</v>
       </c>
       <c r="BE52" t="n">
-        <v>32.08</v>
+        <v>18.92</v>
       </c>
       <c r="BF52" t="n">
-        <v>32.86</v>
+        <v>17.72</v>
       </c>
       <c r="BG52" t="n">
-        <v>29.57</v>
+        <v>15.95</v>
       </c>
       <c r="BH52" t="n">
         <v>3</v>
       </c>
       <c r="BI52" t="n">
-        <v>36.91</v>
+        <v>-7.88</v>
       </c>
       <c r="BJ52" t="n">
-        <v>48.5</v>
+        <v>9.33</v>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="BM52" t="inlineStr">
         <is>
-          <t>última</t>
-        </is>
-      </c>
-      <c r="BN52" t="inlineStr">
-        <is>
-          <t>A Hypera (HYPE3) apresenta-se como um caso de estudo interessante no setor de saúde, onde a eficiência no uso do capital próprio se destaca com um ROE de 12,1%, posicionando-se acima da média setorial de 8,9%, embora o retorno sobre o capital investido (ROIC) de 10,7% fique ligeiramente abaixo dos 12,4% dos seus pares. Essa sólida rentabilidade convive com múltiplos de valuation bastante atrativos, evidenciados pelo P/L de 8,71 e pelo P/VP de 1,05, o que sugere uma relação de qualidade versus preço altamente favorável para o investidor focado em valor. No âmbito financeiro, a companhia demonstra um perfil de endividamento equilibrado, com uma relação dívida/patrimônio de 0,62 e uma confortável liquidez corrente de 1,96, garantindo que a operação permaneça saudável e menos exposta a riscos de crédito. O dividendo atual de 4,87% mostra-se sustentável e coerente com a forte margem líquida de 19,49%, embora o crescimento de longo prazo acenda um sinal de alerta, dado que o CAGR de receita de cinco anos de 86,7% ficou significativamente abaixo da média do setor de 208,6%. Essa perda de tração frente aos concorrentes reflete-se no checklist de critérios fundamentais da empresa, que atendeu a apenas 3 dos 7 requisitos analisados, penalizado principalmente pelo crescimento inferior aos pares, pela ausência de vendas de insiders e por retornos que não superam a taxa Selic. No campo do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa e ativos frente aos de dividendos, variando desde os conservadores R$ 5,97 por Bazin até os R$ 33,88 por Graham. Tomando como referência a média de R$ 32,08 e o preço-teto ajustado com margem de segurança de R$ 29,57, o papel projeta um upside expressivo de 36,9% em relação à cotação atual de R$ 21,60, corroborado por uma tendência gráfica de curto prazo em alta com pivô de alta armado. Em suma, os principais prós da tese residem no valuation descontado, na excelente margem líquida e no robusto potencial de valorização perante os modelos matemáticos, enquanto os contras concentram-se no crescimento histórico abaixo da média setorial e no fraco desempenho no checklist de qualidade e governança.</t>
-        </is>
-      </c>
-      <c r="BO52" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+          <t>próxima</t>
+        </is>
+      </c>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ52" t="n">
-        <v>21.64999961853027</v>
+        <v>18.95059585571289</v>
       </c>
       <c r="BR52" t="n">
-        <v>-0.2309433623165158</v>
+        <v>-8.657228523376116</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41669381125899</v>
+        <v>-18.49890292399284</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
       </c>
       <c r="BU52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12433,41 +12425,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>57.59</v>
+        <v>57.66</v>
       </c>
       <c r="F53" t="n">
-        <v>58.93</v>
+        <v>56.07</v>
       </c>
       <c r="G53" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>74.68000000000001</v>
+        <v>61.02</v>
       </c>
       <c r="J53" t="n">
-        <v>27.16</v>
+        <v>44.93</v>
       </c>
       <c r="K53" t="n">
-        <v>50.39</v>
+        <v>66.41</v>
       </c>
       <c r="L53" t="n">
-        <v>84.56</v>
+        <v>40.94</v>
       </c>
       <c r="M53" t="n">
         <v>52</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
         <v>7</v>
@@ -12487,28 +12479,28 @@
         <v>1</v>
       </c>
       <c r="W53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA53" t="n">
         <v>6</v>
       </c>
       <c r="AB53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="b">
         <v>1</v>
       </c>
       <c r="AD53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>1</v>
@@ -12521,7 +12513,7 @@
         <v>1</v>
       </c>
       <c r="AI53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="b">
         <v>1</v>
@@ -12531,83 +12523,83 @@
         <v>1</v>
       </c>
       <c r="AM53" t="n">
-        <v>40564875264</v>
+        <v>15206233088</v>
       </c>
       <c r="AN53" t="n">
-        <v>8.619999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AO53" t="n">
-        <v>1.7</v>
+        <v>1.05</v>
       </c>
       <c r="AP53" t="n">
-        <v>8.34</v>
+        <v>4.87</v>
       </c>
       <c r="AQ53" t="n">
-        <v>10.68</v>
+        <v>3.87</v>
       </c>
       <c r="AR53" t="n">
-        <v>19.7</v>
+        <v>12.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>10.69</v>
+        <v>10.74</v>
       </c>
       <c r="AT53" t="n">
-        <v>33.52</v>
+        <v>19.49</v>
       </c>
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.49</v>
+        <v>0.62</v>
       </c>
       <c r="AX53" t="n">
-        <v>5.53</v>
+        <v>1.09</v>
       </c>
       <c r="AY53" t="n">
-        <v>39.25</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="AZ53" t="n">
-        <v>29.95</v>
+        <v>5.97</v>
       </c>
       <c r="BA53" t="n">
-        <v>34.23</v>
+        <v>11.08</v>
       </c>
       <c r="BB53" t="n">
-        <v>37.17</v>
+        <v>32.86</v>
       </c>
       <c r="BC53" t="n">
-        <v>48.64</v>
+        <v>33.88</v>
       </c>
       <c r="BD53" t="n">
-        <v>55.74</v>
+        <v>29.49</v>
       </c>
       <c r="BE53" t="n">
-        <v>41.15</v>
+        <v>32.08</v>
       </c>
       <c r="BF53" t="n">
-        <v>37.17</v>
+        <v>32.86</v>
       </c>
       <c r="BG53" t="n">
-        <v>33.46</v>
+        <v>29.57</v>
       </c>
       <c r="BH53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BI53" t="n">
-        <v>-14.76</v>
+        <v>36.91</v>
       </c>
       <c r="BJ53" t="n">
-        <v>4.83</v>
+        <v>48.5</v>
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="BM53" t="inlineStr">
@@ -12615,79 +12607,87 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN53" t="inlineStr"/>
-      <c r="BO53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr">
+        <is>
+          <t>A Hypera (HYPE3) apresenta-se como um caso de estudo interessante no setor de saúde, onde a eficiência no uso do capital próprio se destaca com um ROE de 12,1%, posicionando-se acima da média setorial de 8,9%, embora o retorno sobre o capital investido (ROIC) de 10,7% fique ligeiramente abaixo dos 12,4% dos seus pares. Essa sólida rentabilidade convive com múltiplos de valuation bastante atrativos, evidenciados pelo P/L de 8,71 e pelo P/VP de 1,05, o que sugere uma relação de qualidade versus preço altamente favorável para o investidor focado em valor. No âmbito financeiro, a companhia demonstra um perfil de endividamento equilibrado, com uma relação dívida/patrimônio de 0,62 e uma confortável liquidez corrente de 1,96, garantindo que a operação permaneça saudável e menos exposta a riscos de crédito. O dividendo atual de 4,87% mostra-se sustentável e coerente com a forte margem líquida de 19,49%, embora o crescimento de longo prazo acenda um sinal de alerta, dado que o CAGR de receita de cinco anos de 86,7% ficou significativamente abaixo da média do setor de 208,6%. Essa perda de tração frente aos concorrentes reflete-se no checklist de critérios fundamentais da empresa, que atendeu a apenas 3 dos 7 requisitos analisados, penalizado principalmente pelo crescimento inferior aos pares, pela ausência de vendas de insiders e por retornos que não superam a taxa Selic. No campo do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa e ativos frente aos de dividendos, variando desde os conservadores R$ 5,97 por Bazin até os R$ 33,88 por Graham. Tomando como referência a média de R$ 32,08 e o preço-teto ajustado com margem de segurança de R$ 29,57, o papel projeta um upside expressivo de 36,9% em relação à cotação atual de R$ 21,60, corroborado por uma tendência gráfica de curto prazo em alta com pivô de alta armado. Em suma, os principais prós da tese residem no valuation descontado, na excelente margem líquida e no robusto potencial de valorização perante os modelos matemáticos, enquanto os contras concentram-se no crescimento histórico abaixo da média setorial e no fraco desempenho no checklist de qualidade e governança.</t>
+        </is>
+      </c>
+      <c r="BO53" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ53" t="n">
-        <v>41.59000015258789</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="BR53" t="n">
-        <v>-5.62635283482269</v>
+        <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-11.82997062940927</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
       </c>
       <c r="BU53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11+SMALL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.34</v>
+        <v>57.59</v>
       </c>
       <c r="F54" t="n">
-        <v>52.75</v>
+        <v>58.93</v>
       </c>
       <c r="G54" t="n">
-        <v>83.33333333333333</v>
+        <v>50</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>56.56</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>27.79</v>
+        <v>27.16</v>
       </c>
       <c r="K54" t="n">
-        <v>74.59</v>
+        <v>50.39</v>
       </c>
       <c r="L54" t="n">
-        <v>54.36</v>
+        <v>84.56</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -12718,16 +12718,16 @@
         <v>1</v>
       </c>
       <c r="W54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -12742,10 +12742,10 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
@@ -12762,74 +12762,74 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>1902465664</v>
+        <v>40564875264</v>
       </c>
       <c r="AN54" t="n">
-        <v>12.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.34</v>
+        <v>8.34</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5.97</v>
+        <v>10.68</v>
       </c>
       <c r="AR54" t="n">
-        <v>16.39</v>
+        <v>19.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>10.11</v>
+        <v>10.69</v>
       </c>
       <c r="AT54" t="n">
-        <v>8.91</v>
+        <v>33.52</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.05</v>
+        <v>1.49</v>
       </c>
       <c r="AX54" t="n">
-        <v>2.79</v>
+        <v>5.53</v>
       </c>
       <c r="AY54" t="n">
-        <v>22.85000038146973</v>
+        <v>39.25</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9.75</v>
+        <v>29.95</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.84</v>
+        <v>34.23</v>
       </c>
       <c r="BB54" t="n">
-        <v>20.28</v>
+        <v>37.17</v>
       </c>
       <c r="BC54" t="n">
-        <v>21.84</v>
+        <v>48.64</v>
       </c>
       <c r="BD54" t="n">
-        <v>19.34</v>
+        <v>55.74</v>
       </c>
       <c r="BE54" t="n">
-        <v>17.21</v>
+        <v>41.15</v>
       </c>
       <c r="BF54" t="n">
-        <v>19.34</v>
+        <v>37.17</v>
       </c>
       <c r="BG54" t="n">
-        <v>17.41</v>
+        <v>33.46</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-23.81</v>
+        <v>-14.76</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-24.68</v>
+        <v>4.83</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -12850,17 +12850,17 @@
       <c r="BO54" t="inlineStr"/>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>24.03000068664551</v>
+        <v>41.59000015258789</v>
       </c>
       <c r="BR54" t="n">
-        <v>-4.910529635696426</v>
+        <v>-5.62635283482269</v>
       </c>
       <c r="BS54" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.82997062940927</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -12873,52 +12873,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>57.24</v>
+        <v>57.34</v>
       </c>
       <c r="F55" t="n">
-        <v>55.58</v>
+        <v>52.75</v>
       </c>
       <c r="G55" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>86.20999999999999</v>
+        <v>56.56</v>
       </c>
       <c r="J55" t="n">
-        <v>8.460000000000001</v>
+        <v>27.79</v>
       </c>
       <c r="K55" t="n">
-        <v>63.27</v>
+        <v>74.59</v>
       </c>
       <c r="L55" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -12952,13 +12952,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -12973,17 +12973,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -12993,83 +12993,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN55" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO55" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR55" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS55" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT55" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY55" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB55" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC55" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD55" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE55" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF55" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG55" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -13081,17 +13081,17 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR55" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -13104,14 +13104,14 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -13126,30 +13126,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>56.78</v>
+        <v>57.24</v>
       </c>
       <c r="F56" t="n">
-        <v>55.04</v>
+        <v>55.58</v>
       </c>
       <c r="G56" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>75.51000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>32.69</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>22.81</v>
+        <v>63.27</v>
       </c>
       <c r="L56" t="n">
-        <v>83.22</v>
+        <v>20.13</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -13180,10 +13180,10 @@
         <v>1</v>
       </c>
       <c r="W56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -13204,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
@@ -13214,7 +13214,7 @@
         <v>1</v>
       </c>
       <c r="AI56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="b">
         <v>1</v>
@@ -13224,83 +13224,83 @@
         <v>1</v>
       </c>
       <c r="AM56" t="n">
-        <v>51620999168</v>
+        <v>201903325184</v>
       </c>
       <c r="AN56" t="n">
-        <v>8.960000000000001</v>
+        <v>32.3</v>
       </c>
       <c r="AO56" t="n">
-        <v>2.12</v>
+        <v>10.71</v>
       </c>
       <c r="AP56" t="n">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.16</v>
+        <v>2.33</v>
       </c>
       <c r="AR56" t="n">
-        <v>23.72</v>
+        <v>33.16</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.33</v>
+        <v>24.33</v>
       </c>
       <c r="AT56" t="n">
-        <v>12.79</v>
+        <v>15.58</v>
       </c>
       <c r="AU56" t="inlineStr"/>
       <c r="AV56" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.43</v>
+        <v>0.29</v>
       </c>
       <c r="AX56" t="n">
-        <v>4.23</v>
+        <v>3.94</v>
       </c>
       <c r="AY56" t="n">
-        <v>44.79999923706055</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.52</v>
+        <v>8.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>39.14</v>
+        <v>14.86</v>
       </c>
       <c r="BB56" t="n">
-        <v>42.98</v>
+        <v>19.74</v>
       </c>
       <c r="BC56" t="n">
-        <v>48.76</v>
+        <v>12.27</v>
       </c>
       <c r="BD56" t="n">
-        <v>61.41</v>
+        <v>15.69</v>
       </c>
       <c r="BE56" t="n">
-        <v>44.96</v>
+        <v>14.11</v>
       </c>
       <c r="BF56" t="n">
-        <v>42.98</v>
+        <v>14.86</v>
       </c>
       <c r="BG56" t="n">
-        <v>38.68</v>
+        <v>13.37</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-13.66</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.36</v>
+        <v>-70.67</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM56" t="inlineStr">
@@ -13312,17 +13312,17 @@
       <c r="BO56" t="inlineStr"/>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>46.86999893188477</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR56" t="n">
-        <v>-4.416470539784967</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS56" t="n">
-        <v>-15.45867760032158</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT56" t="b">
         <v>1</v>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32272997776186</v>
+        <v>-16.32273657221009</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -14463,7 +14463,7 @@
         <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.62281758244762</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -16046,7 +16046,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -19161,7 +19161,7 @@
         <v>-15.98513225317606</v>
       </c>
       <c r="BS8" t="n">
-        <v>-43.15146077270641</v>
+        <v>-43.15145724236707</v>
       </c>
       <c r="BT8" t="b">
         <v>1</v>
@@ -25121,7 +25121,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="BS34" t="n">
-        <v>-32.45080650614594</v>
+        <v>-32.45081207696994</v>
       </c>
       <c r="BT34" t="b">
         <v>1</v>
@@ -26501,7 +26501,7 @@
         <v>-5.005441340050498</v>
       </c>
       <c r="BS40" t="n">
-        <v>-38.87866417350647</v>
+        <v>-38.87866842765243</v>
       </c>
       <c r="BT40" t="b">
         <v>1</v>
@@ -27853,7 +27853,7 @@
         <v>-0.7123442596116303</v>
       </c>
       <c r="BS46" t="n">
-        <v>-19.7182148933239</v>
+        <v>-19.71820629342497</v>
       </c>
       <c r="BT46" t="b">
         <v>1</v>
@@ -28343,12 +28343,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BOVA11+SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -28358,30 +28358,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>58.83</v>
+        <v>59.28</v>
       </c>
       <c r="F49" t="n">
-        <v>57.44</v>
+        <v>55.04</v>
       </c>
       <c r="G49" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>72.81999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>34.82</v>
+        <v>32.69</v>
       </c>
       <c r="K49" t="n">
-        <v>69.09999999999999</v>
+        <v>22.81</v>
       </c>
       <c r="L49" t="n">
-        <v>21.48</v>
+        <v>83.22</v>
       </c>
       <c r="M49" t="n">
         <v>48</v>
@@ -28392,10 +28392,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -28406,45 +28406,47 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" t="b">
         <v>1</v>
       </c>
       <c r="W49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
         <v>6</v>
       </c>
       <c r="AB49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD49" t="b">
         <v>1</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
+      <c r="AH49" t="b">
+        <v>1</v>
+      </c>
       <c r="AI49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ49" t="b">
         <v>1</v>
@@ -28453,104 +28455,106 @@
       <c r="AL49" t="b">
         <v>1</v>
       </c>
-      <c r="AM49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>51620999168</v>
+      </c>
       <c r="AN49" t="n">
-        <v>11.31</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AO49" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.21</v>
+        <v>8.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.45</v>
+        <v>10.17</v>
       </c>
       <c r="AR49" t="n">
-        <v>12.93</v>
+        <v>23.72</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.16</v>
+        <v>15.33</v>
       </c>
       <c r="AT49" t="n">
-        <v>41.91</v>
+        <v>12.79</v>
       </c>
       <c r="AU49" t="inlineStr"/>
       <c r="AV49" t="n">
-        <v>2.73</v>
+        <v>1.15</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.9</v>
+        <v>1.43</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.21</v>
+        <v>4.26</v>
       </c>
       <c r="AY49" t="n">
-        <v>24.32999992370605</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.26</v>
+        <v>32.55</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.9</v>
+        <v>39.11</v>
       </c>
       <c r="BB49" t="n">
-        <v>28.5</v>
+        <v>42.92</v>
       </c>
       <c r="BC49" t="n">
-        <v>28.4</v>
+        <v>48.76</v>
       </c>
       <c r="BD49" t="n">
-        <v>25.38</v>
+        <v>61.38</v>
       </c>
       <c r="BE49" t="n">
-        <v>27.43</v>
+        <v>44.94</v>
       </c>
       <c r="BF49" t="n">
-        <v>28.4</v>
+        <v>42.92</v>
       </c>
       <c r="BG49" t="n">
-        <v>25.56</v>
+        <v>38.63</v>
       </c>
       <c r="BH49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI49" t="n">
-        <v>5.06</v>
+        <v>-13.78</v>
       </c>
       <c r="BJ49" t="n">
-        <v>12.73</v>
+        <v>0.32</v>
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr"/>
       <c r="BO49" t="inlineStr"/>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ49" t="n">
-        <v>25.56999969482422</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="BR49" t="n">
-        <v>-4.849432091972849</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="BS49" t="n">
-        <v>-20.03706285314828</v>
+        <v>-15.45867760032158</v>
       </c>
       <c r="BT49" t="b">
         <v>1</v>
@@ -28563,14 +28567,14 @@
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -28585,30 +28589,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>58.81</v>
+        <v>58.83</v>
       </c>
       <c r="F50" t="n">
-        <v>57.42</v>
+        <v>57.44</v>
       </c>
       <c r="G50" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>40.97</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>80.51000000000001</v>
+        <v>34.82</v>
       </c>
       <c r="K50" t="n">
-        <v>76.19</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>36.24</v>
+        <v>21.48</v>
       </c>
       <c r="M50" t="n">
         <v>49</v>
@@ -28622,7 +28626,7 @@
         <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -28657,21 +28661,19 @@
         <v>0</v>
       </c>
       <c r="AC50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="b">
         <v>0</v>
       </c>
@@ -28682,89 +28684,87 @@
       <c r="AL50" t="b">
         <v>1</v>
       </c>
-      <c r="AM50" t="n">
-        <v>3439011840</v>
-      </c>
+      <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="n">
-        <v>4.22</v>
+        <v>11.31</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.44</v>
+        <v>1.46</v>
       </c>
       <c r="AP50" t="n">
-        <v>14.55</v>
+        <v>1.21</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.53</v>
+        <v>2.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>10.39</v>
+        <v>12.93</v>
       </c>
       <c r="AS50" t="n">
-        <v>7.75</v>
+        <v>12.16</v>
       </c>
       <c r="AT50" t="n">
-        <v>7.17</v>
+        <v>41.91</v>
       </c>
       <c r="AU50" t="inlineStr"/>
       <c r="AV50" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.48</v>
+        <v>1.21</v>
       </c>
       <c r="AY50" t="n">
-        <v>17.01000022888184</v>
+        <v>24.32999992370605</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="BA50" t="n">
-        <v>7.96</v>
+        <v>7.9</v>
       </c>
       <c r="BB50" t="n">
-        <v>53.41</v>
+        <v>28.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>59.21</v>
+        <v>28.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>49.87</v>
+        <v>25.38</v>
       </c>
       <c r="BE50" t="n">
-        <v>54.16</v>
+        <v>27.43</v>
       </c>
       <c r="BF50" t="n">
-        <v>53.41</v>
+        <v>28.4</v>
       </c>
       <c r="BG50" t="n">
-        <v>48.07</v>
+        <v>25.56</v>
       </c>
       <c r="BH50" t="n">
         <v>3</v>
       </c>
       <c r="BI50" t="n">
-        <v>182.58</v>
+        <v>5.06</v>
       </c>
       <c r="BJ50" t="n">
-        <v>218.43</v>
+        <v>12.73</v>
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="BM50" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="BN50" t="inlineStr"/>
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="BQ50" t="n">
-        <v>18.59000015258789</v>
+        <v>25.56999969482422</v>
       </c>
       <c r="BR50" t="n">
-        <v>-8.499192634412678</v>
+        <v>-4.849432091972849</v>
       </c>
       <c r="BS50" t="n">
-        <v>-51.36371256871672</v>
+        <v>-20.03706285314828</v>
       </c>
       <c r="BT50" t="b">
         <v>1</v>
@@ -28794,50 +28794,52 @@
       </c>
       <c r="BW50" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>BOVA11+SMALL11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>BOVA11</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BOVA11</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>58.07</v>
+        <v>58.81</v>
       </c>
       <c r="F51" t="n">
-        <v>54.2</v>
+        <v>57.42</v>
       </c>
       <c r="G51" t="n">
-        <v>80</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>51.13</v>
+        <v>40.97</v>
       </c>
       <c r="J51" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
+        <v>80.51000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>76.19</v>
+      </c>
       <c r="L51" t="n">
-        <v>70.47</v>
+        <v>36.24</v>
       </c>
       <c r="M51" t="n">
         <v>50</v>
@@ -28848,10 +28850,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -28867,9 +28869,11 @@
       <c r="V51" t="b">
         <v>1</v>
       </c>
-      <c r="W51" t="inlineStr"/>
+      <c r="W51" t="b">
+        <v>1</v>
+      </c>
       <c r="X51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="b">
         <v>1</v>
@@ -28878,20 +28882,22 @@
         <v>4</v>
       </c>
       <c r="AA51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
-      <c r="AE51" t="inlineStr"/>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
       <c r="AF51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="b">
@@ -28908,84 +28914,88 @@
         <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>188534882304</v>
+        <v>3439011840</v>
       </c>
       <c r="AN51" t="n">
-        <v>7.4</v>
+        <v>4.22</v>
       </c>
       <c r="AO51" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.99</v>
+        <v>14.55</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.32</v>
+        <v>3.53</v>
       </c>
       <c r="AR51" t="n">
-        <v>14.13</v>
+        <v>10.39</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AT51" t="n">
-        <v>26.07</v>
+        <v>7.17</v>
       </c>
       <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
+      <c r="AV51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0.49</v>
+      </c>
       <c r="AX51" t="n">
-        <v>1.36</v>
+        <v>0.48</v>
       </c>
       <c r="AY51" t="n">
-        <v>17.30999946594238</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="AZ51" t="n">
-        <v>10.29</v>
+        <v>4.29</v>
       </c>
       <c r="BA51" t="n">
-        <v>17.72</v>
+        <v>7.96</v>
       </c>
       <c r="BB51" t="n">
-        <v>28.76</v>
+        <v>53.41</v>
       </c>
       <c r="BC51" t="n">
-        <v>29.46</v>
+        <v>59.21</v>
       </c>
       <c r="BD51" t="n">
-        <v>32.16</v>
+        <v>49.87</v>
       </c>
       <c r="BE51" t="n">
-        <v>18.92</v>
+        <v>54.16</v>
       </c>
       <c r="BF51" t="n">
-        <v>17.72</v>
+        <v>53.41</v>
       </c>
       <c r="BG51" t="n">
-        <v>15.95</v>
+        <v>48.07</v>
       </c>
       <c r="BH51" t="n">
         <v>3</v>
       </c>
       <c r="BI51" t="n">
-        <v>-7.88</v>
+        <v>182.58</v>
       </c>
       <c r="BJ51" t="n">
-        <v>9.33</v>
+        <v>218.43</v>
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="BM51" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="BN51" t="inlineStr"/>
@@ -28996,13 +29006,13 @@
         </is>
       </c>
       <c r="BQ51" t="n">
-        <v>18.95059585571289</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="BR51" t="n">
-        <v>-8.657228523376116</v>
+        <v>-8.499192634412678</v>
       </c>
       <c r="BS51" t="n">
-        <v>-18.49889545631056</v>
+        <v>-51.36371256871672</v>
       </c>
       <c r="BT51" t="b">
         <v>1</v>
@@ -29015,19 +29025,19 @@
       </c>
       <c r="BW51" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BOVA11+SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -29037,44 +29047,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>57.66</v>
+        <v>58.07</v>
       </c>
       <c r="F52" t="n">
-        <v>56.07</v>
+        <v>54.2</v>
       </c>
       <c r="G52" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>61.02</v>
+        <v>51.13</v>
       </c>
       <c r="J52" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="K52" t="n">
-        <v>66.41</v>
-      </c>
+        <v>53.24</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>40.94</v>
+        <v>70.47</v>
       </c>
       <c r="M52" t="n">
         <v>51</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -29090,35 +29098,31 @@
       <c r="V52" t="b">
         <v>1</v>
       </c>
-      <c r="W52" t="b">
-        <v>1</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="b">
         <v>1</v>
       </c>
       <c r="Y52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>4</v>
       </c>
       <c r="AA52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
-      <c r="AE52" t="b">
-        <v>1</v>
-      </c>
+      <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="b">
@@ -29135,133 +29139,121 @@
         <v>1</v>
       </c>
       <c r="AM52" t="n">
-        <v>15206233088</v>
+        <v>188534882304</v>
       </c>
       <c r="AN52" t="n">
-        <v>8.710000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AO52" t="n">
         <v>1.05</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.87</v>
+        <v>8.99</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.87</v>
+        <v>8.32</v>
       </c>
       <c r="AR52" t="n">
-        <v>12.1</v>
+        <v>14.13</v>
       </c>
       <c r="AS52" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>19.49</v>
+        <v>26.07</v>
       </c>
       <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AY52" t="n">
-        <v>21.60000038146973</v>
+        <v>17.30999946594238</v>
       </c>
       <c r="AZ52" t="n">
-        <v>5.97</v>
+        <v>10.29</v>
       </c>
       <c r="BA52" t="n">
-        <v>11.08</v>
+        <v>17.72</v>
       </c>
       <c r="BB52" t="n">
-        <v>32.86</v>
+        <v>28.76</v>
       </c>
       <c r="BC52" t="n">
-        <v>33.88</v>
+        <v>29.46</v>
       </c>
       <c r="BD52" t="n">
-        <v>29.49</v>
+        <v>32.16</v>
       </c>
       <c r="BE52" t="n">
-        <v>32.08</v>
+        <v>18.92</v>
       </c>
       <c r="BF52" t="n">
-        <v>32.86</v>
+        <v>17.72</v>
       </c>
       <c r="BG52" t="n">
-        <v>29.57</v>
+        <v>15.95</v>
       </c>
       <c r="BH52" t="n">
         <v>3</v>
       </c>
       <c r="BI52" t="n">
-        <v>36.91</v>
+        <v>-7.88</v>
       </c>
       <c r="BJ52" t="n">
-        <v>48.5</v>
+        <v>9.33</v>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="BM52" t="inlineStr">
         <is>
-          <t>última</t>
-        </is>
-      </c>
-      <c r="BN52" t="inlineStr">
-        <is>
-          <t>A Hypera (HYPE3) apresenta-se como um caso de estudo interessante no setor de saúde, onde a eficiência no uso do capital próprio se destaca com um ROE de 12,1%, posicionando-se acima da média setorial de 8,9%, embora o retorno sobre o capital investido (ROIC) de 10,7% fique ligeiramente abaixo dos 12,4% dos seus pares. Essa sólida rentabilidade convive com múltiplos de valuation bastante atrativos, evidenciados pelo P/L de 8,71 e pelo P/VP de 1,05, o que sugere uma relação de qualidade versus preço altamente favorável para o investidor focado em valor. No âmbito financeiro, a companhia demonstra um perfil de endividamento equilibrado, com uma relação dívida/patrimônio de 0,62 e uma confortável liquidez corrente de 1,96, garantindo que a operação permaneça saudável e menos exposta a riscos de crédito. O dividendo atual de 4,87% mostra-se sustentável e coerente com a forte margem líquida de 19,49%, embora o crescimento de longo prazo acenda um sinal de alerta, dado que o CAGR de receita de cinco anos de 86,7% ficou significativamente abaixo da média do setor de 208,6%. Essa perda de tração frente aos concorrentes reflete-se no checklist de critérios fundamentais da empresa, que atendeu a apenas 3 dos 7 requisitos analisados, penalizado principalmente pelo crescimento inferior aos pares, pela ausência de vendas de insiders e por retornos que não superam a taxa Selic. No campo do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa e ativos frente aos de dividendos, variando desde os conservadores R$ 5,97 por Bazin até os R$ 33,88 por Graham. Tomando como referência a média de R$ 32,08 e o preço-teto ajustado com margem de segurança de R$ 29,57, o papel projeta um upside expressivo de 36,9% em relação à cotação atual de R$ 21,60, corroborado por uma tendência gráfica de curto prazo em alta com pivô de alta armado. Em suma, os principais prós da tese residem no valuation descontado, na excelente margem líquida e no robusto potencial de valorização perante os modelos matemáticos, enquanto os contras concentram-se no crescimento histórico abaixo da média setorial e no fraco desempenho no checklist de qualidade e governança.</t>
-        </is>
-      </c>
-      <c r="BO52" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+          <t>próxima</t>
+        </is>
+      </c>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ52" t="n">
-        <v>21.64999961853027</v>
+        <v>18.95059585571289</v>
       </c>
       <c r="BR52" t="n">
-        <v>-0.2309433623165158</v>
+        <v>-8.657228523376116</v>
       </c>
       <c r="BS52" t="n">
-        <v>-19.41669381125899</v>
+        <v>-18.49890292399284</v>
       </c>
       <c r="BT52" t="b">
         <v>1</v>
       </c>
       <c r="BU52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW52" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -29276,41 +29268,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>57.59</v>
+        <v>57.66</v>
       </c>
       <c r="F53" t="n">
-        <v>58.93</v>
+        <v>56.07</v>
       </c>
       <c r="G53" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>74.68000000000001</v>
+        <v>61.02</v>
       </c>
       <c r="J53" t="n">
-        <v>27.16</v>
+        <v>44.93</v>
       </c>
       <c r="K53" t="n">
-        <v>50.39</v>
+        <v>66.41</v>
       </c>
       <c r="L53" t="n">
-        <v>84.56</v>
+        <v>40.94</v>
       </c>
       <c r="M53" t="n">
         <v>52</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
         <v>7</v>
@@ -29330,28 +29322,28 @@
         <v>1</v>
       </c>
       <c r="W53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA53" t="n">
         <v>6</v>
       </c>
       <c r="AB53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="b">
         <v>1</v>
       </c>
       <c r="AD53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>1</v>
@@ -29364,7 +29356,7 @@
         <v>1</v>
       </c>
       <c r="AI53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="b">
         <v>1</v>
@@ -29374,83 +29366,83 @@
         <v>1</v>
       </c>
       <c r="AM53" t="n">
-        <v>40564875264</v>
+        <v>15206233088</v>
       </c>
       <c r="AN53" t="n">
-        <v>8.619999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AO53" t="n">
-        <v>1.7</v>
+        <v>1.05</v>
       </c>
       <c r="AP53" t="n">
-        <v>8.34</v>
+        <v>4.87</v>
       </c>
       <c r="AQ53" t="n">
-        <v>10.68</v>
+        <v>3.87</v>
       </c>
       <c r="AR53" t="n">
-        <v>19.7</v>
+        <v>12.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>10.69</v>
+        <v>10.74</v>
       </c>
       <c r="AT53" t="n">
-        <v>33.52</v>
+        <v>19.49</v>
       </c>
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.49</v>
+        <v>0.62</v>
       </c>
       <c r="AX53" t="n">
-        <v>5.53</v>
+        <v>1.09</v>
       </c>
       <c r="AY53" t="n">
-        <v>39.25</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="AZ53" t="n">
-        <v>29.95</v>
+        <v>5.97</v>
       </c>
       <c r="BA53" t="n">
-        <v>34.23</v>
+        <v>11.08</v>
       </c>
       <c r="BB53" t="n">
-        <v>37.17</v>
+        <v>32.86</v>
       </c>
       <c r="BC53" t="n">
-        <v>48.64</v>
+        <v>33.88</v>
       </c>
       <c r="BD53" t="n">
-        <v>55.74</v>
+        <v>29.49</v>
       </c>
       <c r="BE53" t="n">
-        <v>41.15</v>
+        <v>32.08</v>
       </c>
       <c r="BF53" t="n">
-        <v>37.17</v>
+        <v>32.86</v>
       </c>
       <c r="BG53" t="n">
-        <v>33.46</v>
+        <v>29.57</v>
       </c>
       <c r="BH53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BI53" t="n">
-        <v>-14.76</v>
+        <v>36.91</v>
       </c>
       <c r="BJ53" t="n">
-        <v>4.83</v>
+        <v>48.5</v>
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="BM53" t="inlineStr">
@@ -29458,79 +29450,87 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BN53" t="inlineStr"/>
-      <c r="BO53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr">
+        <is>
+          <t>A Hypera (HYPE3) apresenta-se como um caso de estudo interessante no setor de saúde, onde a eficiência no uso do capital próprio se destaca com um ROE de 12,1%, posicionando-se acima da média setorial de 8,9%, embora o retorno sobre o capital investido (ROIC) de 10,7% fique ligeiramente abaixo dos 12,4% dos seus pares. Essa sólida rentabilidade convive com múltiplos de valuation bastante atrativos, evidenciados pelo P/L de 8,71 e pelo P/VP de 1,05, o que sugere uma relação de qualidade versus preço altamente favorável para o investidor focado em valor. No âmbito financeiro, a companhia demonstra um perfil de endividamento equilibrado, com uma relação dívida/patrimônio de 0,62 e uma confortável liquidez corrente de 1,96, garantindo que a operação permaneça saudável e menos exposta a riscos de crédito. O dividendo atual de 4,87% mostra-se sustentável e coerente com a forte margem líquida de 19,49%, embora o crescimento de longo prazo acenda um sinal de alerta, dado que o CAGR de receita de cinco anos de 86,7% ficou significativamente abaixo da média do setor de 208,6%. Essa perda de tração frente aos concorrentes reflete-se no checklist de critérios fundamentais da empresa, que atendeu a apenas 3 dos 7 requisitos analisados, penalizado principalmente pelo crescimento inferior aos pares, pela ausência de vendas de insiders e por retornos que não superam a taxa Selic. No campo do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa e ativos frente aos de dividendos, variando desde os conservadores R$ 5,97 por Bazin até os R$ 33,88 por Graham. Tomando como referência a média de R$ 32,08 e o preço-teto ajustado com margem de segurança de R$ 29,57, o papel projeta um upside expressivo de 36,9% em relação à cotação atual de R$ 21,60, corroborado por uma tendência gráfica de curto prazo em alta com pivô de alta armado. Em suma, os principais prós da tese residem no valuation descontado, na excelente margem líquida e no robusto potencial de valorização perante os modelos matemáticos, enquanto os contras concentram-se no crescimento histórico abaixo da média setorial e no fraco desempenho no checklist de qualidade e governança.</t>
+        </is>
+      </c>
+      <c r="BO53" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ53" t="n">
-        <v>41.59000015258789</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="BR53" t="n">
-        <v>-5.62635283482269</v>
+        <v>-0.2309433623165158</v>
       </c>
       <c r="BS53" t="n">
-        <v>-11.82997062940927</v>
+        <v>-19.41669381125899</v>
       </c>
       <c r="BT53" t="b">
         <v>1</v>
       </c>
       <c r="BU53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11+SMALL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SMALL11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>57.34</v>
+        <v>57.59</v>
       </c>
       <c r="F54" t="n">
-        <v>52.75</v>
+        <v>58.93</v>
       </c>
       <c r="G54" t="n">
-        <v>83.33333333333333</v>
+        <v>50</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>56.56</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>27.79</v>
+        <v>27.16</v>
       </c>
       <c r="K54" t="n">
-        <v>74.59</v>
+        <v>50.39</v>
       </c>
       <c r="L54" t="n">
-        <v>54.36</v>
+        <v>84.56</v>
       </c>
       <c r="M54" t="n">
         <v>53</v>
@@ -29561,16 +29561,16 @@
         <v>1</v>
       </c>
       <c r="W54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA54" t="n">
         <v>6</v>
@@ -29585,10 +29585,10 @@
         <v>1</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="b">
@@ -29605,74 +29605,74 @@
         <v>1</v>
       </c>
       <c r="AM54" t="n">
-        <v>1902465664</v>
+        <v>40564875264</v>
       </c>
       <c r="AN54" t="n">
-        <v>12.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.34</v>
+        <v>8.34</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5.97</v>
+        <v>10.68</v>
       </c>
       <c r="AR54" t="n">
-        <v>16.39</v>
+        <v>19.7</v>
       </c>
       <c r="AS54" t="n">
-        <v>10.11</v>
+        <v>10.69</v>
       </c>
       <c r="AT54" t="n">
-        <v>8.91</v>
+        <v>33.52</v>
       </c>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.05</v>
+        <v>1.49</v>
       </c>
       <c r="AX54" t="n">
-        <v>2.79</v>
+        <v>5.53</v>
       </c>
       <c r="AY54" t="n">
-        <v>22.85000038146973</v>
+        <v>39.25</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9.75</v>
+        <v>29.95</v>
       </c>
       <c r="BA54" t="n">
-        <v>14.84</v>
+        <v>34.23</v>
       </c>
       <c r="BB54" t="n">
-        <v>20.28</v>
+        <v>37.17</v>
       </c>
       <c r="BC54" t="n">
-        <v>21.84</v>
+        <v>48.64</v>
       </c>
       <c r="BD54" t="n">
-        <v>19.34</v>
+        <v>55.74</v>
       </c>
       <c r="BE54" t="n">
-        <v>17.21</v>
+        <v>41.15</v>
       </c>
       <c r="BF54" t="n">
-        <v>19.34</v>
+        <v>37.17</v>
       </c>
       <c r="BG54" t="n">
-        <v>17.41</v>
+        <v>33.46</v>
       </c>
       <c r="BH54" t="n">
         <v>5</v>
       </c>
       <c r="BI54" t="n">
-        <v>-23.81</v>
+        <v>-14.76</v>
       </c>
       <c r="BJ54" t="n">
-        <v>-24.68</v>
+        <v>4.83</v>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
@@ -29693,17 +29693,17 @@
       <c r="BO54" t="inlineStr"/>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BQ54" t="n">
-        <v>24.03000068664551</v>
+        <v>41.59000015258789</v>
       </c>
       <c r="BR54" t="n">
-        <v>-4.910529635696426</v>
+        <v>-5.62635283482269</v>
       </c>
       <c r="BS54" t="n">
-        <v>-19.57500722208761</v>
+        <v>-11.82997062940927</v>
       </c>
       <c r="BT54" t="b">
         <v>1</v>
@@ -29716,52 +29716,52 @@
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SMALL11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>57.24</v>
+        <v>57.34</v>
       </c>
       <c r="F55" t="n">
-        <v>55.58</v>
+        <v>52.75</v>
       </c>
       <c r="G55" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>86.20999999999999</v>
+        <v>56.56</v>
       </c>
       <c r="J55" t="n">
-        <v>8.460000000000001</v>
+        <v>27.79</v>
       </c>
       <c r="K55" t="n">
-        <v>63.27</v>
+        <v>74.59</v>
       </c>
       <c r="L55" t="n">
-        <v>20.13</v>
+        <v>54.36</v>
       </c>
       <c r="M55" t="n">
         <v>54</v>
@@ -29772,7 +29772,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
         <v>7</v>
@@ -29795,13 +29795,13 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="b">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
         <v>6</v>
@@ -29816,17 +29816,17 @@
         <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="b">
         <v>1</v>
       </c>
       <c r="AI55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="b">
         <v>1</v>
@@ -29836,83 +29836,83 @@
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>201903325184</v>
+        <v>1902465664</v>
       </c>
       <c r="AN55" t="n">
-        <v>32.3</v>
+        <v>12.25</v>
       </c>
       <c r="AO55" t="n">
-        <v>10.71</v>
+        <v>2.01</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.17</v>
+        <v>9.34</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.33</v>
+        <v>5.97</v>
       </c>
       <c r="AR55" t="n">
-        <v>33.16</v>
+        <v>16.39</v>
       </c>
       <c r="AS55" t="n">
-        <v>24.33</v>
+        <v>10.11</v>
       </c>
       <c r="AT55" t="n">
-        <v>15.58</v>
+        <v>8.91</v>
       </c>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.94</v>
+        <v>2.79</v>
       </c>
       <c r="AY55" t="n">
-        <v>48.11999893188477</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8.01</v>
+        <v>9.75</v>
       </c>
       <c r="BA55" t="n">
-        <v>14.86</v>
+        <v>14.84</v>
       </c>
       <c r="BB55" t="n">
-        <v>19.74</v>
+        <v>20.28</v>
       </c>
       <c r="BC55" t="n">
-        <v>12.27</v>
+        <v>21.84</v>
       </c>
       <c r="BD55" t="n">
-        <v>15.69</v>
+        <v>19.34</v>
       </c>
       <c r="BE55" t="n">
-        <v>14.11</v>
+        <v>17.21</v>
       </c>
       <c r="BF55" t="n">
-        <v>14.86</v>
+        <v>19.34</v>
       </c>
       <c r="BG55" t="n">
-        <v>13.37</v>
+        <v>17.41</v>
       </c>
       <c r="BH55" t="n">
         <v>5</v>
       </c>
       <c r="BI55" t="n">
-        <v>-72.20999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-70.67</v>
+        <v>-24.68</v>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
@@ -29924,17 +29924,17 @@
       <c r="BO55" t="inlineStr"/>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BQ55" t="n">
-        <v>49.16999816894531</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="BR55" t="n">
-        <v>-2.135446972059685</v>
+        <v>-4.910529635696426</v>
       </c>
       <c r="BS55" t="n">
-        <v>-11.35736832508161</v>
+        <v>-19.57500722208761</v>
       </c>
       <c r="BT55" t="b">
         <v>1</v>
@@ -29947,14 +29947,14 @@
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -29969,30 +29969,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>56.78</v>
+        <v>57.24</v>
       </c>
       <c r="F56" t="n">
-        <v>55.04</v>
+        <v>55.58</v>
       </c>
       <c r="G56" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>75.51000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>32.69</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>22.81</v>
+        <v>63.27</v>
       </c>
       <c r="L56" t="n">
-        <v>83.22</v>
+        <v>20.13</v>
       </c>
       <c r="M56" t="n">
         <v>55</v>
@@ -30023,10 +30023,10 @@
         <v>1</v>
       </c>
       <c r="W56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="b">
         <v>1</v>
@@ -30047,7 +30047,7 @@
         <v>1</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
@@ -30057,7 +30057,7 @@
         <v>1</v>
       </c>
       <c r="AI56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="b">
         <v>1</v>
@@ -30067,83 +30067,83 @@
         <v>1</v>
       </c>
       <c r="AM56" t="n">
-        <v>51620999168</v>
+        <v>201903325184</v>
       </c>
       <c r="AN56" t="n">
-        <v>8.960000000000001</v>
+        <v>32.3</v>
       </c>
       <c r="AO56" t="n">
-        <v>2.12</v>
+        <v>10.71</v>
       </c>
       <c r="AP56" t="n">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10.16</v>
+        <v>2.33</v>
       </c>
       <c r="AR56" t="n">
-        <v>23.72</v>
+        <v>33.16</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.33</v>
+        <v>24.33</v>
       </c>
       <c r="AT56" t="n">
-        <v>12.79</v>
+        <v>15.58</v>
       </c>
       <c r="AU56" t="inlineStr"/>
       <c r="AV56" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.43</v>
+        <v>0.29</v>
       </c>
       <c r="AX56" t="n">
-        <v>4.23</v>
+        <v>3.94</v>
       </c>
       <c r="AY56" t="n">
-        <v>44.79999923706055</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="AZ56" t="n">
-        <v>32.52</v>
+        <v>8.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>39.14</v>
+        <v>14.86</v>
       </c>
       <c r="BB56" t="n">
-        <v>42.98</v>
+        <v>19.74</v>
       </c>
       <c r="BC56" t="n">
-        <v>48.76</v>
+        <v>12.27</v>
       </c>
       <c r="BD56" t="n">
-        <v>61.41</v>
+        <v>15.69</v>
       </c>
       <c r="BE56" t="n">
-        <v>44.96</v>
+        <v>14.11</v>
       </c>
       <c r="BF56" t="n">
-        <v>42.98</v>
+        <v>14.86</v>
       </c>
       <c r="BG56" t="n">
-        <v>38.68</v>
+        <v>13.37</v>
       </c>
       <c r="BH56" t="n">
         <v>5</v>
       </c>
       <c r="BI56" t="n">
-        <v>-13.66</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.36</v>
+        <v>-70.67</v>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="BL56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="BM56" t="inlineStr">
@@ -30155,17 +30155,17 @@
       <c r="BO56" t="inlineStr"/>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BQ56" t="n">
-        <v>46.86999893188477</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="BR56" t="n">
-        <v>-4.416470539784967</v>
+        <v>-2.135446972059685</v>
       </c>
       <c r="BS56" t="n">
-        <v>-15.45867760032158</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="BT56" t="b">
         <v>1</v>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -31075,7 +31075,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="BS60" t="n">
-        <v>-16.32272997776186</v>
+        <v>-16.32273657221009</v>
       </c>
       <c r="BT60" t="b">
         <v>1</v>
@@ -31306,7 +31306,7 @@
         <v>-1.846504015123462</v>
       </c>
       <c r="BS61" t="n">
-        <v>-39.62282580198882</v>
+        <v>-39.62281758244762</v>
       </c>
       <c r="BT61" t="b">
         <v>1</v>
@@ -32889,7 +32889,7 @@
         <v>5</v>
       </c>
       <c r="BI68" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="BJ68" t="n">
         <v>-12.4</v>
@@ -35173,7 +35173,7 @@
         <v>4</v>
       </c>
       <c r="BI78" t="n">
-        <v>-36.05</v>
+        <v>-36.06</v>
       </c>
       <c r="BJ78" t="n">
         <v>-23.04</v>
@@ -37013,7 +37013,7 @@
         <v>-2.285089473123469</v>
       </c>
       <c r="BS86" t="n">
-        <v>-17.85090042584634</v>
+        <v>-17.850910086273</v>
       </c>
       <c r="BT86" t="b">
         <v>0</v>
@@ -39699,10 +39699,10 @@
         </is>
       </c>
       <c r="BQ98" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="BR98" t="n">
-        <v>-5.688768057264582</v>
+        <v>-6.042158746971138</v>
       </c>
       <c r="BS98" t="n">
         <v>-27.1670659463897</v>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.0%))</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>-8.526316860265904</v>
       </c>
       <c r="BS119" t="n">
-        <v>-19.44250955845246</v>
+        <v>-19.44251454422593</v>
       </c>
       <c r="BT119" t="b">
         <v>0</v>
@@ -44794,10 +44794,10 @@
         </is>
       </c>
       <c r="BQ121" t="n">
-        <v>4.840000152587891</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="BR121" t="n">
-        <v>-7.85124178638169</v>
+        <v>-5.907167647502643</v>
       </c>
       <c r="BS121" t="n">
         <v>-57.64482287514247</v>
@@ -44813,7 +44813,7 @@
       </c>
       <c r="BW121" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -48101,10 +48101,10 @@
         </is>
       </c>
       <c r="BQ136" t="n">
-        <v>8.840000152587891</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="BR136" t="n">
-        <v>-9.954752253972533</v>
+        <v>-7.549357078384833</v>
       </c>
       <c r="BS136" t="n">
         <v>-47.939829574844</v>
@@ -48120,7 +48120,7 @@
       </c>
       <c r="BW136" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
         </is>
       </c>
     </row>
